--- a/Trade History Reconstructed.xlsx
+++ b/Trade History Reconstructed.xlsx
@@ -429,66 +429,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:N142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Date(UTC)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Fee Coin</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Pair Price</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Price in USDT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Total in USDT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Pair Quantity</t>
         </is>
@@ -498,46 +503,49 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>46081.50087962963</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>0.2791</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1702.7</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>475.22357</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1.617565</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.2792733316666667</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.2791</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>475.2235700000001</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1702.7</v>
       </c>
     </row>
@@ -545,46 +553,49 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>46081.50046296296</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>63986.13</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.00046</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>29.4336198</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>3.528e-05</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>63900.73367266667</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>63986.13</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>29.4336198</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0.00046</v>
       </c>
     </row>
@@ -592,46 +603,49 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>46081.5003125</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>594.34</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.75</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>445.755</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.0005343</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>594.6545034999999</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>594.34</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>445.755</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -639,46 +653,49 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>46054.61652777778</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>770.6900000000001</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.636</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>490.15884</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.00045314</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>753.2940488333334</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>770.6900000000001</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>490.1588400000001</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.636</v>
       </c>
     </row>
@@ -686,46 +703,49 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>46054.61582175926</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>78597.2</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.00114</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>89.600808</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>8.284e-05</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>77971.77212000001</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>78597.2</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>89.60080799999999</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.00114</v>
       </c>
     </row>
@@ -733,46 +753,49 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>46054.61512731481</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.2859</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>1399</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>399.9741</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.00036997</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0.285821665</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.2859</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>399.9741</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1399</v>
       </c>
     </row>
@@ -780,46 +803,49 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>46023.11693287037</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>869.59</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.083</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>72.17597000000001</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>5.913e-05</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>871.1663310000001</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>869.59</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>72.17597000000001</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>0.083</v>
       </c>
     </row>
@@ -827,46 +853,49 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>46023.11655092592</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>511.04</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.011</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>5.62144</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>4.6e-06</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>510.0416685</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>511.04</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>5.62144</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.011</v>
       </c>
     </row>
@@ -874,46 +903,49 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>46023.11655092592</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>511.01</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.015</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>7.66515</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>6.27e-06</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>510.0416685</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>511.01</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>7.66515</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -921,46 +953,49 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>46023.11655092592</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>511.08</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.011</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>5.62188</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>4.6e-06</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>510.0416685</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>511.08</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>5.621879999999999</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0.011</v>
       </c>
     </row>
@@ -968,46 +1003,49 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>46023.11582175926</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>87764.99000000001</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0.00055</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>48.2707445</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>3.955e-05</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>87944.2532895</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>87764.99000000001</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>48.27074450000001</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0.00055</v>
       </c>
     </row>
@@ -1015,46 +1053,49 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2" t="n">
         <v>45990.61078703704</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>0.2812</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>245.1</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>68.92212000000001</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>5.596e-05</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>0.281253335</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>0.2812</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>68.92212000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>245.1</v>
       </c>
     </row>
@@ -1062,46 +1103,49 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>45990.61035879629</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>460.21</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>0.048</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>22.09008</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1.792e-05</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>459.2474745000001</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>460.21</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>22.09008</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>0.048</v>
       </c>
     </row>
@@ -1109,46 +1153,49 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>45990.60915509259</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>877.15</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>0.103</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>90.34645</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>7.334999999999999e-05</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>876.7868385</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>877.15</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>90.34644999999999</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -1156,46 +1203,49 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2" t="n">
         <v>45962.06081018518</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>1088.98</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.136</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>148.10128</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>9.69e-05</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>1088.9890135</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>1088.98</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>148.10128</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -1203,46 +1253,49 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2" t="n">
         <v>45962.05966435185</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>0.296</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>2624.2</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>776.7632</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>2.49299</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="J17" t="n">
-        <v>0.296</v>
       </c>
       <c r="K17" t="n">
         <v>0.296</v>
       </c>
       <c r="L17" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="M17" t="n">
         <v>776.7631999999999</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>2624.2</v>
       </c>
     </row>
@@ -1250,46 +1303,49 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="n">
         <v>45962.05966435185</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>0.296</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>585.2</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>173.2192</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>0.55594</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="J18" t="n">
-        <v>0.296</v>
       </c>
       <c r="K18" t="n">
         <v>0.296</v>
       </c>
       <c r="L18" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="M18" t="n">
         <v>173.2192</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>585.2</v>
       </c>
     </row>
@@ -1297,46 +1353,49 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2" t="n">
         <v>45962.05902777778</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>109727.81</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>0.01002</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>1099.4726562</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1.04449902</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>109764.5000986667</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>109727.81</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>1099.4726562</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>0.01002</v>
       </c>
     </row>
@@ -1344,46 +1403,49 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2" t="n">
         <v>45931.03042824074</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>113954.4</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.00396</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>451.259424</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>3.834e-05</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>113986.300759</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>113954.4</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>451.259424</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>0.00396</v>
       </c>
     </row>
@@ -1391,46 +1453,49 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" s="2" t="n">
         <v>45931.02980324074</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>0.3329</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>905.7</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>301.50753</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>0.28643215</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>0.3333916683333333</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>0.3329</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>301.50753</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>905.7</v>
       </c>
     </row>
@@ -1438,46 +1503,49 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="2" t="n">
         <v>45931.02895833334</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>0.3329</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>452</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>150.4708</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>0.14294726</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>0.3334</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>0.3329</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>150.4708</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>452</v>
       </c>
     </row>
@@ -1485,46 +1553,49 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="2" t="n">
         <v>45900.93915509259</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>0.3425</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>200.6</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>68.7055</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>5.642e-05</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>0.342961665</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>0.3425</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>68.7055</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>200.6</v>
       </c>
     </row>
@@ -1532,46 +1603,49 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" s="2" t="n">
         <v>45900.93896990741</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>109079.99</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>0.00063</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>68.7203937</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>5.645e-05</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>109075.7142211667</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>109079.99</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>68.7203937</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>0.00063</v>
       </c>
     </row>
@@ -1579,46 +1653,49 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" s="2" t="n">
         <v>45900.93672453704</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>0.34241792</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>2022.6</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>692.57447</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>0.00056949</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>0.3431</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>0.34241792</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>692.574484992</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>2022.6</v>
       </c>
     </row>
@@ -1626,46 +1703,49 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" s="2" t="n">
         <v>45900.93601851852</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>867.28</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>0.019</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>16.47832</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>1.353e-05</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>866.8346673333334</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>867.28</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>16.47832</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>0.019</v>
       </c>
     </row>
@@ -1673,46 +1753,49 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" s="2" t="n">
         <v>45900.93578703704</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>ETHUSDT</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>4462.54</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>0.0693</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>309.254022</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>0.00025404</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>4467.496042999999</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>4462.54</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>309.254022</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>0.0693</v>
       </c>
     </row>
@@ -1720,46 +1803,49 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" s="2" t="n">
         <v>45900.93532407407</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>SOLUSDT</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>204.95</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>1.79</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>366.8605</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>0.0003014</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>205.7853301666667</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>204.95</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>366.8605</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>1.79</v>
       </c>
     </row>
@@ -1767,46 +1853,49 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>841.902968</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>1.648052154152757e-05</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>0.013875</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>3.3e-07</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>894.9224991666665</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>841.902968</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>0.013875</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>1.648052154152757e-05</v>
       </c>
     </row>
@@ -1814,46 +1903,49 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>0.024577</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>0.5645522236237132</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>0.013875</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>3.3e-07</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>0.02457696902309403</v>
       </c>
-      <c r="K30" t="n">
-        <v>0.0006040281676805821</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.0003410054451954297</v>
+        <v>0.000604028167680582</v>
       </c>
       <c r="M30" t="n">
+        <v>0.0003410054451954296</v>
+      </c>
+      <c r="N30" t="n">
         <v>0.5645522236237132</v>
       </c>
     </row>
@@ -1861,46 +1953,49 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>0.015385</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>0.9018524536886579</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>0.013875</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>3.3e-07</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>0.01658150016666667</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>0.015385</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>0.013875</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>0.9018524536886579</v>
       </c>
     </row>
@@ -1908,46 +2003,49 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>894.9224991666665</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>2.229999999999999e-06</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>0.001995677173141666</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>4e-08</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J32" t="n">
-        <v>894.9224991666665</v>
       </c>
       <c r="K32" t="n">
         <v>894.9224991666665</v>
       </c>
       <c r="L32" t="n">
-        <v>0.001995677173141666</v>
+        <v>894.9224991666665</v>
       </c>
       <c r="M32" t="n">
+        <v>0.001995677173141665</v>
+      </c>
+      <c r="N32" t="n">
         <v>2.229999999999999e-06</v>
       </c>
     </row>
@@ -1955,46 +2053,49 @@
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>0.163644480872939</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>0.001995677173141666</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>4e-08</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>0.1749</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>0.163644480872939</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>0.001995677173141666</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>0.0121952</v>
       </c>
     </row>
@@ -2002,46 +2103,49 @@
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>3.747533232175975</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>6.02</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>22.56015005769937</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>3.28e-06</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>0.02457696902309403</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>0.09210300816020439</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>0.5544601091244304</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>6.02</v>
       </c>
     </row>
@@ -2049,46 +2153,49 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="2" t="n">
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>894.922499</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>0.0252090545079696</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>22.56015005769937</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>3.28e-06</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>894.9224991666665</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>894.922499</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>22.56015005769937</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>0.0252090545079696</v>
       </c>
     </row>
@@ -2096,46 +2203,49 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" s="2" t="n">
         <v>45891.84428240741</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>0.02457606291472106</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>8718.124</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>214.2571639223396</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>0.00026837</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>0.02457606291472106</v>
       </c>
-      <c r="K36" t="n">
-        <v>0.0006039828683883278</v>
-      </c>
       <c r="L36" t="n">
-        <v>5.265597540485122</v>
+        <v>0.0006039828683883277</v>
       </c>
       <c r="M36" t="n">
+        <v>5.265597540485121</v>
+      </c>
+      <c r="N36" t="n">
         <v>8718.124</v>
       </c>
     </row>
@@ -2143,46 +2253,49 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" s="2" t="n">
         <v>45891.84428240741</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0.3650036864094372</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>586.9999999999999</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>214.2571639223396</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>0.00026837</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>0.3659</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>0.3650036864094372</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>214.2571639223396</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>586.9999999999999</v>
       </c>
     </row>
@@ -2190,46 +2303,49 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" s="2" t="n">
         <v>45891.84357638889</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>0.02458361491986309</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>8724.144000000002</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>214.4709966014341</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>0.00026861</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>0.02458361491986309</v>
       </c>
-      <c r="K38" t="n">
-        <v>0.0006043541225281151</v>
-      </c>
       <c r="L38" t="n">
-        <v>5.272472391928922</v>
+        <v>0.000604354122528115</v>
       </c>
       <c r="M38" t="n">
+        <v>5.272472391928921</v>
+      </c>
+      <c r="N38" t="n">
         <v>8724.144000000002</v>
       </c>
     </row>
@@ -2237,46 +2353,49 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" s="2" t="n">
         <v>45891.84357638889</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>0.01676602537534663</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>12792</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>214.4709966014341</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>0.00026861</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>0.01655750016666666</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>0.01676602537534663</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>214.4709966014341</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>12792</v>
       </c>
     </row>
@@ -2284,46 +2403,49 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" s="2" t="n">
         <v>45878.0263425926</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>794.6106690000001</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>0.01898484</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>1.423e-05</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J40" t="n">
-        <v>794.6106690000001</v>
       </c>
       <c r="K40" t="n">
         <v>794.6106690000001</v>
       </c>
       <c r="L40" t="n">
+        <v>794.6106690000001</v>
+      </c>
+      <c r="M40" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>0.01898484</v>
       </c>
     </row>
@@ -2331,46 +2453,49 @@
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B41" t="n">
+        <v>39</v>
+      </c>
+      <c r="C41" s="2" t="n">
         <v>45878.0263425926</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>0.1296010001139</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>116.4</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>1.423e-05</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>0.13021333</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>0.1296010001139</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>116.4</v>
       </c>
     </row>
@@ -2378,46 +2503,49 @@
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" s="2" t="n">
         <v>45560.6427662037</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>1.1803</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>57</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>67.2771</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>0.057</v>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>1.179691675</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>1.1803</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>67.27709999999999</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>56.99999999999999</v>
       </c>
     </row>
@@ -2425,46 +2553,49 @@
       <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" s="2" t="n">
         <v>45560.6427662037</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
         <v>1.1803</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>34</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>40.1302</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>0.034</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>1.179691675</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>1.1803</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>40.13019999999999</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>34</v>
       </c>
     </row>
@@ -2472,46 +2603,49 @@
       <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B44" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" s="2" t="n">
         <v>45560.6427662037</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
         <v>1.1802</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>94</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>110.9388</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>0.094</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>1.179691675</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>1.1802</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>110.9388</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>94</v>
       </c>
     </row>
@@ -2519,46 +2653,49 @@
       <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B45" t="n">
+        <v>43</v>
+      </c>
+      <c r="C45" s="2" t="n">
         <v>45560.64236111111</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>0.1508</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>1456.1</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>219.57988</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>0.21957988</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>0.1508000016666667</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>0.1508</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>219.57988</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>1456.1</v>
       </c>
     </row>
@@ -2566,46 +2703,49 @@
       <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B46" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" s="2" t="n">
         <v>45553.90638888889</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>60330.29408616667</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>0.00132203</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>79.75845869073494</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>0.073</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
-      </c>
-      <c r="J46" t="n">
-        <v>60330.29408616667</v>
       </c>
       <c r="K46" t="n">
         <v>60330.29408616667</v>
       </c>
       <c r="L46" t="n">
-        <v>79.75845869073494</v>
+        <v>60330.29408616667</v>
       </c>
       <c r="M46" t="n">
+        <v>79.75845869073493</v>
+      </c>
+      <c r="N46" t="n">
         <v>0.00132203</v>
       </c>
     </row>
@@ -2613,46 +2753,49 @@
       <c r="A47" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" t="n">
+        <v>45</v>
+      </c>
+      <c r="C47" s="2" t="n">
         <v>45553.90638888889</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
         <v>1.092581625900479</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>73</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>79.75845869073494</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>0.073</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>1.091139995</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>1.092581625900479</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>79.75845869073497</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>73</v>
       </c>
     </row>
@@ -2660,46 +2803,49 @@
       <c r="A48" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="2" t="n">
+      <c r="B48" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" s="2" t="n">
         <v>45529.90896990741</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>64353.81012600001</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>0.0025413</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>0.985</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="J48" t="n">
-        <v>64353.81012600001</v>
       </c>
       <c r="K48" t="n">
         <v>64353.81012600001</v>
       </c>
       <c r="L48" t="n">
+        <v>64353.81012600001</v>
+      </c>
+      <c r="M48" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>0.0025413</v>
       </c>
     </row>
@@ -2707,46 +2853,49 @@
       <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="2" t="n">
+      <c r="B49" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" s="2" t="n">
         <v>45529.90896990741</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
         <v>0.16603283012508</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>985</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>0.985</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>0.1655</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>0.16603283012508</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>985</v>
       </c>
     </row>
@@ -2754,46 +2903,49 @@
       <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" t="n">
+        <v>48</v>
+      </c>
+      <c r="C50" s="2" t="n">
         <v>45529.90652777778</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
         <v>0.1655</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>453</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>74.97150000000001</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>9.736e-05</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>0.1654599983333334</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>0.1655</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>74.97150000000001</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>453</v>
       </c>
     </row>
@@ -2801,46 +2953,49 @@
       <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="2" t="n">
+      <c r="B51" t="n">
+        <v>49</v>
+      </c>
+      <c r="C51" s="2" t="n">
         <v>45529.90614583333</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>0.343</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>218.6</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>74.9798</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>9.734999999999999e-05</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>0.3429850016666667</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>0.343</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>74.9798</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>218.6</v>
       </c>
     </row>
@@ -2848,46 +3003,49 @@
       <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" s="2" t="n">
         <v>45528.99840277778</v>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>580.5</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>0.1015056</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>58.92400079999999</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>0.371</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="J52" t="n">
-        <v>580.5</v>
       </c>
       <c r="K52" t="n">
         <v>580.5</v>
       </c>
       <c r="L52" t="n">
-        <v>58.92400079999999</v>
+        <v>580.5</v>
       </c>
       <c r="M52" t="n">
+        <v>58.9240008</v>
+      </c>
+      <c r="N52" t="n">
         <v>0.1015056</v>
       </c>
     </row>
@@ -2895,46 +3053,49 @@
       <c r="A53" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="2" t="n">
+      <c r="B53" t="n">
+        <v>51</v>
+      </c>
+      <c r="C53" s="2" t="n">
         <v>45528.99840277778</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
         <v>0.1588248</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>370.9999999999999</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>58.92400079999999</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>0.371</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>0.1589</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>0.1588248</v>
       </c>
-      <c r="L53" t="n">
-        <v>58.92400079999999</v>
-      </c>
       <c r="M53" t="n">
+        <v>58.92400079999998</v>
+      </c>
+      <c r="N53" t="n">
         <v>370.9999999999999</v>
       </c>
     </row>
@@ -2942,46 +3103,49 @@
       <c r="A54" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B54" t="n">
+        <v>52</v>
+      </c>
+      <c r="C54" s="2" t="n">
         <v>45500.56033564815</v>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
         <v>68797.23868549999</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>0.00031044</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>2.709e-05</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J54" t="n">
-        <v>68797.23868549999</v>
       </c>
       <c r="K54" t="n">
         <v>68797.23868549999</v>
       </c>
       <c r="L54" t="n">
+        <v>68797.23868549999</v>
+      </c>
+      <c r="M54" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>0.00031044</v>
       </c>
     </row>
@@ -2989,46 +3153,49 @@
       <c r="A55" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B55" t="n">
+        <v>53</v>
+      </c>
+      <c r="C55" s="2" t="n">
         <v>45500.56033564815</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>0.136906504984145</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>156</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>2.709e-05</v>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>0.137311665</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>0.136906504984145</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>156</v>
       </c>
     </row>
@@ -3036,46 +3203,49 @@
       <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" t="n">
+        <v>54</v>
+      </c>
+      <c r="C56" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
         <v>68786.2337</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>0.0002774880000000001</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>19.0873544169456</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>2.447e-05</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J56" t="n">
-        <v>68786.2337</v>
       </c>
       <c r="K56" t="n">
         <v>68786.2337</v>
       </c>
       <c r="L56" t="n">
-        <v>19.0873544169456</v>
+        <v>68786.2337</v>
       </c>
       <c r="M56" t="n">
+        <v>19.08735441694561</v>
+      </c>
+      <c r="N56" t="n">
         <v>0.0002774880000000001</v>
       </c>
     </row>
@@ -3083,46 +3253,49 @@
       <c r="A57" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B57" t="n">
+        <v>55</v>
+      </c>
+      <c r="C57" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>MKRUSDT</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>0.0072</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>19.0873544169456</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>2.447e-05</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>2650.85005</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>19.0873544169456</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>0.007199999999999999</v>
       </c>
     </row>
@@ -3130,46 +3303,49 @@
       <c r="A58" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" t="n">
+        <v>56</v>
+      </c>
+      <c r="C58" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
         <v>68786.2337</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>0.001452958</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>0.00012672</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J58" t="n">
-        <v>68786.2337</v>
       </c>
       <c r="K58" t="n">
         <v>68786.2337</v>
       </c>
       <c r="L58" t="n">
+        <v>68786.2337</v>
+      </c>
+      <c r="M58" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>0.001452958</v>
       </c>
     </row>
@@ -3177,46 +3353,49 @@
       <c r="A59" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="2" t="n">
+      <c r="B59" t="n">
+        <v>57</v>
+      </c>
+      <c r="C59" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>MKRUSDT</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>0.0377</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>0.00012672</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>2650.85005</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>0.0377</v>
       </c>
     </row>
@@ -3224,46 +3403,49 @@
       <c r="A60" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" t="n">
+        <v>58</v>
+      </c>
+      <c r="C60" s="2" t="n">
         <v>45488.03726851852</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>OMEUR</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
         <v>1.00660569</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>194.71378022</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>200</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>4</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>1.0889</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>1.096092935841</v>
       </c>
-      <c r="L60" t="n">
-        <v>213.4243990100391</v>
-      </c>
       <c r="M60" t="n">
+        <v>213.424399010039</v>
+      </c>
+      <c r="N60" t="n">
         <v>194.71378022</v>
       </c>
     </row>
@@ -3271,46 +3453,49 @@
       <c r="A61" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="2" t="n">
+      <c r="B61" t="n">
+        <v>59</v>
+      </c>
+      <c r="C61" s="2" t="n">
         <v>45479.77708333333</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>BNBEUR</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
         <v>485.5</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>0.1</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>48.55</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>7.499999999999999e-05</v>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>1.080199998333333</v>
       </c>
-      <c r="K61" t="n">
-        <v>524.4370991908334</v>
-      </c>
       <c r="L61" t="n">
-        <v>52.44370991908334</v>
+        <v>524.4370991908332</v>
       </c>
       <c r="M61" t="n">
+        <v>52.44370991908333</v>
+      </c>
+      <c r="N61" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3318,46 +3503,49 @@
       <c r="A62" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B62" t="n">
+        <v>60</v>
+      </c>
+      <c r="C62" s="2" t="n">
         <v>45479.76871527778</v>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
         <v>0.398</v>
       </c>
-      <c r="F62" t="n">
+      <c r="G62" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>34.0688</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>4.857e-05</v>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
         <v>0.39797001</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>0.398</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
         <v>34.0688</v>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
         <v>85.59999999999998</v>
       </c>
     </row>
@@ -3365,46 +3553,49 @@
       <c r="A63" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="2" t="n">
+      <c r="B63" t="n">
+        <v>61</v>
+      </c>
+      <c r="C63" s="2" t="n">
         <v>45479.76849537037</v>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>524.6</v>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>0.065</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>34.099</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>4.873e-05</v>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>524.5999999999999</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
         <v>524.6</v>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
         <v>34.099</v>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
         <v>0.065</v>
       </c>
     </row>
@@ -3412,46 +3603,49 @@
       <c r="A64" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="2" t="n">
+      <c r="B64" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" s="2" t="n">
         <v>45479.673125</v>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
         <v>0.02414</v>
       </c>
-      <c r="F64" t="n">
+      <c r="G64" t="n">
         <v>1976.8</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>47.719952</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>6.879e-05</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
         <v>0.02414200066666666</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
         <v>0.02414</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
         <v>47.719952</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
         <v>1976.8</v>
       </c>
     </row>
@@ -3459,46 +3653,49 @@
       <c r="A65" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="2" t="n">
+      <c r="B65" t="n">
+        <v>63</v>
+      </c>
+      <c r="C65" s="2" t="n">
         <v>45479.67239583333</v>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>PEPEUSDT</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>9.21e-06</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>5181574</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>47.72229654</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>6.889e-05</v>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
         <v>9.215000333333332e-06</v>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
         <v>9.21e-06</v>
       </c>
-      <c r="L65" t="n">
+      <c r="M65" t="n">
         <v>47.72229654</v>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
         <v>5181574</v>
       </c>
     </row>
@@ -3506,46 +3703,49 @@
       <c r="A66" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" t="n">
+        <v>64</v>
+      </c>
+      <c r="C66" s="2" t="n">
         <v>45459.61185185185</v>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>NOTUSDT</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>0.020114</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>2036</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>40.952104</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>0.0409521</v>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="K66" t="n">
         <v>0.02009346653333333</v>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
         <v>0.020114</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
         <v>40.952104</v>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
         <v>2036</v>
       </c>
     </row>
@@ -3553,46 +3753,49 @@
       <c r="A67" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="B67" s="2" t="n">
+      <c r="B67" t="n">
+        <v>65</v>
+      </c>
+      <c r="C67" s="2" t="n">
         <v>45457.95482638889</v>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>NOTUSDT</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
         <v>0.019619</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>88</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>1.726472</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>2.2e-06</v>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" t="n">
         <v>0.01962085005</v>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" t="n">
         <v>0.019619</v>
       </c>
-      <c r="L67" t="n">
+      <c r="M67" t="n">
         <v>1.726472</v>
       </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
         <v>88</v>
       </c>
     </row>
@@ -3600,46 +3803,49 @@
       <c r="A68" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B68" t="n">
+        <v>66</v>
+      </c>
+      <c r="C68" s="2" t="n">
         <v>45457.95482638889</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>NOTUSDT</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
         <v>0.019619</v>
       </c>
-      <c r="F68" t="n">
+      <c r="G68" t="n">
         <v>1950</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>38.25705</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>1.95</v>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="J68" t="n">
+      <c r="K68" t="n">
         <v>0.01962085005</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>0.019619</v>
       </c>
-      <c r="L68" t="n">
+      <c r="M68" t="n">
         <v>38.25705</v>
       </c>
-      <c r="M68" t="n">
+      <c r="N68" t="n">
         <v>1950</v>
       </c>
     </row>
@@ -3647,46 +3853,49 @@
       <c r="A69" s="1" t="n">
         <v>67</v>
       </c>
-      <c r="B69" s="2" t="n">
+      <c r="B69" t="n">
+        <v>67</v>
+      </c>
+      <c r="C69" s="2" t="n">
         <v>45457.95456018519</v>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="F69" t="n">
         <v>0.5085</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>9.5</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>4.83075</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>6.02e-06</v>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" t="n">
         <v>0.5088133366666666</v>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
         <v>0.5085</v>
       </c>
-      <c r="L69" t="n">
+      <c r="M69" t="n">
         <v>4.830749999999999</v>
       </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -3694,46 +3903,49 @@
       <c r="A70" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" t="n">
+        <v>68</v>
+      </c>
+      <c r="C70" s="2" t="n">
         <v>45457.95456018519</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="F70" t="n">
         <v>0.5086000000000001</v>
       </c>
-      <c r="F70" t="n">
+      <c r="G70" t="n">
         <v>29.8</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>15.15628</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>1.891e-05</v>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="K70" t="n">
         <v>0.5088133366666666</v>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
         <v>0.5086000000000001</v>
       </c>
-      <c r="L70" t="n">
+      <c r="M70" t="n">
         <v>15.15628</v>
       </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
         <v>29.8</v>
       </c>
     </row>
@@ -3741,46 +3953,49 @@
       <c r="A71" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="B71" s="2" t="n">
+      <c r="B71" t="n">
+        <v>69</v>
+      </c>
+      <c r="C71" s="2" t="n">
         <v>45457.95416666667</v>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>PEPEUSDT</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="F71" t="n">
         <v>1.145e-05</v>
       </c>
-      <c r="F71" t="n">
+      <c r="G71" t="n">
         <v>1746724</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>19.9999898</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>2.433e-05</v>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" t="n">
         <v>1.14600005e-05</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
         <v>1.145e-05</v>
       </c>
-      <c r="L71" t="n">
+      <c r="M71" t="n">
         <v>19.9999898</v>
       </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
         <v>1746724</v>
       </c>
     </row>
@@ -3788,46 +4003,49 @@
       <c r="A72" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="B72" s="2" t="n">
+      <c r="B72" t="n">
+        <v>70</v>
+      </c>
+      <c r="C72" s="2" t="n">
         <v>45455.6309837963</v>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
         <v>0.037824</v>
       </c>
-      <c r="F72" t="n">
+      <c r="G72" t="n">
         <v>3465.2</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>131.0677248</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>3.4652</v>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>JASMY</t>
         </is>
       </c>
-      <c r="J72" t="n">
+      <c r="K72" t="n">
         <v>0.03777478451666667</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>0.037824</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" t="n">
         <v>131.0677248</v>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
         <v>3465.2</v>
       </c>
     </row>
@@ -3835,46 +4053,49 @@
       <c r="A73" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" t="n">
+        <v>71</v>
+      </c>
+      <c r="C73" s="2" t="n">
         <v>45455.630625</v>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="F73" t="n">
         <v>69787.49000000001</v>
       </c>
-      <c r="F73" t="n">
+      <c r="G73" t="n">
         <v>0.00188</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>131.2004812</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>0.13120048</v>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
         <v>69787.75104183334</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
         <v>69787.49000000001</v>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" t="n">
         <v>131.2004812</v>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
         <v>0.00188</v>
       </c>
     </row>
@@ -3882,46 +4103,49 @@
       <c r="A74" s="1" t="n">
         <v>72</v>
       </c>
-      <c r="B74" s="2" t="n">
+      <c r="B74" t="n">
+        <v>72</v>
+      </c>
+      <c r="C74" s="2" t="n">
         <v>45455.03658564815</v>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
         <v>67225.22887250001</v>
       </c>
-      <c r="F74" t="n">
+      <c r="G74" t="n">
         <v>0.0001384</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>1.176e-05</v>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J74" t="n">
-        <v>67225.22887250001</v>
       </c>
       <c r="K74" t="n">
         <v>67225.22887250001</v>
       </c>
       <c r="L74" t="n">
+        <v>67225.22887250001</v>
+      </c>
+      <c r="M74" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="M74" t="n">
+      <c r="N74" t="n">
         <v>0.0001384</v>
       </c>
     </row>
@@ -3929,46 +4153,49 @@
       <c r="A75" s="1" t="n">
         <v>73</v>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B75" t="n">
+        <v>73</v>
+      </c>
+      <c r="C75" s="2" t="n">
         <v>45455.03658564815</v>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>0.116299645949425</v>
       </c>
-      <c r="F75" t="n">
+      <c r="G75" t="n">
         <v>80</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>1.176e-05</v>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
         <v>0.11652</v>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
         <v>0.116299645949425</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="M75" t="n">
+      <c r="N75" t="n">
         <v>80</v>
       </c>
     </row>
@@ -3976,46 +4203,49 @@
       <c r="A76" s="1" t="n">
         <v>74</v>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B76" t="n">
+        <v>74</v>
+      </c>
+      <c r="C76" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G76" t="n">
         <v>0.001252093</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>1.25e-06</v>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J76" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K76" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L76" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M76" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="M76" t="n">
+      <c r="N76" t="n">
         <v>0.001252093</v>
       </c>
     </row>
@@ -4023,46 +4253,49 @@
       <c r="A77" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="B77" s="2" t="n">
+      <c r="B77" t="n">
+        <v>75</v>
+      </c>
+      <c r="C77" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>0.127</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>1.25e-06</v>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="M77" t="n">
+      <c r="N77" t="n">
         <v>0.127</v>
       </c>
     </row>
@@ -4070,46 +4303,49 @@
       <c r="A78" s="1" t="n">
         <v>76</v>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B78" t="n">
+        <v>76</v>
+      </c>
+      <c r="C78" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F78" t="n">
+      <c r="G78" t="n">
         <v>0.0029577</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>2.96e-06</v>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J78" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K78" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L78" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M78" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="M78" t="n">
+      <c r="N78" t="n">
         <v>0.0029577</v>
       </c>
     </row>
@@ -4117,46 +4353,49 @@
       <c r="A79" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="B79" s="2" t="n">
+      <c r="B79" t="n">
+        <v>77</v>
+      </c>
+      <c r="C79" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>0.3</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>2.96e-06</v>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="K79" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="M79" t="n">
+      <c r="N79" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -4164,46 +4403,49 @@
       <c r="A80" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="B80" s="2" t="n">
+      <c r="B80" t="n">
+        <v>78</v>
+      </c>
+      <c r="C80" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F80" t="n">
+      <c r="G80" t="n">
         <v>0.002464749999999999</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>2.46e-06</v>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J80" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K80" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L80" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M80" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="M80" t="n">
+      <c r="N80" t="n">
         <v>0.002464749999999999</v>
       </c>
     </row>
@@ -4211,46 +4453,49 @@
       <c r="A81" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="B81" s="2" t="n">
+      <c r="B81" t="n">
+        <v>79</v>
+      </c>
+      <c r="C81" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="F81" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F81" t="n">
+      <c r="G81" t="n">
         <v>0.25</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>2.46e-06</v>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="M81" t="n">
+      <c r="N81" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -4258,46 +4503,49 @@
       <c r="A82" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="B82" s="2" t="n">
+      <c r="B82" t="n">
+        <v>80</v>
+      </c>
+      <c r="C82" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F82" t="n">
+      <c r="G82" t="n">
         <v>0.004929499999999999</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>0.000375</v>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J82" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K82" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L82" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M82" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="M82" t="n">
+      <c r="N82" t="n">
         <v>0.004929499999999999</v>
       </c>
     </row>
@@ -4305,46 +4553,49 @@
       <c r="A83" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="B83" s="2" t="n">
+      <c r="B83" t="n">
+        <v>81</v>
+      </c>
+      <c r="C83" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E83" t="n">
+      <c r="F83" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F83" t="n">
+      <c r="G83" t="n">
         <v>0.5</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>0.000375</v>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L83" t="n">
+      <c r="M83" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="M83" t="n">
+      <c r="N83" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4352,46 +4603,49 @@
       <c r="A84" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B84" t="n">
+        <v>82</v>
+      </c>
+      <c r="C84" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F84" t="n">
+      <c r="G84" t="n">
         <v>0.000808438</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>6.161e-05</v>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J84" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K84" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L84" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M84" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="M84" t="n">
+      <c r="N84" t="n">
         <v>0.000808438</v>
       </c>
     </row>
@@ -4399,46 +4653,49 @@
       <c r="A85" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="B85" s="2" t="n">
+      <c r="B85" t="n">
+        <v>83</v>
+      </c>
+      <c r="C85" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E85" t="n">
+      <c r="F85" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F85" t="n">
+      <c r="G85" t="n">
         <v>0.082</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>6.161e-05</v>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J85" t="n">
+      <c r="K85" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K85" t="n">
+      <c r="L85" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L85" t="n">
+      <c r="M85" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="M85" t="n">
+      <c r="N85" t="n">
         <v>0.082</v>
       </c>
     </row>
@@ -4446,46 +4703,49 @@
       <c r="A86" s="1" t="n">
         <v>84</v>
       </c>
-      <c r="B86" s="2" t="n">
+      <c r="B86" t="n">
+        <v>84</v>
+      </c>
+      <c r="C86" s="2" t="n">
         <v>45451.5195949074</v>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
         <v>683.8948187155901</v>
       </c>
-      <c r="F86" t="n">
+      <c r="G86" t="n">
         <v>1.121</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>766.6460917801764</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>0.00084075</v>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J86" t="n">
+      <c r="K86" t="n">
         <v>683.7183116666666</v>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" t="n">
         <v>683.8948187155901</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
         <v>766.6460917801764</v>
       </c>
-      <c r="M86" t="n">
+      <c r="N86" t="n">
         <v>1.121</v>
       </c>
     </row>
@@ -4493,46 +4753,49 @@
       <c r="A87" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="B87" s="2" t="n">
+      <c r="B87" t="n">
+        <v>85</v>
+      </c>
+      <c r="C87" s="2" t="n">
         <v>45451.5195949074</v>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E87" t="n">
+      <c r="F87" t="n">
         <v>69360.5292815</v>
       </c>
-      <c r="F87" t="n">
+      <c r="G87" t="n">
         <v>0.01105306</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>766.6460917801764</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>0.00084075</v>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J87" t="n">
-        <v>69360.5292815</v>
       </c>
       <c r="K87" t="n">
         <v>69360.5292815</v>
       </c>
       <c r="L87" t="n">
-        <v>766.6460917801764</v>
+        <v>69360.5292815</v>
       </c>
       <c r="M87" t="n">
+        <v>766.6460917801763</v>
+      </c>
+      <c r="N87" t="n">
         <v>0.01105306</v>
       </c>
     </row>
@@ -4540,46 +4803,49 @@
       <c r="A88" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="B88" s="2" t="n">
+      <c r="B88" t="n">
+        <v>86</v>
+      </c>
+      <c r="C88" s="2" t="n">
         <v>45451.50400462963</v>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E88" t="n">
+      <c r="F88" t="n">
         <v>681.2</v>
       </c>
-      <c r="F88" t="n">
+      <c r="G88" t="n">
         <v>0.015</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>10.218</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
         <v>1.124e-05</v>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="K88" t="n">
         <v>681.9633216666666</v>
       </c>
-      <c r="K88" t="n">
+      <c r="L88" t="n">
         <v>681.2</v>
       </c>
-      <c r="L88" t="n">
+      <c r="M88" t="n">
         <v>10.218</v>
       </c>
-      <c r="M88" t="n">
+      <c r="N88" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -4587,46 +4853,49 @@
       <c r="A89" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="B89" s="2" t="n">
+      <c r="B89" t="n">
+        <v>87</v>
+      </c>
+      <c r="C89" s="2" t="n">
         <v>45450.92207175926</v>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
         <v>0.041304</v>
       </c>
-      <c r="F89" t="n">
+      <c r="G89" t="n">
         <v>1210.5</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>49.998492</v>
       </c>
-      <c r="H89" t="n">
+      <c r="I89" t="n">
         <v>1.2105</v>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>JASMY</t>
         </is>
       </c>
-      <c r="J89" t="n">
+      <c r="K89" t="n">
         <v>0.04132561585</v>
       </c>
-      <c r="K89" t="n">
+      <c r="L89" t="n">
         <v>0.041304</v>
       </c>
-      <c r="L89" t="n">
+      <c r="M89" t="n">
         <v>49.998492</v>
       </c>
-      <c r="M89" t="n">
+      <c r="N89" t="n">
         <v>1210.5</v>
       </c>
     </row>
@@ -4634,46 +4903,49 @@
       <c r="A90" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="B90" s="2" t="n">
+      <c r="B90" t="n">
+        <v>88</v>
+      </c>
+      <c r="C90" s="2" t="n">
         <v>45450.92207175926</v>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
         <v>0.041305</v>
       </c>
-      <c r="F90" t="n">
+      <c r="G90" t="n">
         <v>1082.2</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>44.700271</v>
       </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
         <v>1.0822</v>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>JASMY</t>
         </is>
       </c>
-      <c r="J90" t="n">
+      <c r="K90" t="n">
         <v>0.04132561585</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
         <v>0.041305</v>
       </c>
-      <c r="L90" t="n">
+      <c r="M90" t="n">
         <v>44.700271</v>
       </c>
-      <c r="M90" t="n">
+      <c r="N90" t="n">
         <v>1082.2</v>
       </c>
     </row>
@@ -4681,46 +4953,49 @@
       <c r="A91" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="B91" s="2" t="n">
+      <c r="B91" t="n">
+        <v>89</v>
+      </c>
+      <c r="C91" s="2" t="n">
         <v>45450.92138888889</v>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>ENSUSDT</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E91" t="n">
+      <c r="F91" t="n">
         <v>21.97</v>
       </c>
-      <c r="F91" t="n">
+      <c r="G91" t="n">
         <v>2.01</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>44.1597</v>
       </c>
-      <c r="H91" t="n">
+      <c r="I91" t="n">
         <v>0.0441597</v>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J91" t="n">
+      <c r="K91" t="n">
         <v>21.95600116666667</v>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" t="n">
         <v>21.97</v>
       </c>
-      <c r="L91" t="n">
+      <c r="M91" t="n">
         <v>44.15969999999999</v>
       </c>
-      <c r="M91" t="n">
+      <c r="N91" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -4728,46 +5003,49 @@
       <c r="A92" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="B92" s="2" t="n">
+      <c r="B92" t="n">
+        <v>90</v>
+      </c>
+      <c r="C92" s="2" t="n">
         <v>45450.92039351852</v>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>ARUSDT</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E92" t="n">
+      <c r="F92" t="n">
         <v>39.245</v>
       </c>
-      <c r="F92" t="n">
+      <c r="G92" t="n">
         <v>1.3</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>51.0185</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>0.0510185</v>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J92" t="n">
+      <c r="K92" t="n">
         <v>39.20989994999999</v>
       </c>
-      <c r="K92" t="n">
+      <c r="L92" t="n">
         <v>39.245</v>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" t="n">
         <v>51.0185</v>
       </c>
-      <c r="M92" t="n">
+      <c r="N92" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -4775,46 +5053,49 @@
       <c r="A93" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="B93" s="2" t="n">
+      <c r="B93" t="n">
+        <v>91</v>
+      </c>
+      <c r="C93" s="2" t="n">
         <v>45447.9729050926</v>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
         <v>70502.70711650001</v>
       </c>
-      <c r="F93" t="n">
+      <c r="G93" t="n">
         <v>5.1689e-05</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="H93" t="n">
+      <c r="I93" t="n">
         <v>5e-08</v>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J93" t="n">
-        <v>70502.70711650001</v>
       </c>
       <c r="K93" t="n">
         <v>70502.70711650001</v>
       </c>
       <c r="L93" t="n">
+        <v>70502.70711650001</v>
+      </c>
+      <c r="M93" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="M93" t="n">
+      <c r="N93" t="n">
         <v>5.1689e-05</v>
       </c>
     </row>
@@ -4822,46 +5103,49 @@
       <c r="A94" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="B94" s="2" t="n">
+      <c r="B94" t="n">
+        <v>92</v>
+      </c>
+      <c r="C94" s="2" t="n">
         <v>45447.9729050926</v>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>UMAUSDT</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E94" t="n">
+      <c r="F94" t="n">
         <v>3.312922207404335</v>
       </c>
-      <c r="F94" t="n">
+      <c r="G94" t="n">
         <v>1.1</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="H94" t="n">
+      <c r="I94" t="n">
         <v>5e-08</v>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J94" t="n">
+      <c r="K94" t="n">
         <v>3.312983350000001</v>
       </c>
-      <c r="K94" t="n">
+      <c r="L94" t="n">
         <v>3.312922207404335</v>
       </c>
-      <c r="L94" t="n">
+      <c r="M94" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="M94" t="n">
+      <c r="N94" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -4869,46 +5153,49 @@
       <c r="A95" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="B95" s="2" t="n">
+      <c r="B95" t="n">
+        <v>93</v>
+      </c>
+      <c r="C95" s="2" t="n">
         <v>45447.94982638889</v>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
         <v>70534.99716683332</v>
       </c>
-      <c r="F95" t="n">
+      <c r="G95" t="n">
         <v>0.0002490470000000001</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>17.56652943940834</v>
       </c>
-      <c r="H95" t="n">
+      <c r="I95" t="n">
         <v>2.5e-07</v>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J95" t="n">
-        <v>70534.99716683332</v>
       </c>
       <c r="K95" t="n">
         <v>70534.99716683332</v>
       </c>
       <c r="L95" t="n">
-        <v>17.56652943940834</v>
+        <v>70534.99716683332</v>
       </c>
       <c r="M95" t="n">
+        <v>17.56652943940835</v>
+      </c>
+      <c r="N95" t="n">
         <v>0.0002490470000000001</v>
       </c>
     </row>
@@ -4916,46 +5203,49 @@
       <c r="A96" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="B96" s="2" t="n">
+      <c r="B96" t="n">
+        <v>94</v>
+      </c>
+      <c r="C96" s="2" t="n">
         <v>45447.94982638889</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>UMAUSDT</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E96" t="n">
+      <c r="F96" t="n">
         <v>3.314439516869498</v>
       </c>
-      <c r="F96" t="n">
+      <c r="G96" t="n">
         <v>5.3</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>17.56652943940834</v>
       </c>
-      <c r="H96" t="n">
+      <c r="I96" t="n">
         <v>2.5e-07</v>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J96" t="n">
+      <c r="K96" t="n">
         <v>3.311750016666666</v>
       </c>
-      <c r="K96" t="n">
+      <c r="L96" t="n">
         <v>3.314439516869498</v>
       </c>
-      <c r="L96" t="n">
+      <c r="M96" t="n">
         <v>17.56652943940834</v>
       </c>
-      <c r="M96" t="n">
+      <c r="N96" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -4963,46 +5253,49 @@
       <c r="A97" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="B97" s="2" t="n">
+      <c r="B97" t="n">
+        <v>95</v>
+      </c>
+      <c r="C97" s="2" t="n">
         <v>45446.50150462963</v>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>ETHUSDT</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
         <v>3810.458332166667</v>
       </c>
-      <c r="F97" t="n">
+      <c r="G97" t="n">
         <v>0.01363</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="H97" t="n">
+      <c r="I97" t="n">
         <v>1.363e-05</v>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
-      </c>
-      <c r="J97" t="n">
-        <v>3810.458332166667</v>
       </c>
       <c r="K97" t="n">
         <v>3810.458332166667</v>
       </c>
       <c r="L97" t="n">
+        <v>3810.458332166667</v>
+      </c>
+      <c r="M97" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="M97" t="n">
+      <c r="N97" t="n">
         <v>0.01363</v>
       </c>
     </row>
@@ -5010,46 +5303,49 @@
       <c r="A98" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="B98" s="2" t="n">
+      <c r="B98" t="n">
+        <v>96</v>
+      </c>
+      <c r="C98" s="2" t="n">
         <v>45446.50150462963</v>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>XRPUSDT</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E98" t="n">
+      <c r="F98" t="n">
         <v>0.5193654706743167</v>
       </c>
-      <c r="F98" t="n">
+      <c r="G98" t="n">
         <v>100</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="H98" t="n">
+      <c r="I98" t="n">
         <v>1.363e-05</v>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="J98" t="n">
+      <c r="K98" t="n">
         <v>0.5193833316666667</v>
       </c>
-      <c r="K98" t="n">
+      <c r="L98" t="n">
         <v>0.5193654706743167</v>
       </c>
-      <c r="L98" t="n">
+      <c r="M98" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="M98" t="n">
+      <c r="N98" t="n">
         <v>100</v>
       </c>
     </row>
@@ -5057,46 +5353,49 @@
       <c r="A99" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="B99" s="2" t="n">
+      <c r="B99" t="n">
+        <v>97</v>
+      </c>
+      <c r="C99" s="2" t="n">
         <v>45446.49649305556</v>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
         <v>69129.98950016667</v>
       </c>
-      <c r="F99" t="n">
+      <c r="G99" t="n">
         <v>0.00069092</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="H99" t="n">
+      <c r="I99" t="n">
         <v>6.9e-07</v>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J99" t="n">
-        <v>69129.98950016667</v>
       </c>
       <c r="K99" t="n">
         <v>69129.98950016667</v>
       </c>
       <c r="L99" t="n">
+        <v>69129.98950016667</v>
+      </c>
+      <c r="M99" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="M99" t="n">
+      <c r="N99" t="n">
         <v>0.00069092</v>
       </c>
     </row>
@@ -5104,46 +5403,49 @@
       <c r="A100" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="B100" s="2" t="n">
+      <c r="B100" t="n">
+        <v>98</v>
+      </c>
+      <c r="C100" s="2" t="n">
         <v>45446.49649305556</v>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>XRPUSDT</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E100" t="n">
+      <c r="F100" t="n">
         <v>0.5191662211462518</v>
       </c>
-      <c r="F100" t="n">
+      <c r="G100" t="n">
         <v>92</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="H100" t="n">
+      <c r="I100" t="n">
         <v>6.9e-07</v>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J100" t="n">
+      <c r="K100" t="n">
         <v>0.5193049983333333</v>
       </c>
-      <c r="K100" t="n">
+      <c r="L100" t="n">
         <v>0.5191662211462518</v>
       </c>
-      <c r="L100" t="n">
+      <c r="M100" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="M100" t="n">
+      <c r="N100" t="n">
         <v>92</v>
       </c>
     </row>
@@ -5151,46 +5453,49 @@
       <c r="A101" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="B101" s="2" t="n">
+      <c r="B101" t="n">
+        <v>99</v>
+      </c>
+      <c r="C101" s="2" t="n">
         <v>45446.42081018518</v>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
         <v>69115.08947183334</v>
       </c>
-      <c r="F101" t="n">
+      <c r="G101" t="n">
         <v>0.0006642089999999999</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="H101" t="n">
+      <c r="I101" t="n">
         <v>6.6e-07</v>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J101" t="n">
-        <v>69115.08947183334</v>
       </c>
       <c r="K101" t="n">
         <v>69115.08947183334</v>
       </c>
       <c r="L101" t="n">
+        <v>69115.08947183334</v>
+      </c>
+      <c r="M101" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="M101" t="n">
+      <c r="N101" t="n">
         <v>0.0006642089999999999</v>
       </c>
     </row>
@@ -5198,46 +5503,49 @@
       <c r="A102" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B102" s="2" t="n">
+      <c r="B102" t="n">
+        <v>100</v>
+      </c>
+      <c r="C102" s="2" t="n">
         <v>45446.42081018518</v>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>NEARUSDT</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E102" t="n">
+      <c r="F102" t="n">
         <v>7.28680388301539</v>
       </c>
-      <c r="F102" t="n">
+      <c r="G102" t="n">
         <v>6.3</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="H102" t="n">
+      <c r="I102" t="n">
         <v>6.6e-07</v>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J102" t="n">
+      <c r="K102" t="n">
         <v>7.287033316666666</v>
       </c>
-      <c r="K102" t="n">
+      <c r="L102" t="n">
         <v>7.28680388301539</v>
       </c>
-      <c r="L102" t="n">
+      <c r="M102" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="M102" t="n">
+      <c r="N102" t="n">
         <v>6.299999999999999</v>
       </c>
     </row>
@@ -5245,46 +5553,49 @@
       <c r="A103" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="B103" s="2" t="n">
+      <c r="B103" t="n">
+        <v>101</v>
+      </c>
+      <c r="C103" s="2" t="n">
         <v>45442.00921296296</v>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
         <v>67749.86920016666</v>
       </c>
-      <c r="F103" t="n">
+      <c r="G103" t="n">
         <v>0.00093258</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="H103" t="n">
+      <c r="I103" t="n">
         <v>9.3e-07</v>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J103" t="n">
-        <v>67749.86920016666</v>
       </c>
       <c r="K103" t="n">
         <v>67749.86920016666</v>
       </c>
       <c r="L103" t="n">
+        <v>67749.86920016666</v>
+      </c>
+      <c r="M103" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="M103" t="n">
+      <c r="N103" t="n">
         <v>0.00093258</v>
       </c>
     </row>
@@ -5292,46 +5603,49 @@
       <c r="A104" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="B104" s="2" t="n">
+      <c r="B104" t="n">
+        <v>102</v>
+      </c>
+      <c r="C104" s="2" t="n">
         <v>45442.00921296296</v>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>LPTUSDT</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E104" t="n">
+      <c r="F104" t="n">
         <v>21.27345892885233</v>
       </c>
-      <c r="F104" t="n">
+      <c r="G104" t="n">
         <v>2.97</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="H104" t="n">
+      <c r="I104" t="n">
         <v>9.3e-07</v>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J104" t="n">
+      <c r="K104" t="n">
         <v>21.26066758333333</v>
       </c>
-      <c r="K104" t="n">
+      <c r="L104" t="n">
         <v>21.27345892885233</v>
       </c>
-      <c r="L104" t="n">
+      <c r="M104" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="M104" t="n">
+      <c r="N104" t="n">
         <v>2.97</v>
       </c>
     </row>
@@ -5339,46 +5653,49 @@
       <c r="A105" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="B105" s="2" t="n">
+      <c r="B105" t="n">
+        <v>103</v>
+      </c>
+      <c r="C105" s="2" t="n">
         <v>45441.90847222223</v>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
         <v>67695.03782550001</v>
       </c>
-      <c r="F105" t="n">
+      <c r="G105" t="n">
         <v>0.0007335899999999999</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="H105" t="n">
+      <c r="I105" t="n">
         <v>7.3e-07</v>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J105" t="n">
-        <v>67695.03782550001</v>
       </c>
       <c r="K105" t="n">
         <v>67695.03782550001</v>
       </c>
       <c r="L105" t="n">
+        <v>67695.03782550001</v>
+      </c>
+      <c r="M105" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="M105" t="n">
+      <c r="N105" t="n">
         <v>0.0007335899999999999</v>
       </c>
     </row>
@@ -5386,46 +5703,49 @@
       <c r="A106" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B106" s="2" t="n">
+      <c r="B106" t="n">
+        <v>104</v>
+      </c>
+      <c r="C106" s="2" t="n">
         <v>45441.90847222223</v>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>NEARUSDT</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E106" t="n">
+      <c r="F106" t="n">
         <v>7.640061968985931</v>
       </c>
-      <c r="F106" t="n">
+      <c r="G106" t="n">
         <v>6.5</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="H106" t="n">
+      <c r="I106" t="n">
         <v>7.3e-07</v>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J106" t="n">
+      <c r="K106" t="n">
         <v>7.64060005</v>
       </c>
-      <c r="K106" t="n">
+      <c r="L106" t="n">
         <v>7.640061968985931</v>
       </c>
-      <c r="L106" t="n">
+      <c r="M106" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="M106" t="n">
+      <c r="N106" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -5433,46 +5753,49 @@
       <c r="A107" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="B107" s="2" t="n">
+      <c r="B107" t="n">
+        <v>105</v>
+      </c>
+      <c r="C107" s="2" t="n">
         <v>45440.88619212963</v>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
         <v>64131.08918148</v>
       </c>
-      <c r="F107" t="n">
+      <c r="G107" t="n">
         <v>0.00076406</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>50</v>
       </c>
-      <c r="H107" t="n">
+      <c r="I107" t="n">
         <v>1</v>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J107" t="n">
+      <c r="K107" t="n">
         <v>1.086388331666667</v>
       </c>
-      <c r="K107" t="n">
-        <v>69671.26698383427</v>
-      </c>
       <c r="L107" t="n">
+        <v>69671.26698383428</v>
+      </c>
+      <c r="M107" t="n">
         <v>53.23302825166842</v>
       </c>
-      <c r="M107" t="n">
+      <c r="N107" t="n">
         <v>0.00076406</v>
       </c>
     </row>
@@ -5480,46 +5803,49 @@
       <c r="A108" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="B108" s="2" t="n">
+      <c r="B108" t="n">
+        <v>106</v>
+      </c>
+      <c r="C108" s="2" t="n">
         <v>45439.96682870371</v>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
         <v>69531.81351050001</v>
       </c>
-      <c r="F108" t="n">
+      <c r="G108" t="n">
         <v>0.0004004640000000001</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="H108" t="n">
+      <c r="I108" t="n">
         <v>4e-07</v>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J108" t="n">
-        <v>69531.81351050001</v>
       </c>
       <c r="K108" t="n">
         <v>69531.81351050001</v>
       </c>
       <c r="L108" t="n">
+        <v>69531.81351050001</v>
+      </c>
+      <c r="M108" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="M108" t="n">
+      <c r="N108" t="n">
         <v>0.0004004640000000001</v>
       </c>
     </row>
@@ -5527,46 +5853,49 @@
       <c r="A109" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="B109" s="2" t="n">
+      <c r="B109" t="n">
+        <v>107</v>
+      </c>
+      <c r="C109" s="2" t="n">
         <v>45439.96682870371</v>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>INJUSDT</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E109" t="n">
+      <c r="F109" t="n">
         <v>25.7823964496934</v>
       </c>
-      <c r="F109" t="n">
+      <c r="G109" t="n">
         <v>1.08</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="H109" t="n">
+      <c r="I109" t="n">
         <v>4e-07</v>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J109" t="n">
+      <c r="K109" t="n">
         <v>25.7770005</v>
       </c>
-      <c r="K109" t="n">
+      <c r="L109" t="n">
         <v>25.7823964496934</v>
       </c>
-      <c r="L109" t="n">
+      <c r="M109" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="M109" t="n">
+      <c r="N109" t="n">
         <v>1.08</v>
       </c>
     </row>
@@ -5574,46 +5903,49 @@
       <c r="A110" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="B110" s="2" t="n">
+      <c r="B110" t="n">
+        <v>108</v>
+      </c>
+      <c r="C110" s="2" t="n">
         <v>45439.96547453704</v>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
         <v>69520.8794125</v>
       </c>
-      <c r="F110" t="n">
+      <c r="G110" t="n">
         <v>0.000231</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="H110" t="n">
+      <c r="I110" t="n">
         <v>2.3e-07</v>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J110" t="n">
-        <v>69520.8794125</v>
       </c>
       <c r="K110" t="n">
         <v>69520.8794125</v>
       </c>
       <c r="L110" t="n">
+        <v>69520.8794125</v>
+      </c>
+      <c r="M110" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="M110" t="n">
+      <c r="N110" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -5621,46 +5953,49 @@
       <c r="A111" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B111" s="2" t="n">
+      <c r="B111" t="n">
+        <v>109</v>
+      </c>
+      <c r="C111" s="2" t="n">
         <v>45439.96547453704</v>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>FETUSDT</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E111" t="n">
+      <c r="F111" t="n">
         <v>2.2941890206125</v>
       </c>
-      <c r="F111" t="n">
+      <c r="G111" t="n">
         <v>7</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="H111" t="n">
+      <c r="I111" t="n">
         <v>2.3e-07</v>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J111" t="n">
+      <c r="K111" t="n">
         <v>2.2945667</v>
       </c>
-      <c r="K111" t="n">
+      <c r="L111" t="n">
         <v>2.2941890206125</v>
       </c>
-      <c r="L111" t="n">
+      <c r="M111" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="M111" t="n">
+      <c r="N111" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5668,46 +6003,49 @@
       <c r="A112" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="B112" s="2" t="n">
+      <c r="B112" t="n">
+        <v>110</v>
+      </c>
+      <c r="C112" s="2" t="n">
         <v>45438.41358796296</v>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
         <v>64764.05726993</v>
       </c>
-      <c r="F112" t="n">
+      <c r="G112" t="n">
         <v>0.00302637</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>200</v>
       </c>
-      <c r="H112" t="n">
+      <c r="I112" t="n">
         <v>4</v>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J112" t="n">
+      <c r="K112" t="n">
         <v>1.084943331666667</v>
       </c>
-      <c r="K112" t="n">
-        <v>70265.33206668866</v>
-      </c>
       <c r="L112" t="n">
-        <v>212.6488930066646</v>
+        <v>70265.33206668869</v>
       </c>
       <c r="M112" t="n">
+        <v>212.6488930066647</v>
+      </c>
+      <c r="N112" t="n">
         <v>0.00302637</v>
       </c>
     </row>
@@ -5715,46 +6053,49 @@
       <c r="A113" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="B113" s="2" t="n">
+      <c r="B113" t="n">
+        <v>111</v>
+      </c>
+      <c r="C113" s="2" t="n">
         <v>45438.06670138889</v>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>ENSEUR</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
         <v>21.88048003</v>
       </c>
-      <c r="F113" t="n">
+      <c r="G113" t="n">
         <v>3.35870145</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>75</v>
       </c>
-      <c r="H113" t="n">
+      <c r="I113" t="n">
         <v>1</v>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J113" t="n">
+      <c r="K113" t="n">
         <v>1.084505001666667</v>
       </c>
-      <c r="K113" t="n">
-        <v>23.72949003140262</v>
-      </c>
       <c r="L113" t="n">
-        <v>79.70027257623251</v>
+        <v>23.72949003140263</v>
       </c>
       <c r="M113" t="n">
+        <v>79.70027257623255</v>
+      </c>
+      <c r="N113" t="n">
         <v>3.35870145</v>
       </c>
     </row>
@@ -5762,46 +6103,49 @@
       <c r="A114" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="B114" s="2" t="n">
+      <c r="B114" t="n">
+        <v>112</v>
+      </c>
+      <c r="C114" s="2" t="n">
         <v>45438.06428240741</v>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>LPTEUR</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
         <v>21.40068094</v>
       </c>
-      <c r="F114" t="n">
+      <c r="G114" t="n">
         <v>4.57929354</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>100</v>
       </c>
-      <c r="H114" t="n">
+      <c r="I114" t="n">
         <v>2</v>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J114" t="n">
+      <c r="K114" t="n">
         <v>1.084456668333333</v>
       </c>
-      <c r="K114" t="n">
-        <v>23.20811115225707</v>
-      </c>
       <c r="L114" t="n">
-        <v>106.2767534751328</v>
+        <v>23.20811115225706</v>
       </c>
       <c r="M114" t="n">
+        <v>106.2767534751327</v>
+      </c>
+      <c r="N114" t="n">
         <v>4.57929354</v>
       </c>
     </row>
@@ -5809,46 +6153,49 @@
       <c r="A115" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="B115" s="2" t="n">
+      <c r="B115" t="n">
+        <v>113</v>
+      </c>
+      <c r="C115" s="2" t="n">
         <v>45438.06288194445</v>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>JASMYEUR</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
         <v>0.02039718</v>
       </c>
-      <c r="F115" t="n">
+      <c r="G115" t="n">
         <v>4804.58606935</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>100</v>
       </c>
-      <c r="H115" t="n">
+      <c r="I115" t="n">
         <v>2</v>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J115" t="n">
+      <c r="K115" t="n">
         <v>1.084644998333333</v>
       </c>
-      <c r="K115" t="n">
+      <c r="L115" t="n">
         <v>0.0221236992671047</v>
       </c>
-      <c r="L115" t="n">
+      <c r="M115" t="n">
         <v>106.29521730122</v>
       </c>
-      <c r="M115" t="n">
+      <c r="N115" t="n">
         <v>4804.58606935</v>
       </c>
     </row>
@@ -5856,46 +6203,49 @@
       <c r="A116" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="B116" s="2" t="n">
+      <c r="B116" t="n">
+        <v>114</v>
+      </c>
+      <c r="C116" s="2" t="n">
         <v>45438.01670138889</v>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>BBEUR</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
         <v>0.5091575699999999</v>
       </c>
-      <c r="F116" t="n">
+      <c r="G116" t="n">
         <v>288.7121952</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>150</v>
       </c>
-      <c r="H116" t="n">
+      <c r="I116" t="n">
         <v>3</v>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J116" t="n">
+      <c r="K116" t="n">
         <v>1.084505001666667</v>
       </c>
-      <c r="K116" t="n">
-        <v>0.5521839313014458</v>
-      </c>
       <c r="L116" t="n">
-        <v>159.4222349602064</v>
+        <v>0.5521839313014461</v>
       </c>
       <c r="M116" t="n">
+        <v>159.4222349602065</v>
+      </c>
+      <c r="N116" t="n">
         <v>288.7121952</v>
       </c>
     </row>
@@ -5903,46 +6253,49 @@
       <c r="A117" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="B117" s="2" t="n">
+      <c r="B117" t="n">
+        <v>115</v>
+      </c>
+      <c r="C117" s="2" t="n">
         <v>45438.01179398148</v>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>XRPEUR</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
         <v>0.50817649</v>
       </c>
-      <c r="F117" t="n">
+      <c r="G117" t="n">
         <v>192.84638819</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>100</v>
       </c>
-      <c r="H117" t="n">
+      <c r="I117" t="n">
         <v>2</v>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J117" t="n">
+      <c r="K117" t="n">
         <v>1.0845</v>
       </c>
-      <c r="K117" t="n">
+      <c r="L117" t="n">
         <v>0.551117403405</v>
       </c>
-      <c r="L117" t="n">
+      <c r="M117" t="n">
         <v>106.2810007153055</v>
       </c>
-      <c r="M117" t="n">
+      <c r="N117" t="n">
         <v>192.84638819</v>
       </c>
     </row>
@@ -5950,46 +6303,49 @@
       <c r="A118" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="B118" s="2" t="n">
+      <c r="B118" t="n">
+        <v>116</v>
+      </c>
+      <c r="C118" s="2" t="n">
         <v>45437.93450231481</v>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>PEPEEUR</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
         <v>1.414e-05</v>
       </c>
-      <c r="F118" t="n">
+      <c r="G118" t="n">
         <v>6928298.24</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>100</v>
       </c>
-      <c r="H118" t="n">
+      <c r="I118" t="n">
         <v>2</v>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J118" t="n">
+      <c r="K118" t="n">
         <v>1.0845</v>
       </c>
-      <c r="K118" t="n">
+      <c r="L118" t="n">
         <v>1.533483e-05</v>
       </c>
-      <c r="L118" t="n">
+      <c r="M118" t="n">
         <v>106.2442756996992</v>
       </c>
-      <c r="M118" t="n">
+      <c r="N118" t="n">
         <v>6928298.24</v>
       </c>
     </row>
@@ -5997,46 +6353,49 @@
       <c r="A119" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="B119" s="2" t="n">
+      <c r="B119" t="n">
+        <v>117</v>
+      </c>
+      <c r="C119" s="2" t="n">
         <v>45437.92731481481</v>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>NEAREUR</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
         <v>7.62742061</v>
       </c>
-      <c r="F119" t="n">
+      <c r="G119" t="n">
         <v>12.8483802</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>100</v>
       </c>
-      <c r="H119" t="n">
+      <c r="I119" t="n">
         <v>2</v>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J119" t="n">
+      <c r="K119" t="n">
         <v>1.0846</v>
       </c>
-      <c r="K119" t="n">
+      <c r="L119" t="n">
         <v>8.272700393606</v>
       </c>
-      <c r="L119" t="n">
+      <c r="M119" t="n">
         <v>106.2907999377395</v>
       </c>
-      <c r="M119" t="n">
+      <c r="N119" t="n">
         <v>12.8483802</v>
       </c>
     </row>
@@ -6044,46 +6403,49 @@
       <c r="A120" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="B120" s="2" t="n">
+      <c r="B120" t="n">
+        <v>118</v>
+      </c>
+      <c r="C120" s="2" t="n">
         <v>45436.94775462963</v>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>MKREUR</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
         <v>2571.01241222</v>
       </c>
-      <c r="F120" t="n">
+      <c r="G120" t="n">
         <v>0.03811728</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>100</v>
       </c>
-      <c r="H120" t="n">
+      <c r="I120" t="n">
         <v>2</v>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J120" t="n">
+      <c r="K120" t="n">
         <v>1.084</v>
       </c>
-      <c r="K120" t="n">
+      <c r="L120" t="n">
         <v>2786.97745484648</v>
       </c>
-      <c r="L120" t="n">
-        <v>106.2320000000706</v>
-      </c>
       <c r="M120" t="n">
+        <v>106.2320000000707</v>
+      </c>
+      <c r="N120" t="n">
         <v>0.03811728</v>
       </c>
     </row>
@@ -6091,46 +6453,49 @@
       <c r="A121" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="B121" s="2" t="n">
+      <c r="B121" t="n">
+        <v>119</v>
+      </c>
+      <c r="C121" s="2" t="n">
         <v>45436.93561342593</v>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>ETHEUR</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
         <v>3502.04619556</v>
       </c>
-      <c r="F121" t="n">
+      <c r="G121" t="n">
         <v>0.04197546</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>150</v>
       </c>
-      <c r="H121" t="n">
+      <c r="I121" t="n">
         <v>3</v>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J121" t="n">
+      <c r="K121" t="n">
         <v>1.084</v>
       </c>
-      <c r="K121" t="n">
+      <c r="L121" t="n">
         <v>3796.21807598704</v>
       </c>
-      <c r="L121" t="n">
+      <c r="M121" t="n">
         <v>159.347999999871</v>
       </c>
-      <c r="M121" t="n">
+      <c r="N121" t="n">
         <v>0.04197546</v>
       </c>
     </row>
@@ -6138,46 +6503,49 @@
       <c r="A122" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="B122" s="2" t="n">
+      <c r="B122" t="n">
+        <v>120</v>
+      </c>
+      <c r="C122" s="2" t="n">
         <v>45436.93466435185</v>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E122" t="n">
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
         <v>157.11043262</v>
       </c>
-      <c r="F122" t="n">
+      <c r="G122" t="n">
         <v>0.62376507</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>100</v>
       </c>
-      <c r="H122" t="n">
+      <c r="I122" t="n">
         <v>2</v>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="J122" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J122" t="n">
+      <c r="K122" t="n">
         <v>1.084108331666667</v>
       </c>
-      <c r="K122" t="n">
+      <c r="L122" t="n">
         <v>170.3247289950965</v>
       </c>
-      <c r="L122" t="n">
+      <c r="M122" t="n">
         <v>106.2426165043574</v>
       </c>
-      <c r="M122" t="n">
+      <c r="N122" t="n">
         <v>0.62376507</v>
       </c>
     </row>
@@ -6185,46 +6553,49 @@
       <c r="A123" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="B123" s="2" t="n">
+      <c r="B123" t="n">
+        <v>121</v>
+      </c>
+      <c r="C123" s="2" t="n">
         <v>45436.43322916667</v>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
         <v>63003.06014864</v>
       </c>
-      <c r="F123" t="n">
+      <c r="G123" t="n">
         <v>0.00155548</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>100</v>
       </c>
-      <c r="H123" t="n">
+      <c r="I123" t="n">
         <v>2</v>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="J123" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J123" t="n">
+      <c r="K123" t="n">
         <v>1.0829</v>
       </c>
-      <c r="K123" t="n">
+      <c r="L123" t="n">
         <v>68226.01383496226</v>
       </c>
-      <c r="L123" t="n">
+      <c r="M123" t="n">
         <v>106.1242000000071</v>
       </c>
-      <c r="M123" t="n">
+      <c r="N123" t="n">
         <v>0.00155548</v>
       </c>
     </row>
@@ -6232,46 +6603,49 @@
       <c r="A124" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="B124" s="2" t="n">
+      <c r="B124" t="n">
+        <v>122</v>
+      </c>
+      <c r="C124" s="2" t="n">
         <v>45426.64160879629</v>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
         <v>57930.57788707</v>
       </c>
-      <c r="F124" t="n">
+      <c r="G124" t="n">
         <v>0.00084584</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>50</v>
       </c>
-      <c r="H124" t="n">
+      <c r="I124" t="n">
         <v>1</v>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="J124" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J124" t="n">
+      <c r="K124" t="n">
         <v>1.0814</v>
       </c>
-      <c r="K124" t="n">
+      <c r="L124" t="n">
         <v>62646.12692707749</v>
       </c>
-      <c r="L124" t="n">
+      <c r="M124" t="n">
         <v>52.98859999999923</v>
       </c>
-      <c r="M124" t="n">
+      <c r="N124" t="n">
         <v>0.00084584</v>
       </c>
     </row>
@@ -6279,46 +6653,49 @@
       <c r="A125" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="B125" s="2" t="n">
+      <c r="B125" t="n">
+        <v>123</v>
+      </c>
+      <c r="C125" s="2" t="n">
         <v>45425.85847222222</v>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
         <v>140.23996862</v>
       </c>
-      <c r="F125" t="n">
+      <c r="G125" t="n">
         <v>0.69880221</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>100</v>
       </c>
-      <c r="H125" t="n">
+      <c r="I125" t="n">
         <v>2</v>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="J125" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J125" t="n">
+      <c r="K125" t="n">
         <v>1.078779998333333</v>
       </c>
-      <c r="K125" t="n">
-        <v>151.2880731141504</v>
-      </c>
       <c r="L125" t="n">
-        <v>105.7204398388099</v>
+        <v>151.2880731141503</v>
       </c>
       <c r="M125" t="n">
+        <v>105.7204398388098</v>
+      </c>
+      <c r="N125" t="n">
         <v>0.69880221</v>
       </c>
     </row>
@@ -6326,46 +6703,49 @@
       <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="B126" s="2" t="n">
+      <c r="B126" t="n">
+        <v>124</v>
+      </c>
+      <c r="C126" s="2" t="n">
         <v>45422.83993055556</v>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>RNDREUR</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
         <v>10.58084967</v>
       </c>
-      <c r="F126" t="n">
+      <c r="G126" t="n">
         <v>1.85240322</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>20</v>
       </c>
-      <c r="H126" t="n">
+      <c r="I126" t="n">
         <v>0.4</v>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="J126" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J126" t="n">
+      <c r="K126" t="n">
         <v>1.076449998333333</v>
       </c>
-      <c r="K126" t="n">
+      <c r="L126" t="n">
         <v>11.38975560963675</v>
       </c>
-      <c r="L126" t="n">
+      <c r="M126" t="n">
         <v>21.09841996630417</v>
       </c>
-      <c r="M126" t="n">
+      <c r="N126" t="n">
         <v>1.85240322</v>
       </c>
     </row>
@@ -6373,46 +6753,49 @@
       <c r="A127" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="B127" s="2" t="n">
+      <c r="B127" t="n">
+        <v>125</v>
+      </c>
+      <c r="C127" s="2" t="n">
         <v>45422.83865740741</v>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>ETHEUR</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
         <v>2752.33311287</v>
       </c>
-      <c r="F127" t="n">
+      <c r="G127" t="n">
         <v>0.00533729</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>15</v>
       </c>
-      <c r="H127" t="n">
+      <c r="I127" t="n">
         <v>0.31</v>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="J127" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J127" t="n">
+      <c r="K127" t="n">
         <v>1.0764</v>
       </c>
-      <c r="K127" t="n">
+      <c r="L127" t="n">
         <v>2962.611362693268</v>
       </c>
-      <c r="L127" t="n">
+      <c r="M127" t="n">
         <v>15.81231599998915</v>
       </c>
-      <c r="M127" t="n">
+      <c r="N127" t="n">
         <v>0.00533729</v>
       </c>
     </row>
@@ -6420,46 +6803,49 @@
       <c r="A128" s="1" t="n">
         <v>126</v>
       </c>
-      <c r="B128" s="2" t="n">
+      <c r="B128" t="n">
+        <v>126</v>
+      </c>
+      <c r="C128" s="2" t="n">
         <v>45422.83754629629</v>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
         <v>57425.23976014</v>
       </c>
-      <c r="F128" t="n">
+      <c r="G128" t="n">
         <v>0.00051197</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>30</v>
       </c>
-      <c r="H128" t="n">
+      <c r="I128" t="n">
         <v>0.6</v>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="J128" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J128" t="n">
+      <c r="K128" t="n">
         <v>1.0764</v>
       </c>
-      <c r="K128" t="n">
+      <c r="L128" t="n">
         <v>61812.5280778147</v>
       </c>
-      <c r="L128" t="n">
+      <c r="M128" t="n">
         <v>31.64615999999879</v>
       </c>
-      <c r="M128" t="n">
+      <c r="N128" t="n">
         <v>0.00051197</v>
       </c>
     </row>
@@ -6467,46 +6853,49 @@
       <c r="A129" s="1" t="n">
         <v>127</v>
       </c>
-      <c r="B129" s="2" t="n">
+      <c r="B129" t="n">
+        <v>127</v>
+      </c>
+      <c r="C129" s="2" t="n">
         <v>45422.83584490741</v>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>FETEUR</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
         <v>2.10457801</v>
       </c>
-      <c r="F129" t="n">
+      <c r="G129" t="n">
         <v>6.98002161</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>15</v>
       </c>
-      <c r="H129" t="n">
+      <c r="I129" t="n">
         <v>0.31</v>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J129" t="n">
+      <c r="K129" t="n">
         <v>1.076438331666667</v>
       </c>
-      <c r="K129" t="n">
-        <v>2.265448441946753</v>
-      </c>
       <c r="L129" t="n">
+        <v>2.265448441946754</v>
+      </c>
+      <c r="M129" t="n">
         <v>15.81287908112917</v>
       </c>
-      <c r="M129" t="n">
+      <c r="N129" t="n">
         <v>6.98002161</v>
       </c>
     </row>
@@ -6514,46 +6903,49 @@
       <c r="A130" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="B130" s="2" t="n">
+      <c r="B130" t="n">
+        <v>128</v>
+      </c>
+      <c r="C130" s="2" t="n">
         <v>45422.83362268518</v>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>TRXEUR</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
         <v>0.1200639</v>
       </c>
-      <c r="F130" t="n">
+      <c r="G130" t="n">
         <v>163.24640485</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>20</v>
       </c>
-      <c r="H130" t="n">
+      <c r="I130" t="n">
         <v>0.4</v>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="J130" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J130" t="n">
+      <c r="K130" t="n">
         <v>1.0763</v>
       </c>
-      <c r="K130" t="n">
+      <c r="L130" t="n">
         <v>0.12922477557</v>
       </c>
-      <c r="L130" t="n">
+      <c r="M130" t="n">
         <v>21.09548002935061</v>
       </c>
-      <c r="M130" t="n">
+      <c r="N130" t="n">
         <v>163.24640485</v>
       </c>
     </row>
@@ -6561,46 +6953,49 @@
       <c r="A131" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="B131" s="2" t="n">
+      <c r="B131" t="n">
+        <v>129</v>
+      </c>
+      <c r="C131" s="2" t="n">
         <v>45422.83130787037</v>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
         <v>140.17980062</v>
       </c>
-      <c r="F131" t="n">
+      <c r="G131" t="n">
         <v>0.13982043</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>20</v>
       </c>
-      <c r="H131" t="n">
+      <c r="I131" t="n">
         <v>0.4</v>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="J131" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J131" t="n">
+      <c r="K131" t="n">
         <v>1.076308335</v>
       </c>
-      <c r="K131" t="n">
+      <c r="L131" t="n">
         <v>150.8766878059442</v>
       </c>
-      <c r="L131" t="n">
+      <c r="M131" t="n">
         <v>21.09564336600287</v>
       </c>
-      <c r="M131" t="n">
+      <c r="N131" t="n">
         <v>0.13982043</v>
       </c>
     </row>
@@ -6608,46 +7003,49 @@
       <c r="A132" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="B132" s="2" t="n">
+      <c r="B132" t="n">
+        <v>130</v>
+      </c>
+      <c r="C132" s="2" t="n">
         <v>45422.82967592592</v>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>TNSREUR</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
         <v>0.79988478</v>
       </c>
-      <c r="F132" t="n">
+      <c r="G132" t="n">
         <v>18.36514507</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>15</v>
       </c>
-      <c r="H132" t="n">
+      <c r="I132" t="n">
         <v>0.31</v>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="J132" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J132" t="n">
+      <c r="K132" t="n">
         <v>1.076426665</v>
       </c>
-      <c r="K132" t="n">
+      <c r="L132" t="n">
         <v>0.8610173061196587</v>
       </c>
-      <c r="L132" t="n">
+      <c r="M132" t="n">
         <v>15.81270773466813</v>
       </c>
-      <c r="M132" t="n">
+      <c r="N132" t="n">
         <v>18.36514507</v>
       </c>
     </row>
@@ -6655,46 +7053,49 @@
       <c r="A133" s="1" t="n">
         <v>131</v>
       </c>
-      <c r="B133" s="2" t="n">
+      <c r="B133" t="n">
+        <v>131</v>
+      </c>
+      <c r="C133" s="2" t="n">
         <v>45422.08221064815</v>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
         <v>143.75063899</v>
       </c>
-      <c r="F133" t="n">
+      <c r="G133" t="n">
         <v>0.13634722</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>20</v>
       </c>
-      <c r="H133" t="n">
+      <c r="I133" t="n">
         <v>0.4</v>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="J133" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J133" t="n">
+      <c r="K133" t="n">
         <v>1.077761665</v>
       </c>
-      <c r="K133" t="n">
+      <c r="L133" t="n">
         <v>154.9289280226763</v>
       </c>
-      <c r="L133" t="n">
-        <v>21.12412863347202</v>
-      </c>
       <c r="M133" t="n">
+        <v>21.12412863347201</v>
+      </c>
+      <c r="N133" t="n">
         <v>0.13634722</v>
       </c>
     </row>
@@ -6702,46 +7103,49 @@
       <c r="A134" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="B134" s="2" t="n">
+      <c r="B134" t="n">
+        <v>132</v>
+      </c>
+      <c r="C134" s="2" t="n">
         <v>45422.07099537037</v>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>USDTEUR</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
         <v>0.93873598</v>
       </c>
-      <c r="F134" t="n">
+      <c r="G134" t="n">
         <v>26.08827246</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>25</v>
       </c>
-      <c r="H134" t="n">
+      <c r="I134" t="n">
         <v>0.51</v>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="J134" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J134" t="n">
+      <c r="K134" t="n">
         <v>1.0778</v>
       </c>
-      <c r="K134" t="n">
+      <c r="L134" t="n">
         <v>1.011769639244</v>
       </c>
-      <c r="L134" t="n">
+      <c r="M134" t="n">
         <v>26.39532201535338</v>
       </c>
-      <c r="M134" t="n">
+      <c r="N134" t="n">
         <v>26.08827246</v>
       </c>
     </row>
@@ -6749,93 +7153,99 @@
       <c r="A135" s="1" t="n">
         <v>133</v>
       </c>
-      <c r="B135" s="2" t="n">
+      <c r="B135" t="n">
+        <v>133</v>
+      </c>
+      <c r="C135" s="2" t="n">
         <v>45422.06987268518</v>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>MKREUR</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E135" t="n">
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
         <v>2583.15065304</v>
       </c>
-      <c r="F135" t="n">
+      <c r="G135" t="n">
         <v>0.00682887</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>18</v>
       </c>
-      <c r="H135" t="n">
+      <c r="I135" t="n">
         <v>0.36</v>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="J135" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J135" t="n">
+      <c r="K135" t="n">
         <v>1.077938331666667</v>
       </c>
-      <c r="K135" t="n">
+      <c r="L135" t="n">
         <v>2784.477105381599</v>
       </c>
-      <c r="L135" t="n">
+      <c r="M135" t="n">
         <v>19.01483217062724</v>
       </c>
-      <c r="M135" t="n">
-        <v>0.006828870000000001</v>
+      <c r="N135" t="n">
+        <v>0.006828869999999999</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="B136" s="2" t="n">
+      <c r="B136" t="n">
+        <v>134</v>
+      </c>
+      <c r="C136" s="2" t="n">
         <v>45422.05619212963</v>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>FETEUR</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E136" t="n">
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
         <v>2.1432031</v>
       </c>
-      <c r="F136" t="n">
+      <c r="G136" t="n">
         <v>11.42682187</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>25</v>
       </c>
-      <c r="H136" t="n">
+      <c r="I136" t="n">
         <v>0.51</v>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="J136" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J136" t="n">
+      <c r="K136" t="n">
         <v>1.077691668333334</v>
       </c>
-      <c r="K136" t="n">
-        <v>2.309712124416172</v>
-      </c>
       <c r="L136" t="n">
-        <v>26.39266901668288</v>
+        <v>2.309712124416173</v>
       </c>
       <c r="M136" t="n">
+        <v>26.39266901668289</v>
+      </c>
+      <c r="N136" t="n">
         <v>11.42682187</v>
       </c>
     </row>
@@ -6843,46 +7253,49 @@
       <c r="A137" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="B137" s="2" t="n">
+      <c r="B137" t="n">
+        <v>135</v>
+      </c>
+      <c r="C137" s="2" t="n">
         <v>45422.01804398148</v>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>RNDREUR</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
         <v>10.23426316</v>
       </c>
-      <c r="F137" t="n">
+      <c r="G137" t="n">
         <v>2.39294218</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>25</v>
       </c>
-      <c r="H137" t="n">
+      <c r="I137" t="n">
         <v>0.51</v>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J137" t="n">
+      <c r="K137" t="n">
         <v>1.077698335</v>
       </c>
-      <c r="K137" t="n">
+      <c r="L137" t="n">
         <v>11.02944836748384</v>
       </c>
-      <c r="L137" t="n">
+      <c r="M137" t="n">
         <v>26.39283222068422</v>
       </c>
-      <c r="M137" t="n">
+      <c r="N137" t="n">
         <v>2.39294218</v>
       </c>
     </row>
@@ -6890,46 +7303,49 @@
       <c r="A138" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="B138" s="2" t="n">
+      <c r="B138" t="n">
+        <v>136</v>
+      </c>
+      <c r="C138" s="2" t="n">
         <v>45421.93954861111</v>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>TRXEUR</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
         <v>0.11898276</v>
       </c>
-      <c r="F138" t="n">
+      <c r="G138" t="n">
         <v>205.82814242</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>25</v>
       </c>
-      <c r="H138" t="n">
+      <c r="I138" t="n">
         <v>0.51</v>
       </c>
-      <c r="I138" t="inlineStr">
+      <c r="J138" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J138" t="n">
+      <c r="K138" t="n">
         <v>1.077904998333333</v>
       </c>
-      <c r="K138" t="n">
+      <c r="L138" t="n">
         <v>0.1282521117194954</v>
       </c>
-      <c r="L138" t="n">
+      <c r="M138" t="n">
         <v>26.39789391666605</v>
       </c>
-      <c r="M138" t="n">
+      <c r="N138" t="n">
         <v>205.82814242</v>
       </c>
     </row>
@@ -6937,46 +7353,49 @@
       <c r="A139" s="1" t="n">
         <v>137</v>
       </c>
-      <c r="B139" s="2" t="n">
+      <c r="B139" t="n">
+        <v>137</v>
+      </c>
+      <c r="C139" s="2" t="n">
         <v>45421.81724537037</v>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>UMAEUR</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
         <v>3.80349912</v>
       </c>
-      <c r="F139" t="n">
+      <c r="G139" t="n">
         <v>6.43880785</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>25</v>
       </c>
-      <c r="H139" t="n">
+      <c r="I139" t="n">
         <v>0.51</v>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="J139" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J139" t="n">
+      <c r="K139" t="n">
         <v>1.077516665</v>
       </c>
-      <c r="K139" t="n">
-        <v>4.098333687112834</v>
-      </c>
       <c r="L139" t="n">
-        <v>26.38838311650156</v>
+        <v>4.098333687112835</v>
       </c>
       <c r="M139" t="n">
+        <v>26.38838311650157</v>
+      </c>
+      <c r="N139" t="n">
         <v>6.43880785</v>
       </c>
     </row>
@@ -6984,46 +7403,49 @@
       <c r="A140" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="B140" s="2" t="n">
+      <c r="B140" t="n">
+        <v>138</v>
+      </c>
+      <c r="C140" s="2" t="n">
         <v>45418.97721064815</v>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>ETHEUR</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
         <v>2912.26895648</v>
       </c>
-      <c r="F140" t="n">
+      <c r="G140" t="n">
         <v>0.00840723</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>25</v>
       </c>
-      <c r="H140" t="n">
+      <c r="I140" t="n">
         <v>0.51</v>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="J140" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J140" t="n">
+      <c r="K140" t="n">
         <v>1.076</v>
       </c>
-      <c r="K140" t="n">
+      <c r="L140" t="n">
         <v>3133.60139717248</v>
       </c>
-      <c r="L140" t="n">
+      <c r="M140" t="n">
         <v>26.34490767435039</v>
       </c>
-      <c r="M140" t="n">
+      <c r="N140" t="n">
         <v>0.00840723</v>
       </c>
     </row>
@@ -7031,46 +7453,49 @@
       <c r="A141" s="1" t="n">
         <v>139</v>
       </c>
-      <c r="B141" s="2" t="n">
+      <c r="B141" t="n">
+        <v>139</v>
+      </c>
+      <c r="C141" s="2" t="n">
         <v>45418.96918981482</v>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
         <v>59899.71272325</v>
       </c>
-      <c r="F141" t="n">
+      <c r="G141" t="n">
         <v>0.00040885</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>25</v>
       </c>
-      <c r="H141" t="n">
+      <c r="I141" t="n">
         <v>0.51</v>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="J141" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J141" t="n">
+      <c r="K141" t="n">
         <v>1.0761</v>
       </c>
-      <c r="K141" t="n">
-        <v>64458.08086148931</v>
-      </c>
       <c r="L141" t="n">
-        <v>26.3536863602199</v>
+        <v>64458.08086148932</v>
       </c>
       <c r="M141" t="n">
+        <v>26.35368636021991</v>
+      </c>
+      <c r="N141" t="n">
         <v>0.00040885</v>
       </c>
     </row>
@@ -7078,46 +7503,49 @@
       <c r="A142" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="B142" s="2" t="n">
+      <c r="B142" t="n">
+        <v>140</v>
+      </c>
+      <c r="C142" s="2" t="n">
         <v>45414.95027777777</v>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
         <v>131.18665751</v>
       </c>
-      <c r="F142" t="n">
+      <c r="G142" t="n">
         <v>0.18668057</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>25</v>
       </c>
-      <c r="H142" t="n">
+      <c r="I142" t="n">
         <v>0.51</v>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="J142" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J142" t="n">
+      <c r="K142" t="n">
         <v>1.070940001666667</v>
       </c>
-      <c r="K142" t="n">
-        <v>140.4930392124038</v>
-      </c>
       <c r="L142" t="n">
-        <v>26.2273206412039</v>
+        <v>140.4930392124039</v>
       </c>
       <c r="M142" t="n">
+        <v>26.22732064120391</v>
+      </c>
+      <c r="N142" t="n">
         <v>0.18668057</v>
       </c>
     </row>

--- a/Trade History Reconstructed.xlsx
+++ b/Trade History Reconstructed.xlsx
@@ -429,66 +429,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:N142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Date(UTC)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Fee Coin</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Pair Price</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Price in USDT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Total in USDT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Pair Quantity</t>
         </is>
@@ -498,46 +503,49 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>46081.50087962963</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>0.2791</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1702.7</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>475.22357</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1.617565</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.2792733316666667</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.2791</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>475.2235700000001</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1702.7</v>
       </c>
     </row>
@@ -545,46 +553,49 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>46081.50046296296</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>63986.13</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.00046</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>29.4336198</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>3.528e-05</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>63900.73367266667</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>63986.13</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>29.4336198</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0.00046</v>
       </c>
     </row>
@@ -592,46 +603,49 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>46081.5003125</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>594.34</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.75</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>445.755</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.0005343</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>594.6545034999999</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>594.34</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>445.755</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -639,46 +653,49 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>46054.61652777778</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>770.6900000000001</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.636</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>490.15884</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.00045314</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>753.2940488333334</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>770.6900000000001</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>490.1588400000001</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.636</v>
       </c>
     </row>
@@ -686,46 +703,49 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>46054.61582175926</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>78597.2</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.00114</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>89.600808</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>8.284e-05</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>77971.77212000001</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>78597.2</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>89.60080799999999</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.00114</v>
       </c>
     </row>
@@ -733,46 +753,49 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>46054.61512731481</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.2859</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>1399</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>399.9741</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.00036997</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0.285821665</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.2859</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>399.9741</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1399</v>
       </c>
     </row>
@@ -780,46 +803,49 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>46023.11693287037</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>869.59</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.083</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>72.17597000000001</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>5.913e-05</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>871.1663310000001</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>869.59</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>72.17597000000001</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>0.083</v>
       </c>
     </row>
@@ -827,46 +853,49 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>46023.11655092592</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>511.04</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.011</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>5.62144</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>4.6e-06</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>510.0416685</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>511.04</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>5.62144</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.011</v>
       </c>
     </row>
@@ -874,46 +903,49 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>46023.11655092592</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>511.01</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.015</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>7.66515</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>6.27e-06</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>510.0416685</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>511.01</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>7.66515</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -921,46 +953,49 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>46023.11655092592</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>511.08</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.011</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>5.62188</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>4.6e-06</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>510.0416685</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>511.08</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>5.621879999999999</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0.011</v>
       </c>
     </row>
@@ -968,46 +1003,49 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>46023.11582175926</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>87764.99000000001</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0.00055</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>48.2707445</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>3.955e-05</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>87944.2532895</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>87764.99000000001</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>48.27074450000001</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0.00055</v>
       </c>
     </row>
@@ -1015,46 +1053,49 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2" t="n">
         <v>45990.61078703704</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>0.2812</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>245.1</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>68.92212000000001</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>5.596e-05</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>0.281253335</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>0.2812</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>68.92212000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>245.1</v>
       </c>
     </row>
@@ -1062,46 +1103,49 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>45990.61035879629</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>460.21</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>0.048</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>22.09008</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1.792e-05</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>459.2474745000001</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>460.21</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>22.09008</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>0.048</v>
       </c>
     </row>
@@ -1109,46 +1153,49 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>45990.60915509259</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>877.15</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>0.103</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>90.34645</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>7.334999999999999e-05</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>876.7868385</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>877.15</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>90.34644999999999</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -1156,46 +1203,49 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2" t="n">
         <v>45962.06081018518</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>1088.98</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.136</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>148.10128</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>9.69e-05</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>1088.9890135</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>1088.98</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>148.10128</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -1203,46 +1253,49 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2" t="n">
         <v>45962.05966435185</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>0.296</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>2624.2</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>776.7632</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>2.49299</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="J17" t="n">
-        <v>0.296</v>
       </c>
       <c r="K17" t="n">
         <v>0.296</v>
       </c>
       <c r="L17" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="M17" t="n">
         <v>776.7631999999999</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>2624.2</v>
       </c>
     </row>
@@ -1250,46 +1303,49 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="n">
         <v>45962.05966435185</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>0.296</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>585.2</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>173.2192</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>0.55594</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="J18" t="n">
-        <v>0.296</v>
       </c>
       <c r="K18" t="n">
         <v>0.296</v>
       </c>
       <c r="L18" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="M18" t="n">
         <v>173.2192</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>585.2</v>
       </c>
     </row>
@@ -1297,46 +1353,49 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2" t="n">
         <v>45962.05902777778</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>109727.81</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>0.01002</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>1099.4726562</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1.04449902</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>109764.5000986667</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>109727.81</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>1099.4726562</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>0.01002</v>
       </c>
     </row>
@@ -1344,46 +1403,49 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2" t="n">
         <v>45931.03042824074</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>113954.4</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.00396</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>451.259424</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>3.834e-05</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>113986.300759</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>113954.4</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>451.259424</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>0.00396</v>
       </c>
     </row>
@@ -1391,46 +1453,49 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" s="2" t="n">
         <v>45931.02980324074</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>0.3329</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>905.7</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>301.50753</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>0.28643215</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>0.3333916683333333</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>0.3329</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>301.50753</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>905.7</v>
       </c>
     </row>
@@ -1438,46 +1503,49 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="2" t="n">
         <v>45931.02895833334</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>0.3329</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>452</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>150.4708</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>0.14294726</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>0.3334</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>0.3329</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>150.4708</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>452</v>
       </c>
     </row>
@@ -1485,46 +1553,49 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="2" t="n">
         <v>45900.93915509259</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>0.3425</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>200.6</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>68.7055</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>5.642e-05</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>0.342961665</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>0.3425</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>68.7055</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>200.6</v>
       </c>
     </row>
@@ -1532,46 +1603,49 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" s="2" t="n">
         <v>45900.93896990741</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>109079.99</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>0.00063</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>68.7203937</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>5.645e-05</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>109075.7142211667</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>109079.99</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>68.7203937</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>0.00063</v>
       </c>
     </row>
@@ -1579,46 +1653,49 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" s="2" t="n">
         <v>45900.93672453704</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>0.34241792</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>2022.6</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>692.57447</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>0.00056949</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>0.3431</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>0.34241792</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>692.574484992</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>2022.6</v>
       </c>
     </row>
@@ -1626,46 +1703,49 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" s="2" t="n">
         <v>45900.93601851852</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>867.28</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>0.019</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>16.47832</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>1.353e-05</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>866.8346673333334</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>867.28</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>16.47832</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>0.019</v>
       </c>
     </row>
@@ -1673,46 +1753,49 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" s="2" t="n">
         <v>45900.93578703704</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>ETHUSDT</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>4462.54</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>0.0693</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>309.254022</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>0.00025404</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>4467.496042999999</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>4462.54</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>309.254022</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>0.0693</v>
       </c>
     </row>
@@ -1720,46 +1803,49 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" s="2" t="n">
         <v>45900.93532407407</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>SOLUSDT</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>204.95</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>1.79</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>366.8605</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>0.0003014</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>205.7853301666667</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>204.95</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>366.8605</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>1.79</v>
       </c>
     </row>
@@ -1767,46 +1853,49 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>841.902968</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>1.648052154152757e-05</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>0.013875</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>3.3e-07</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>894.9224991666665</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>841.902968</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>0.013875</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>1.648052154152757e-05</v>
       </c>
     </row>
@@ -1814,46 +1903,49 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>0.024577</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>0.5645522236237132</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>0.013875</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>3.3e-07</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>0.02457696902309403</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>0.000604028167680582</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>0.0003410054451954296</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>0.5645522236237132</v>
       </c>
     </row>
@@ -1861,46 +1953,49 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>0.015385</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>0.9018524536886579</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>0.013875</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>3.3e-07</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>0.01658150016666667</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>0.015385</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>0.013875</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>0.9018524536886579</v>
       </c>
     </row>
@@ -1908,46 +2003,49 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>894.9224991666665</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>2.229999999999999e-06</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>0.001995677173141666</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>4e-08</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J32" t="n">
-        <v>894.9224991666665</v>
       </c>
       <c r="K32" t="n">
         <v>894.9224991666665</v>
       </c>
       <c r="L32" t="n">
+        <v>894.9224991666665</v>
+      </c>
+      <c r="M32" t="n">
         <v>0.001995677173141665</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2.229999999999999e-06</v>
       </c>
     </row>
@@ -1955,46 +2053,49 @@
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>0.163644480872939</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>0.001995677173141666</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>4e-08</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>0.1749</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>0.163644480872939</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>0.001995677173141666</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>0.0121952</v>
       </c>
     </row>
@@ -2002,46 +2103,49 @@
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>3.747533232175975</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>6.02</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>22.56015005769937</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>3.28e-06</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>0.02457696902309403</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>0.09210300816020439</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>0.5544601091244304</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>6.02</v>
       </c>
     </row>
@@ -2049,46 +2153,49 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="2" t="n">
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>894.922499</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>0.0252090545079696</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>22.56015005769937</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>3.28e-06</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>894.9224991666665</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>894.922499</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>22.56015005769937</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>0.0252090545079696</v>
       </c>
     </row>
@@ -2096,46 +2203,49 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" s="2" t="n">
         <v>45891.84428240741</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>0.02457606291472106</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>8718.124</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>214.2571639223396</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>0.00026837</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>0.02457606291472106</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>0.0006039828683883277</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>5.265597540485121</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8718.124</v>
       </c>
     </row>
@@ -2143,46 +2253,49 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" s="2" t="n">
         <v>45891.84428240741</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0.3650036864094372</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>586.9999999999999</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>214.2571639223396</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>0.00026837</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>0.3659</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>0.3650036864094372</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>214.2571639223396</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>586.9999999999999</v>
       </c>
     </row>
@@ -2190,46 +2303,49 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" s="2" t="n">
         <v>45891.84357638889</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>0.02458361491986309</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>8724.144000000002</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>214.4709966014341</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>0.00026861</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>0.02458361491986309</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>0.000604354122528115</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>5.272472391928921</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>8724.144000000002</v>
       </c>
     </row>
@@ -2237,46 +2353,49 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" s="2" t="n">
         <v>45891.84357638889</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>0.01676602537534663</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>12792</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>214.4709966014341</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>0.00026861</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>0.01655750016666666</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>0.01676602537534663</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>214.4709966014341</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>12792</v>
       </c>
     </row>
@@ -2284,46 +2403,49 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" s="2" t="n">
         <v>45878.0263425926</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>794.6106690000001</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>0.01898484</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>1.423e-05</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J40" t="n">
-        <v>794.6106690000001</v>
       </c>
       <c r="K40" t="n">
         <v>794.6106690000001</v>
       </c>
       <c r="L40" t="n">
+        <v>794.6106690000001</v>
+      </c>
+      <c r="M40" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>0.01898484</v>
       </c>
     </row>
@@ -2331,46 +2453,49 @@
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B41" t="n">
+        <v>39</v>
+      </c>
+      <c r="C41" s="2" t="n">
         <v>45878.0263425926</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>0.1296010001139</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>116.4</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>1.423e-05</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>0.13021333</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>0.1296010001139</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>116.4</v>
       </c>
     </row>
@@ -2378,46 +2503,49 @@
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" s="2" t="n">
         <v>45560.6427662037</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>1.1803</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>57</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>67.2771</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>0.057</v>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>1.179691675</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>1.1803</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>67.27709999999999</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>56.99999999999999</v>
       </c>
     </row>
@@ -2425,46 +2553,49 @@
       <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" s="2" t="n">
         <v>45560.6427662037</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
         <v>1.1803</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>34</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>40.1302</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>0.034</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>1.179691675</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>1.1803</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>40.13019999999999</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>34</v>
       </c>
     </row>
@@ -2472,46 +2603,49 @@
       <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B44" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" s="2" t="n">
         <v>45560.6427662037</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
         <v>1.1802</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>94</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>110.9388</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>0.094</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>1.179691675</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>1.1802</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>110.9388</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>94</v>
       </c>
     </row>
@@ -2519,46 +2653,49 @@
       <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B45" t="n">
+        <v>43</v>
+      </c>
+      <c r="C45" s="2" t="n">
         <v>45560.64236111111</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>0.1508</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>1456.1</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>219.57988</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>0.21957988</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>0.1508000016666667</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>0.1508</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>219.57988</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>1456.1</v>
       </c>
     </row>
@@ -2566,46 +2703,49 @@
       <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B46" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" s="2" t="n">
         <v>45553.90638888889</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>60330.29408616667</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>0.00132203</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>79.75845869073494</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>0.073</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
-      </c>
-      <c r="J46" t="n">
-        <v>60330.29408616667</v>
       </c>
       <c r="K46" t="n">
         <v>60330.29408616667</v>
       </c>
       <c r="L46" t="n">
+        <v>60330.29408616667</v>
+      </c>
+      <c r="M46" t="n">
         <v>79.75845869073493</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>0.00132203</v>
       </c>
     </row>
@@ -2613,46 +2753,49 @@
       <c r="A47" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" t="n">
+        <v>45</v>
+      </c>
+      <c r="C47" s="2" t="n">
         <v>45553.90638888889</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
         <v>1.092581625900479</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>73</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>79.75845869073494</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>0.073</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>1.091139995</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>1.092581625900479</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>79.75845869073497</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>73</v>
       </c>
     </row>
@@ -2660,46 +2803,49 @@
       <c r="A48" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="2" t="n">
+      <c r="B48" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" s="2" t="n">
         <v>45529.90896990741</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>64353.81012600001</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>0.0025413</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>0.985</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="J48" t="n">
-        <v>64353.81012600001</v>
       </c>
       <c r="K48" t="n">
         <v>64353.81012600001</v>
       </c>
       <c r="L48" t="n">
+        <v>64353.81012600001</v>
+      </c>
+      <c r="M48" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>0.0025413</v>
       </c>
     </row>
@@ -2707,46 +2853,49 @@
       <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="2" t="n">
+      <c r="B49" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" s="2" t="n">
         <v>45529.90896990741</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
         <v>0.16603283012508</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>985</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>0.985</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>0.1655</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>0.16603283012508</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>985</v>
       </c>
     </row>
@@ -2754,46 +2903,49 @@
       <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" t="n">
+        <v>48</v>
+      </c>
+      <c r="C50" s="2" t="n">
         <v>45529.90652777778</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
         <v>0.1655</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>453</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>74.97150000000001</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>9.736e-05</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>0.1654599983333334</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>0.1655</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>74.97150000000001</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>453</v>
       </c>
     </row>
@@ -2801,46 +2953,49 @@
       <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="2" t="n">
+      <c r="B51" t="n">
+        <v>49</v>
+      </c>
+      <c r="C51" s="2" t="n">
         <v>45529.90614583333</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>0.343</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>218.6</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>74.9798</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>9.734999999999999e-05</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>0.3429850016666667</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>0.343</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>74.9798</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>218.6</v>
       </c>
     </row>
@@ -2848,46 +3003,49 @@
       <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" s="2" t="n">
         <v>45528.99840277778</v>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>580.5</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>0.1015056</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>58.92400079999999</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>0.371</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="J52" t="n">
-        <v>580.5</v>
       </c>
       <c r="K52" t="n">
         <v>580.5</v>
       </c>
       <c r="L52" t="n">
+        <v>580.5</v>
+      </c>
+      <c r="M52" t="n">
         <v>58.9240008</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>0.1015056</v>
       </c>
     </row>
@@ -2895,46 +3053,49 @@
       <c r="A53" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="2" t="n">
+      <c r="B53" t="n">
+        <v>51</v>
+      </c>
+      <c r="C53" s="2" t="n">
         <v>45528.99840277778</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
         <v>0.1588248</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>370.9999999999999</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>58.92400079999999</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>0.371</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>0.1589</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>0.1588248</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>58.92400079999998</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>370.9999999999999</v>
       </c>
     </row>
@@ -2942,46 +3103,49 @@
       <c r="A54" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B54" t="n">
+        <v>52</v>
+      </c>
+      <c r="C54" s="2" t="n">
         <v>45500.56033564815</v>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
         <v>68797.23868549999</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>0.00031044</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>2.709e-05</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J54" t="n">
-        <v>68797.23868549999</v>
       </c>
       <c r="K54" t="n">
         <v>68797.23868549999</v>
       </c>
       <c r="L54" t="n">
+        <v>68797.23868549999</v>
+      </c>
+      <c r="M54" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>0.00031044</v>
       </c>
     </row>
@@ -2989,46 +3153,49 @@
       <c r="A55" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B55" t="n">
+        <v>53</v>
+      </c>
+      <c r="C55" s="2" t="n">
         <v>45500.56033564815</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>0.136906504984145</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>156</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>2.709e-05</v>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>0.137311665</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>0.136906504984145</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>156</v>
       </c>
     </row>
@@ -3036,46 +3203,49 @@
       <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" t="n">
+        <v>54</v>
+      </c>
+      <c r="C56" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
         <v>68786.2337</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>0.0002774880000000001</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>19.0873544169456</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>2.447e-05</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J56" t="n">
-        <v>68786.2337</v>
       </c>
       <c r="K56" t="n">
         <v>68786.2337</v>
       </c>
       <c r="L56" t="n">
+        <v>68786.2337</v>
+      </c>
+      <c r="M56" t="n">
         <v>19.08735441694561</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>0.0002774880000000001</v>
       </c>
     </row>
@@ -3083,46 +3253,49 @@
       <c r="A57" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B57" t="n">
+        <v>55</v>
+      </c>
+      <c r="C57" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>MKRUSDT</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>0.0072</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>19.0873544169456</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>2.447e-05</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>2650.85005</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>19.0873544169456</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>0.007199999999999999</v>
       </c>
     </row>
@@ -3130,46 +3303,49 @@
       <c r="A58" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" t="n">
+        <v>56</v>
+      </c>
+      <c r="C58" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
         <v>68786.2337</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>0.001452958</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>0.00012672</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J58" t="n">
-        <v>68786.2337</v>
       </c>
       <c r="K58" t="n">
         <v>68786.2337</v>
       </c>
       <c r="L58" t="n">
+        <v>68786.2337</v>
+      </c>
+      <c r="M58" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>0.001452958</v>
       </c>
     </row>
@@ -3177,46 +3353,49 @@
       <c r="A59" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="2" t="n">
+      <c r="B59" t="n">
+        <v>57</v>
+      </c>
+      <c r="C59" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>MKRUSDT</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>0.0377</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>0.00012672</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>2650.85005</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>0.0377</v>
       </c>
     </row>
@@ -3224,46 +3403,49 @@
       <c r="A60" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" t="n">
+        <v>58</v>
+      </c>
+      <c r="C60" s="2" t="n">
         <v>45488.03726851852</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>OMEUR</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
         <v>1.00660569</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>194.71378022</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>200</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>4</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>1.0889</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>1.096092935841</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>213.424399010039</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>194.71378022</v>
       </c>
     </row>
@@ -3271,46 +3453,49 @@
       <c r="A61" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="2" t="n">
+      <c r="B61" t="n">
+        <v>59</v>
+      </c>
+      <c r="C61" s="2" t="n">
         <v>45479.77708333333</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>BNBEUR</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
         <v>485.5</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>0.1</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>48.55</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>7.499999999999999e-05</v>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>1.080199998333333</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>524.4370991908332</v>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
         <v>52.44370991908333</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3318,46 +3503,49 @@
       <c r="A62" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B62" t="n">
+        <v>60</v>
+      </c>
+      <c r="C62" s="2" t="n">
         <v>45479.76871527778</v>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
         <v>0.398</v>
       </c>
-      <c r="F62" t="n">
+      <c r="G62" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>34.0688</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>4.857e-05</v>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
         <v>0.39797001</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>0.398</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
         <v>34.0688</v>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
         <v>85.59999999999998</v>
       </c>
     </row>
@@ -3365,46 +3553,49 @@
       <c r="A63" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="2" t="n">
+      <c r="B63" t="n">
+        <v>61</v>
+      </c>
+      <c r="C63" s="2" t="n">
         <v>45479.76849537037</v>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>524.6</v>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>0.065</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>34.099</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>4.873e-05</v>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>524.5999999999999</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
         <v>524.6</v>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
         <v>34.099</v>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
         <v>0.065</v>
       </c>
     </row>
@@ -3412,46 +3603,49 @@
       <c r="A64" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="2" t="n">
+      <c r="B64" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" s="2" t="n">
         <v>45479.673125</v>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
         <v>0.02414</v>
       </c>
-      <c r="F64" t="n">
+      <c r="G64" t="n">
         <v>1976.8</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>47.719952</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>6.879e-05</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
         <v>0.02414200066666666</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
         <v>0.02414</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
         <v>47.719952</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
         <v>1976.8</v>
       </c>
     </row>
@@ -3459,46 +3653,49 @@
       <c r="A65" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="2" t="n">
+      <c r="B65" t="n">
+        <v>63</v>
+      </c>
+      <c r="C65" s="2" t="n">
         <v>45479.67239583333</v>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>PEPEUSDT</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>9.21e-06</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>5181574</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>47.72229654</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>6.889e-05</v>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
         <v>9.215000333333332e-06</v>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
         <v>9.21e-06</v>
       </c>
-      <c r="L65" t="n">
+      <c r="M65" t="n">
         <v>47.72229654</v>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
         <v>5181574</v>
       </c>
     </row>
@@ -3506,46 +3703,49 @@
       <c r="A66" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" t="n">
+        <v>64</v>
+      </c>
+      <c r="C66" s="2" t="n">
         <v>45459.61185185185</v>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>NOTUSDT</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>0.020114</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>2036</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>40.952104</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>0.0409521</v>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="K66" t="n">
         <v>0.02009346653333333</v>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
         <v>0.020114</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
         <v>40.952104</v>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
         <v>2036</v>
       </c>
     </row>
@@ -3553,46 +3753,49 @@
       <c r="A67" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="B67" s="2" t="n">
+      <c r="B67" t="n">
+        <v>65</v>
+      </c>
+      <c r="C67" s="2" t="n">
         <v>45457.95482638889</v>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>NOTUSDT</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
         <v>0.019619</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>88</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>1.726472</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>2.2e-06</v>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" t="n">
         <v>0.01962085005</v>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" t="n">
         <v>0.019619</v>
       </c>
-      <c r="L67" t="n">
+      <c r="M67" t="n">
         <v>1.726472</v>
       </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
         <v>88</v>
       </c>
     </row>
@@ -3600,46 +3803,49 @@
       <c r="A68" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B68" t="n">
+        <v>66</v>
+      </c>
+      <c r="C68" s="2" t="n">
         <v>45457.95482638889</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>NOTUSDT</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
         <v>0.019619</v>
       </c>
-      <c r="F68" t="n">
+      <c r="G68" t="n">
         <v>1950</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>38.25705</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>1.95</v>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="J68" t="n">
+      <c r="K68" t="n">
         <v>0.01962085005</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>0.019619</v>
       </c>
-      <c r="L68" t="n">
+      <c r="M68" t="n">
         <v>38.25705</v>
       </c>
-      <c r="M68" t="n">
+      <c r="N68" t="n">
         <v>1950</v>
       </c>
     </row>
@@ -3647,46 +3853,49 @@
       <c r="A69" s="1" t="n">
         <v>67</v>
       </c>
-      <c r="B69" s="2" t="n">
+      <c r="B69" t="n">
+        <v>67</v>
+      </c>
+      <c r="C69" s="2" t="n">
         <v>45457.95456018519</v>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="F69" t="n">
         <v>0.5085</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>9.5</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>4.83075</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>6.02e-06</v>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" t="n">
         <v>0.5088133366666666</v>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
         <v>0.5085</v>
       </c>
-      <c r="L69" t="n">
+      <c r="M69" t="n">
         <v>4.830749999999999</v>
       </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -3694,46 +3903,49 @@
       <c r="A70" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" t="n">
+        <v>68</v>
+      </c>
+      <c r="C70" s="2" t="n">
         <v>45457.95456018519</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="F70" t="n">
         <v>0.5086000000000001</v>
       </c>
-      <c r="F70" t="n">
+      <c r="G70" t="n">
         <v>29.8</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>15.15628</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>1.891e-05</v>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="K70" t="n">
         <v>0.5088133366666666</v>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
         <v>0.5086000000000001</v>
       </c>
-      <c r="L70" t="n">
+      <c r="M70" t="n">
         <v>15.15628</v>
       </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
         <v>29.8</v>
       </c>
     </row>
@@ -3741,46 +3953,49 @@
       <c r="A71" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="B71" s="2" t="n">
+      <c r="B71" t="n">
+        <v>69</v>
+      </c>
+      <c r="C71" s="2" t="n">
         <v>45457.95416666667</v>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>PEPEUSDT</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="F71" t="n">
         <v>1.145e-05</v>
       </c>
-      <c r="F71" t="n">
+      <c r="G71" t="n">
         <v>1746724</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>19.9999898</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>2.433e-05</v>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" t="n">
         <v>1.14600005e-05</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
         <v>1.145e-05</v>
       </c>
-      <c r="L71" t="n">
+      <c r="M71" t="n">
         <v>19.9999898</v>
       </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
         <v>1746724</v>
       </c>
     </row>
@@ -3788,46 +4003,49 @@
       <c r="A72" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="B72" s="2" t="n">
+      <c r="B72" t="n">
+        <v>70</v>
+      </c>
+      <c r="C72" s="2" t="n">
         <v>45455.6309837963</v>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
         <v>0.037824</v>
       </c>
-      <c r="F72" t="n">
+      <c r="G72" t="n">
         <v>3465.2</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>131.0677248</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>3.4652</v>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>JASMY</t>
         </is>
       </c>
-      <c r="J72" t="n">
+      <c r="K72" t="n">
         <v>0.03777478451666667</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>0.037824</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" t="n">
         <v>131.0677248</v>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
         <v>3465.2</v>
       </c>
     </row>
@@ -3835,46 +4053,49 @@
       <c r="A73" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" t="n">
+        <v>71</v>
+      </c>
+      <c r="C73" s="2" t="n">
         <v>45455.630625</v>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="F73" t="n">
         <v>69787.49000000001</v>
       </c>
-      <c r="F73" t="n">
+      <c r="G73" t="n">
         <v>0.00188</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>131.2004812</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>0.13120048</v>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
         <v>69787.75104183334</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
         <v>69787.49000000001</v>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" t="n">
         <v>131.2004812</v>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
         <v>0.00188</v>
       </c>
     </row>
@@ -3882,46 +4103,49 @@
       <c r="A74" s="1" t="n">
         <v>72</v>
       </c>
-      <c r="B74" s="2" t="n">
+      <c r="B74" t="n">
+        <v>72</v>
+      </c>
+      <c r="C74" s="2" t="n">
         <v>45455.03658564815</v>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
         <v>67225.22887250001</v>
       </c>
-      <c r="F74" t="n">
+      <c r="G74" t="n">
         <v>0.0001384</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>1.176e-05</v>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J74" t="n">
-        <v>67225.22887250001</v>
       </c>
       <c r="K74" t="n">
         <v>67225.22887250001</v>
       </c>
       <c r="L74" t="n">
+        <v>67225.22887250001</v>
+      </c>
+      <c r="M74" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="M74" t="n">
+      <c r="N74" t="n">
         <v>0.0001384</v>
       </c>
     </row>
@@ -3929,46 +4153,49 @@
       <c r="A75" s="1" t="n">
         <v>73</v>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B75" t="n">
+        <v>73</v>
+      </c>
+      <c r="C75" s="2" t="n">
         <v>45455.03658564815</v>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>0.116299645949425</v>
       </c>
-      <c r="F75" t="n">
+      <c r="G75" t="n">
         <v>80</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>1.176e-05</v>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
         <v>0.11652</v>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
         <v>0.116299645949425</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="M75" t="n">
+      <c r="N75" t="n">
         <v>80</v>
       </c>
     </row>
@@ -3976,46 +4203,49 @@
       <c r="A76" s="1" t="n">
         <v>74</v>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B76" t="n">
+        <v>74</v>
+      </c>
+      <c r="C76" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G76" t="n">
         <v>0.001252093</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>1.25e-06</v>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J76" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K76" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L76" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M76" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="M76" t="n">
+      <c r="N76" t="n">
         <v>0.001252093</v>
       </c>
     </row>
@@ -4023,46 +4253,49 @@
       <c r="A77" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="B77" s="2" t="n">
+      <c r="B77" t="n">
+        <v>75</v>
+      </c>
+      <c r="C77" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>0.127</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>1.25e-06</v>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="M77" t="n">
+      <c r="N77" t="n">
         <v>0.127</v>
       </c>
     </row>
@@ -4070,46 +4303,49 @@
       <c r="A78" s="1" t="n">
         <v>76</v>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B78" t="n">
+        <v>76</v>
+      </c>
+      <c r="C78" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F78" t="n">
+      <c r="G78" t="n">
         <v>0.0029577</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>2.96e-06</v>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J78" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K78" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L78" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M78" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="M78" t="n">
+      <c r="N78" t="n">
         <v>0.0029577</v>
       </c>
     </row>
@@ -4117,46 +4353,49 @@
       <c r="A79" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="B79" s="2" t="n">
+      <c r="B79" t="n">
+        <v>77</v>
+      </c>
+      <c r="C79" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>0.3</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>2.96e-06</v>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="K79" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="M79" t="n">
+      <c r="N79" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -4164,46 +4403,49 @@
       <c r="A80" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="B80" s="2" t="n">
+      <c r="B80" t="n">
+        <v>78</v>
+      </c>
+      <c r="C80" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F80" t="n">
+      <c r="G80" t="n">
         <v>0.002464749999999999</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>2.46e-06</v>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J80" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K80" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L80" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M80" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="M80" t="n">
+      <c r="N80" t="n">
         <v>0.002464749999999999</v>
       </c>
     </row>
@@ -4211,46 +4453,49 @@
       <c r="A81" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="B81" s="2" t="n">
+      <c r="B81" t="n">
+        <v>79</v>
+      </c>
+      <c r="C81" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="F81" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F81" t="n">
+      <c r="G81" t="n">
         <v>0.25</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>2.46e-06</v>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="M81" t="n">
+      <c r="N81" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -4258,46 +4503,49 @@
       <c r="A82" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="B82" s="2" t="n">
+      <c r="B82" t="n">
+        <v>80</v>
+      </c>
+      <c r="C82" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F82" t="n">
+      <c r="G82" t="n">
         <v>0.004929499999999999</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>0.000375</v>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J82" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K82" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L82" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M82" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="M82" t="n">
+      <c r="N82" t="n">
         <v>0.004929499999999999</v>
       </c>
     </row>
@@ -4305,46 +4553,49 @@
       <c r="A83" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="B83" s="2" t="n">
+      <c r="B83" t="n">
+        <v>81</v>
+      </c>
+      <c r="C83" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E83" t="n">
+      <c r="F83" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F83" t="n">
+      <c r="G83" t="n">
         <v>0.5</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>0.000375</v>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L83" t="n">
+      <c r="M83" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="M83" t="n">
+      <c r="N83" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4352,46 +4603,49 @@
       <c r="A84" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B84" t="n">
+        <v>82</v>
+      </c>
+      <c r="C84" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F84" t="n">
+      <c r="G84" t="n">
         <v>0.000808438</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>6.161e-05</v>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J84" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K84" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L84" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M84" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="M84" t="n">
+      <c r="N84" t="n">
         <v>0.000808438</v>
       </c>
     </row>
@@ -4399,46 +4653,49 @@
       <c r="A85" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="B85" s="2" t="n">
+      <c r="B85" t="n">
+        <v>83</v>
+      </c>
+      <c r="C85" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E85" t="n">
+      <c r="F85" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F85" t="n">
+      <c r="G85" t="n">
         <v>0.082</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>6.161e-05</v>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J85" t="n">
+      <c r="K85" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K85" t="n">
+      <c r="L85" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L85" t="n">
+      <c r="M85" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="M85" t="n">
+      <c r="N85" t="n">
         <v>0.082</v>
       </c>
     </row>
@@ -4446,46 +4703,49 @@
       <c r="A86" s="1" t="n">
         <v>84</v>
       </c>
-      <c r="B86" s="2" t="n">
+      <c r="B86" t="n">
+        <v>84</v>
+      </c>
+      <c r="C86" s="2" t="n">
         <v>45451.5195949074</v>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
         <v>683.8948187155901</v>
       </c>
-      <c r="F86" t="n">
+      <c r="G86" t="n">
         <v>1.121</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>766.6460917801764</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>0.00084075</v>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J86" t="n">
+      <c r="K86" t="n">
         <v>683.7183116666666</v>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" t="n">
         <v>683.8948187155901</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
         <v>766.6460917801764</v>
       </c>
-      <c r="M86" t="n">
+      <c r="N86" t="n">
         <v>1.121</v>
       </c>
     </row>
@@ -4493,46 +4753,49 @@
       <c r="A87" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="B87" s="2" t="n">
+      <c r="B87" t="n">
+        <v>85</v>
+      </c>
+      <c r="C87" s="2" t="n">
         <v>45451.5195949074</v>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E87" t="n">
+      <c r="F87" t="n">
         <v>69360.5292815</v>
       </c>
-      <c r="F87" t="n">
+      <c r="G87" t="n">
         <v>0.01105306</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>766.6460917801764</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>0.00084075</v>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J87" t="n">
-        <v>69360.5292815</v>
       </c>
       <c r="K87" t="n">
         <v>69360.5292815</v>
       </c>
       <c r="L87" t="n">
+        <v>69360.5292815</v>
+      </c>
+      <c r="M87" t="n">
         <v>766.6460917801763</v>
       </c>
-      <c r="M87" t="n">
+      <c r="N87" t="n">
         <v>0.01105306</v>
       </c>
     </row>
@@ -4540,46 +4803,49 @@
       <c r="A88" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="B88" s="2" t="n">
+      <c r="B88" t="n">
+        <v>86</v>
+      </c>
+      <c r="C88" s="2" t="n">
         <v>45451.50400462963</v>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E88" t="n">
+      <c r="F88" t="n">
         <v>681.2</v>
       </c>
-      <c r="F88" t="n">
+      <c r="G88" t="n">
         <v>0.015</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>10.218</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
         <v>1.124e-05</v>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="K88" t="n">
         <v>681.9633216666666</v>
       </c>
-      <c r="K88" t="n">
+      <c r="L88" t="n">
         <v>681.2</v>
       </c>
-      <c r="L88" t="n">
+      <c r="M88" t="n">
         <v>10.218</v>
       </c>
-      <c r="M88" t="n">
+      <c r="N88" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -4587,46 +4853,49 @@
       <c r="A89" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="B89" s="2" t="n">
+      <c r="B89" t="n">
+        <v>87</v>
+      </c>
+      <c r="C89" s="2" t="n">
         <v>45450.92207175926</v>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
         <v>0.041304</v>
       </c>
-      <c r="F89" t="n">
+      <c r="G89" t="n">
         <v>1210.5</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>49.998492</v>
       </c>
-      <c r="H89" t="n">
+      <c r="I89" t="n">
         <v>1.2105</v>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>JASMY</t>
         </is>
       </c>
-      <c r="J89" t="n">
+      <c r="K89" t="n">
         <v>0.04132561585</v>
       </c>
-      <c r="K89" t="n">
+      <c r="L89" t="n">
         <v>0.041304</v>
       </c>
-      <c r="L89" t="n">
+      <c r="M89" t="n">
         <v>49.998492</v>
       </c>
-      <c r="M89" t="n">
+      <c r="N89" t="n">
         <v>1210.5</v>
       </c>
     </row>
@@ -4634,46 +4903,49 @@
       <c r="A90" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="B90" s="2" t="n">
+      <c r="B90" t="n">
+        <v>88</v>
+      </c>
+      <c r="C90" s="2" t="n">
         <v>45450.92207175926</v>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
         <v>0.041305</v>
       </c>
-      <c r="F90" t="n">
+      <c r="G90" t="n">
         <v>1082.2</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>44.700271</v>
       </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
         <v>1.0822</v>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>JASMY</t>
         </is>
       </c>
-      <c r="J90" t="n">
+      <c r="K90" t="n">
         <v>0.04132561585</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
         <v>0.041305</v>
       </c>
-      <c r="L90" t="n">
+      <c r="M90" t="n">
         <v>44.700271</v>
       </c>
-      <c r="M90" t="n">
+      <c r="N90" t="n">
         <v>1082.2</v>
       </c>
     </row>
@@ -4681,46 +4953,49 @@
       <c r="A91" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="B91" s="2" t="n">
+      <c r="B91" t="n">
+        <v>89</v>
+      </c>
+      <c r="C91" s="2" t="n">
         <v>45450.92138888889</v>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>ENSUSDT</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E91" t="n">
+      <c r="F91" t="n">
         <v>21.97</v>
       </c>
-      <c r="F91" t="n">
+      <c r="G91" t="n">
         <v>2.01</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>44.1597</v>
       </c>
-      <c r="H91" t="n">
+      <c r="I91" t="n">
         <v>0.0441597</v>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J91" t="n">
+      <c r="K91" t="n">
         <v>21.95600116666667</v>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" t="n">
         <v>21.97</v>
       </c>
-      <c r="L91" t="n">
+      <c r="M91" t="n">
         <v>44.15969999999999</v>
       </c>
-      <c r="M91" t="n">
+      <c r="N91" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -4728,46 +5003,49 @@
       <c r="A92" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="B92" s="2" t="n">
+      <c r="B92" t="n">
+        <v>90</v>
+      </c>
+      <c r="C92" s="2" t="n">
         <v>45450.92039351852</v>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>ARUSDT</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E92" t="n">
+      <c r="F92" t="n">
         <v>39.245</v>
       </c>
-      <c r="F92" t="n">
+      <c r="G92" t="n">
         <v>1.3</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>51.0185</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>0.0510185</v>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J92" t="n">
+      <c r="K92" t="n">
         <v>39.20989994999999</v>
       </c>
-      <c r="K92" t="n">
+      <c r="L92" t="n">
         <v>39.245</v>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" t="n">
         <v>51.0185</v>
       </c>
-      <c r="M92" t="n">
+      <c r="N92" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -4775,46 +5053,49 @@
       <c r="A93" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="B93" s="2" t="n">
+      <c r="B93" t="n">
+        <v>91</v>
+      </c>
+      <c r="C93" s="2" t="n">
         <v>45447.9729050926</v>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
         <v>70502.70711650001</v>
       </c>
-      <c r="F93" t="n">
+      <c r="G93" t="n">
         <v>5.1689e-05</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="H93" t="n">
+      <c r="I93" t="n">
         <v>5e-08</v>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J93" t="n">
-        <v>70502.70711650001</v>
       </c>
       <c r="K93" t="n">
         <v>70502.70711650001</v>
       </c>
       <c r="L93" t="n">
+        <v>70502.70711650001</v>
+      </c>
+      <c r="M93" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="M93" t="n">
+      <c r="N93" t="n">
         <v>5.1689e-05</v>
       </c>
     </row>
@@ -4822,46 +5103,49 @@
       <c r="A94" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="B94" s="2" t="n">
+      <c r="B94" t="n">
+        <v>92</v>
+      </c>
+      <c r="C94" s="2" t="n">
         <v>45447.9729050926</v>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>UMAUSDT</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E94" t="n">
+      <c r="F94" t="n">
         <v>3.312922207404335</v>
       </c>
-      <c r="F94" t="n">
+      <c r="G94" t="n">
         <v>1.1</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="H94" t="n">
+      <c r="I94" t="n">
         <v>5e-08</v>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J94" t="n">
+      <c r="K94" t="n">
         <v>3.312983350000001</v>
       </c>
-      <c r="K94" t="n">
+      <c r="L94" t="n">
         <v>3.312922207404335</v>
       </c>
-      <c r="L94" t="n">
+      <c r="M94" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="M94" t="n">
+      <c r="N94" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -4869,46 +5153,49 @@
       <c r="A95" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="B95" s="2" t="n">
+      <c r="B95" t="n">
+        <v>93</v>
+      </c>
+      <c r="C95" s="2" t="n">
         <v>45447.94982638889</v>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
         <v>70534.99716683332</v>
       </c>
-      <c r="F95" t="n">
+      <c r="G95" t="n">
         <v>0.0002490470000000001</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>17.56652943940834</v>
       </c>
-      <c r="H95" t="n">
+      <c r="I95" t="n">
         <v>2.5e-07</v>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J95" t="n">
-        <v>70534.99716683332</v>
       </c>
       <c r="K95" t="n">
         <v>70534.99716683332</v>
       </c>
       <c r="L95" t="n">
+        <v>70534.99716683332</v>
+      </c>
+      <c r="M95" t="n">
         <v>17.56652943940835</v>
       </c>
-      <c r="M95" t="n">
+      <c r="N95" t="n">
         <v>0.0002490470000000001</v>
       </c>
     </row>
@@ -4916,46 +5203,49 @@
       <c r="A96" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="B96" s="2" t="n">
+      <c r="B96" t="n">
+        <v>94</v>
+      </c>
+      <c r="C96" s="2" t="n">
         <v>45447.94982638889</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>UMAUSDT</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E96" t="n">
+      <c r="F96" t="n">
         <v>3.314439516869498</v>
       </c>
-      <c r="F96" t="n">
+      <c r="G96" t="n">
         <v>5.3</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>17.56652943940834</v>
       </c>
-      <c r="H96" t="n">
+      <c r="I96" t="n">
         <v>2.5e-07</v>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J96" t="n">
+      <c r="K96" t="n">
         <v>3.311750016666666</v>
       </c>
-      <c r="K96" t="n">
+      <c r="L96" t="n">
         <v>3.314439516869498</v>
       </c>
-      <c r="L96" t="n">
+      <c r="M96" t="n">
         <v>17.56652943940834</v>
       </c>
-      <c r="M96" t="n">
+      <c r="N96" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -4963,46 +5253,49 @@
       <c r="A97" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="B97" s="2" t="n">
+      <c r="B97" t="n">
+        <v>95</v>
+      </c>
+      <c r="C97" s="2" t="n">
         <v>45446.50150462963</v>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>ETHUSDT</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
         <v>3810.458332166667</v>
       </c>
-      <c r="F97" t="n">
+      <c r="G97" t="n">
         <v>0.01363</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="H97" t="n">
+      <c r="I97" t="n">
         <v>1.363e-05</v>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
-      </c>
-      <c r="J97" t="n">
-        <v>3810.458332166667</v>
       </c>
       <c r="K97" t="n">
         <v>3810.458332166667</v>
       </c>
       <c r="L97" t="n">
+        <v>3810.458332166667</v>
+      </c>
+      <c r="M97" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="M97" t="n">
+      <c r="N97" t="n">
         <v>0.01363</v>
       </c>
     </row>
@@ -5010,46 +5303,49 @@
       <c r="A98" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="B98" s="2" t="n">
+      <c r="B98" t="n">
+        <v>96</v>
+      </c>
+      <c r="C98" s="2" t="n">
         <v>45446.50150462963</v>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>XRPUSDT</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E98" t="n">
+      <c r="F98" t="n">
         <v>0.5193654706743167</v>
       </c>
-      <c r="F98" t="n">
+      <c r="G98" t="n">
         <v>100</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="H98" t="n">
+      <c r="I98" t="n">
         <v>1.363e-05</v>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="J98" t="n">
+      <c r="K98" t="n">
         <v>0.5193833316666667</v>
       </c>
-      <c r="K98" t="n">
+      <c r="L98" t="n">
         <v>0.5193654706743167</v>
       </c>
-      <c r="L98" t="n">
+      <c r="M98" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="M98" t="n">
+      <c r="N98" t="n">
         <v>100</v>
       </c>
     </row>
@@ -5057,46 +5353,49 @@
       <c r="A99" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="B99" s="2" t="n">
+      <c r="B99" t="n">
+        <v>97</v>
+      </c>
+      <c r="C99" s="2" t="n">
         <v>45446.49649305556</v>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
         <v>69129.98950016667</v>
       </c>
-      <c r="F99" t="n">
+      <c r="G99" t="n">
         <v>0.00069092</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="H99" t="n">
+      <c r="I99" t="n">
         <v>6.9e-07</v>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J99" t="n">
-        <v>69129.98950016667</v>
       </c>
       <c r="K99" t="n">
         <v>69129.98950016667</v>
       </c>
       <c r="L99" t="n">
+        <v>69129.98950016667</v>
+      </c>
+      <c r="M99" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="M99" t="n">
+      <c r="N99" t="n">
         <v>0.00069092</v>
       </c>
     </row>
@@ -5104,46 +5403,49 @@
       <c r="A100" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="B100" s="2" t="n">
+      <c r="B100" t="n">
+        <v>98</v>
+      </c>
+      <c r="C100" s="2" t="n">
         <v>45446.49649305556</v>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>XRPUSDT</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E100" t="n">
+      <c r="F100" t="n">
         <v>0.5191662211462518</v>
       </c>
-      <c r="F100" t="n">
+      <c r="G100" t="n">
         <v>92</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="H100" t="n">
+      <c r="I100" t="n">
         <v>6.9e-07</v>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J100" t="n">
+      <c r="K100" t="n">
         <v>0.5193049983333333</v>
       </c>
-      <c r="K100" t="n">
+      <c r="L100" t="n">
         <v>0.5191662211462518</v>
       </c>
-      <c r="L100" t="n">
+      <c r="M100" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="M100" t="n">
+      <c r="N100" t="n">
         <v>92</v>
       </c>
     </row>
@@ -5151,46 +5453,49 @@
       <c r="A101" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="B101" s="2" t="n">
+      <c r="B101" t="n">
+        <v>99</v>
+      </c>
+      <c r="C101" s="2" t="n">
         <v>45446.42081018518</v>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
         <v>69115.08947183334</v>
       </c>
-      <c r="F101" t="n">
+      <c r="G101" t="n">
         <v>0.0006642089999999999</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="H101" t="n">
+      <c r="I101" t="n">
         <v>6.6e-07</v>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J101" t="n">
-        <v>69115.08947183334</v>
       </c>
       <c r="K101" t="n">
         <v>69115.08947183334</v>
       </c>
       <c r="L101" t="n">
+        <v>69115.08947183334</v>
+      </c>
+      <c r="M101" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="M101" t="n">
+      <c r="N101" t="n">
         <v>0.0006642089999999999</v>
       </c>
     </row>
@@ -5198,46 +5503,49 @@
       <c r="A102" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B102" s="2" t="n">
+      <c r="B102" t="n">
+        <v>100</v>
+      </c>
+      <c r="C102" s="2" t="n">
         <v>45446.42081018518</v>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>NEARUSDT</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E102" t="n">
+      <c r="F102" t="n">
         <v>7.28680388301539</v>
       </c>
-      <c r="F102" t="n">
+      <c r="G102" t="n">
         <v>6.3</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="H102" t="n">
+      <c r="I102" t="n">
         <v>6.6e-07</v>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J102" t="n">
+      <c r="K102" t="n">
         <v>7.287033316666666</v>
       </c>
-      <c r="K102" t="n">
+      <c r="L102" t="n">
         <v>7.28680388301539</v>
       </c>
-      <c r="L102" t="n">
+      <c r="M102" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="M102" t="n">
+      <c r="N102" t="n">
         <v>6.299999999999999</v>
       </c>
     </row>
@@ -5245,46 +5553,49 @@
       <c r="A103" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="B103" s="2" t="n">
+      <c r="B103" t="n">
+        <v>101</v>
+      </c>
+      <c r="C103" s="2" t="n">
         <v>45442.00921296296</v>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
         <v>67749.86920016666</v>
       </c>
-      <c r="F103" t="n">
+      <c r="G103" t="n">
         <v>0.00093258</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="H103" t="n">
+      <c r="I103" t="n">
         <v>9.3e-07</v>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J103" t="n">
-        <v>67749.86920016666</v>
       </c>
       <c r="K103" t="n">
         <v>67749.86920016666</v>
       </c>
       <c r="L103" t="n">
+        <v>67749.86920016666</v>
+      </c>
+      <c r="M103" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="M103" t="n">
+      <c r="N103" t="n">
         <v>0.00093258</v>
       </c>
     </row>
@@ -5292,46 +5603,49 @@
       <c r="A104" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="B104" s="2" t="n">
+      <c r="B104" t="n">
+        <v>102</v>
+      </c>
+      <c r="C104" s="2" t="n">
         <v>45442.00921296296</v>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>LPTUSDT</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E104" t="n">
+      <c r="F104" t="n">
         <v>21.27345892885233</v>
       </c>
-      <c r="F104" t="n">
+      <c r="G104" t="n">
         <v>2.97</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="H104" t="n">
+      <c r="I104" t="n">
         <v>9.3e-07</v>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J104" t="n">
+      <c r="K104" t="n">
         <v>21.26066758333333</v>
       </c>
-      <c r="K104" t="n">
+      <c r="L104" t="n">
         <v>21.27345892885233</v>
       </c>
-      <c r="L104" t="n">
+      <c r="M104" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="M104" t="n">
+      <c r="N104" t="n">
         <v>2.97</v>
       </c>
     </row>
@@ -5339,46 +5653,49 @@
       <c r="A105" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="B105" s="2" t="n">
+      <c r="B105" t="n">
+        <v>103</v>
+      </c>
+      <c r="C105" s="2" t="n">
         <v>45441.90847222223</v>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
         <v>67695.03782550001</v>
       </c>
-      <c r="F105" t="n">
+      <c r="G105" t="n">
         <v>0.0007335899999999999</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="H105" t="n">
+      <c r="I105" t="n">
         <v>7.3e-07</v>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J105" t="n">
-        <v>67695.03782550001</v>
       </c>
       <c r="K105" t="n">
         <v>67695.03782550001</v>
       </c>
       <c r="L105" t="n">
+        <v>67695.03782550001</v>
+      </c>
+      <c r="M105" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="M105" t="n">
+      <c r="N105" t="n">
         <v>0.0007335899999999999</v>
       </c>
     </row>
@@ -5386,46 +5703,49 @@
       <c r="A106" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B106" s="2" t="n">
+      <c r="B106" t="n">
+        <v>104</v>
+      </c>
+      <c r="C106" s="2" t="n">
         <v>45441.90847222223</v>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>NEARUSDT</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E106" t="n">
+      <c r="F106" t="n">
         <v>7.640061968985931</v>
       </c>
-      <c r="F106" t="n">
+      <c r="G106" t="n">
         <v>6.5</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="H106" t="n">
+      <c r="I106" t="n">
         <v>7.3e-07</v>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J106" t="n">
+      <c r="K106" t="n">
         <v>7.64060005</v>
       </c>
-      <c r="K106" t="n">
+      <c r="L106" t="n">
         <v>7.640061968985931</v>
       </c>
-      <c r="L106" t="n">
+      <c r="M106" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="M106" t="n">
+      <c r="N106" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -5433,46 +5753,49 @@
       <c r="A107" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="B107" s="2" t="n">
+      <c r="B107" t="n">
+        <v>105</v>
+      </c>
+      <c r="C107" s="2" t="n">
         <v>45440.88619212963</v>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
         <v>64131.08918148</v>
       </c>
-      <c r="F107" t="n">
+      <c r="G107" t="n">
         <v>0.00076406</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>50</v>
       </c>
-      <c r="H107" t="n">
+      <c r="I107" t="n">
         <v>1</v>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J107" t="n">
+      <c r="K107" t="n">
         <v>1.086388331666667</v>
       </c>
-      <c r="K107" t="n">
+      <c r="L107" t="n">
         <v>69671.26698383428</v>
       </c>
-      <c r="L107" t="n">
+      <c r="M107" t="n">
         <v>53.23302825166842</v>
       </c>
-      <c r="M107" t="n">
+      <c r="N107" t="n">
         <v>0.00076406</v>
       </c>
     </row>
@@ -5480,46 +5803,49 @@
       <c r="A108" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="B108" s="2" t="n">
+      <c r="B108" t="n">
+        <v>106</v>
+      </c>
+      <c r="C108" s="2" t="n">
         <v>45439.96682870371</v>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
         <v>69531.81351050001</v>
       </c>
-      <c r="F108" t="n">
+      <c r="G108" t="n">
         <v>0.0004004640000000001</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="H108" t="n">
+      <c r="I108" t="n">
         <v>4e-07</v>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J108" t="n">
-        <v>69531.81351050001</v>
       </c>
       <c r="K108" t="n">
         <v>69531.81351050001</v>
       </c>
       <c r="L108" t="n">
+        <v>69531.81351050001</v>
+      </c>
+      <c r="M108" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="M108" t="n">
+      <c r="N108" t="n">
         <v>0.0004004640000000001</v>
       </c>
     </row>
@@ -5527,46 +5853,49 @@
       <c r="A109" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="B109" s="2" t="n">
+      <c r="B109" t="n">
+        <v>107</v>
+      </c>
+      <c r="C109" s="2" t="n">
         <v>45439.96682870371</v>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>INJUSDT</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E109" t="n">
+      <c r="F109" t="n">
         <v>25.7823964496934</v>
       </c>
-      <c r="F109" t="n">
+      <c r="G109" t="n">
         <v>1.08</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="H109" t="n">
+      <c r="I109" t="n">
         <v>4e-07</v>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J109" t="n">
+      <c r="K109" t="n">
         <v>25.7770005</v>
       </c>
-      <c r="K109" t="n">
+      <c r="L109" t="n">
         <v>25.7823964496934</v>
       </c>
-      <c r="L109" t="n">
+      <c r="M109" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="M109" t="n">
+      <c r="N109" t="n">
         <v>1.08</v>
       </c>
     </row>
@@ -5574,46 +5903,49 @@
       <c r="A110" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="B110" s="2" t="n">
+      <c r="B110" t="n">
+        <v>108</v>
+      </c>
+      <c r="C110" s="2" t="n">
         <v>45439.96547453704</v>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
         <v>69520.8794125</v>
       </c>
-      <c r="F110" t="n">
+      <c r="G110" t="n">
         <v>0.000231</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="H110" t="n">
+      <c r="I110" t="n">
         <v>2.3e-07</v>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J110" t="n">
-        <v>69520.8794125</v>
       </c>
       <c r="K110" t="n">
         <v>69520.8794125</v>
       </c>
       <c r="L110" t="n">
+        <v>69520.8794125</v>
+      </c>
+      <c r="M110" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="M110" t="n">
+      <c r="N110" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -5621,46 +5953,49 @@
       <c r="A111" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B111" s="2" t="n">
+      <c r="B111" t="n">
+        <v>109</v>
+      </c>
+      <c r="C111" s="2" t="n">
         <v>45439.96547453704</v>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>FETUSDT</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E111" t="n">
+      <c r="F111" t="n">
         <v>2.2941890206125</v>
       </c>
-      <c r="F111" t="n">
+      <c r="G111" t="n">
         <v>7</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="H111" t="n">
+      <c r="I111" t="n">
         <v>2.3e-07</v>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J111" t="n">
+      <c r="K111" t="n">
         <v>2.2945667</v>
       </c>
-      <c r="K111" t="n">
+      <c r="L111" t="n">
         <v>2.2941890206125</v>
       </c>
-      <c r="L111" t="n">
+      <c r="M111" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="M111" t="n">
+      <c r="N111" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5668,46 +6003,49 @@
       <c r="A112" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="B112" s="2" t="n">
+      <c r="B112" t="n">
+        <v>110</v>
+      </c>
+      <c r="C112" s="2" t="n">
         <v>45438.41358796296</v>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
         <v>64764.05726993</v>
       </c>
-      <c r="F112" t="n">
+      <c r="G112" t="n">
         <v>0.00302637</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>200</v>
       </c>
-      <c r="H112" t="n">
+      <c r="I112" t="n">
         <v>4</v>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J112" t="n">
+      <c r="K112" t="n">
         <v>1.084943331666667</v>
       </c>
-      <c r="K112" t="n">
+      <c r="L112" t="n">
         <v>70265.33206668869</v>
       </c>
-      <c r="L112" t="n">
+      <c r="M112" t="n">
         <v>212.6488930066647</v>
       </c>
-      <c r="M112" t="n">
+      <c r="N112" t="n">
         <v>0.00302637</v>
       </c>
     </row>
@@ -5715,46 +6053,49 @@
       <c r="A113" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="B113" s="2" t="n">
+      <c r="B113" t="n">
+        <v>111</v>
+      </c>
+      <c r="C113" s="2" t="n">
         <v>45438.06670138889</v>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>ENSEUR</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
         <v>21.88048003</v>
       </c>
-      <c r="F113" t="n">
+      <c r="G113" t="n">
         <v>3.35870145</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>75</v>
       </c>
-      <c r="H113" t="n">
+      <c r="I113" t="n">
         <v>1</v>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J113" t="n">
+      <c r="K113" t="n">
         <v>1.084505001666667</v>
       </c>
-      <c r="K113" t="n">
+      <c r="L113" t="n">
         <v>23.72949003140263</v>
       </c>
-      <c r="L113" t="n">
+      <c r="M113" t="n">
         <v>79.70027257623255</v>
       </c>
-      <c r="M113" t="n">
+      <c r="N113" t="n">
         <v>3.35870145</v>
       </c>
     </row>
@@ -5762,46 +6103,49 @@
       <c r="A114" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="B114" s="2" t="n">
+      <c r="B114" t="n">
+        <v>112</v>
+      </c>
+      <c r="C114" s="2" t="n">
         <v>45438.06428240741</v>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>LPTEUR</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
         <v>21.40068094</v>
       </c>
-      <c r="F114" t="n">
+      <c r="G114" t="n">
         <v>4.57929354</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>100</v>
       </c>
-      <c r="H114" t="n">
+      <c r="I114" t="n">
         <v>2</v>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J114" t="n">
+      <c r="K114" t="n">
         <v>1.084456668333333</v>
       </c>
-      <c r="K114" t="n">
+      <c r="L114" t="n">
         <v>23.20811115225706</v>
       </c>
-      <c r="L114" t="n">
+      <c r="M114" t="n">
         <v>106.2767534751327</v>
       </c>
-      <c r="M114" t="n">
+      <c r="N114" t="n">
         <v>4.57929354</v>
       </c>
     </row>
@@ -5809,46 +6153,49 @@
       <c r="A115" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="B115" s="2" t="n">
+      <c r="B115" t="n">
+        <v>113</v>
+      </c>
+      <c r="C115" s="2" t="n">
         <v>45438.06288194445</v>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>JASMYEUR</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
         <v>0.02039718</v>
       </c>
-      <c r="F115" t="n">
+      <c r="G115" t="n">
         <v>4804.58606935</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>100</v>
       </c>
-      <c r="H115" t="n">
+      <c r="I115" t="n">
         <v>2</v>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J115" t="n">
+      <c r="K115" t="n">
         <v>1.084644998333333</v>
       </c>
-      <c r="K115" t="n">
+      <c r="L115" t="n">
         <v>0.0221236992671047</v>
       </c>
-      <c r="L115" t="n">
+      <c r="M115" t="n">
         <v>106.29521730122</v>
       </c>
-      <c r="M115" t="n">
+      <c r="N115" t="n">
         <v>4804.58606935</v>
       </c>
     </row>
@@ -5856,46 +6203,49 @@
       <c r="A116" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="B116" s="2" t="n">
+      <c r="B116" t="n">
+        <v>114</v>
+      </c>
+      <c r="C116" s="2" t="n">
         <v>45438.01670138889</v>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>BBEUR</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
         <v>0.5091575699999999</v>
       </c>
-      <c r="F116" t="n">
+      <c r="G116" t="n">
         <v>288.7121952</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>150</v>
       </c>
-      <c r="H116" t="n">
+      <c r="I116" t="n">
         <v>3</v>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J116" t="n">
+      <c r="K116" t="n">
         <v>1.084505001666667</v>
       </c>
-      <c r="K116" t="n">
+      <c r="L116" t="n">
         <v>0.5521839313014461</v>
       </c>
-      <c r="L116" t="n">
+      <c r="M116" t="n">
         <v>159.4222349602065</v>
       </c>
-      <c r="M116" t="n">
+      <c r="N116" t="n">
         <v>288.7121952</v>
       </c>
     </row>
@@ -5903,46 +6253,49 @@
       <c r="A117" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="B117" s="2" t="n">
+      <c r="B117" t="n">
+        <v>115</v>
+      </c>
+      <c r="C117" s="2" t="n">
         <v>45438.01179398148</v>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>XRPEUR</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
         <v>0.50817649</v>
       </c>
-      <c r="F117" t="n">
+      <c r="G117" t="n">
         <v>192.84638819</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>100</v>
       </c>
-      <c r="H117" t="n">
+      <c r="I117" t="n">
         <v>2</v>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J117" t="n">
+      <c r="K117" t="n">
         <v>1.0845</v>
       </c>
-      <c r="K117" t="n">
+      <c r="L117" t="n">
         <v>0.551117403405</v>
       </c>
-      <c r="L117" t="n">
+      <c r="M117" t="n">
         <v>106.2810007153055</v>
       </c>
-      <c r="M117" t="n">
+      <c r="N117" t="n">
         <v>192.84638819</v>
       </c>
     </row>
@@ -5950,46 +6303,49 @@
       <c r="A118" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="B118" s="2" t="n">
+      <c r="B118" t="n">
+        <v>116</v>
+      </c>
+      <c r="C118" s="2" t="n">
         <v>45437.93450231481</v>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>PEPEEUR</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
         <v>1.414e-05</v>
       </c>
-      <c r="F118" t="n">
+      <c r="G118" t="n">
         <v>6928298.24</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>100</v>
       </c>
-      <c r="H118" t="n">
+      <c r="I118" t="n">
         <v>2</v>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J118" t="n">
+      <c r="K118" t="n">
         <v>1.0845</v>
       </c>
-      <c r="K118" t="n">
+      <c r="L118" t="n">
         <v>1.533483e-05</v>
       </c>
-      <c r="L118" t="n">
+      <c r="M118" t="n">
         <v>106.2442756996992</v>
       </c>
-      <c r="M118" t="n">
+      <c r="N118" t="n">
         <v>6928298.24</v>
       </c>
     </row>
@@ -5997,46 +6353,49 @@
       <c r="A119" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="B119" s="2" t="n">
+      <c r="B119" t="n">
+        <v>117</v>
+      </c>
+      <c r="C119" s="2" t="n">
         <v>45437.92731481481</v>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>NEAREUR</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
         <v>7.62742061</v>
       </c>
-      <c r="F119" t="n">
+      <c r="G119" t="n">
         <v>12.8483802</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>100</v>
       </c>
-      <c r="H119" t="n">
+      <c r="I119" t="n">
         <v>2</v>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J119" t="n">
+      <c r="K119" t="n">
         <v>1.0846</v>
       </c>
-      <c r="K119" t="n">
+      <c r="L119" t="n">
         <v>8.272700393606</v>
       </c>
-      <c r="L119" t="n">
+      <c r="M119" t="n">
         <v>106.2907999377395</v>
       </c>
-      <c r="M119" t="n">
+      <c r="N119" t="n">
         <v>12.8483802</v>
       </c>
     </row>
@@ -6044,46 +6403,49 @@
       <c r="A120" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="B120" s="2" t="n">
+      <c r="B120" t="n">
+        <v>118</v>
+      </c>
+      <c r="C120" s="2" t="n">
         <v>45436.94775462963</v>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>MKREUR</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
         <v>2571.01241222</v>
       </c>
-      <c r="F120" t="n">
+      <c r="G120" t="n">
         <v>0.03811728</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>100</v>
       </c>
-      <c r="H120" t="n">
+      <c r="I120" t="n">
         <v>2</v>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J120" t="n">
+      <c r="K120" t="n">
         <v>1.084</v>
       </c>
-      <c r="K120" t="n">
+      <c r="L120" t="n">
         <v>2786.97745484648</v>
       </c>
-      <c r="L120" t="n">
+      <c r="M120" t="n">
         <v>106.2320000000707</v>
       </c>
-      <c r="M120" t="n">
+      <c r="N120" t="n">
         <v>0.03811728</v>
       </c>
     </row>
@@ -6091,46 +6453,49 @@
       <c r="A121" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="B121" s="2" t="n">
+      <c r="B121" t="n">
+        <v>119</v>
+      </c>
+      <c r="C121" s="2" t="n">
         <v>45436.93561342593</v>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>ETHEUR</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
         <v>3502.04619556</v>
       </c>
-      <c r="F121" t="n">
+      <c r="G121" t="n">
         <v>0.04197546</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>150</v>
       </c>
-      <c r="H121" t="n">
+      <c r="I121" t="n">
         <v>3</v>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J121" t="n">
+      <c r="K121" t="n">
         <v>1.084</v>
       </c>
-      <c r="K121" t="n">
+      <c r="L121" t="n">
         <v>3796.21807598704</v>
       </c>
-      <c r="L121" t="n">
+      <c r="M121" t="n">
         <v>159.347999999871</v>
       </c>
-      <c r="M121" t="n">
+      <c r="N121" t="n">
         <v>0.04197546</v>
       </c>
     </row>
@@ -6138,46 +6503,49 @@
       <c r="A122" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="B122" s="2" t="n">
+      <c r="B122" t="n">
+        <v>120</v>
+      </c>
+      <c r="C122" s="2" t="n">
         <v>45436.93466435185</v>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E122" t="n">
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
         <v>157.11043262</v>
       </c>
-      <c r="F122" t="n">
+      <c r="G122" t="n">
         <v>0.62376507</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>100</v>
       </c>
-      <c r="H122" t="n">
+      <c r="I122" t="n">
         <v>2</v>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="J122" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J122" t="n">
+      <c r="K122" t="n">
         <v>1.084108331666667</v>
       </c>
-      <c r="K122" t="n">
+      <c r="L122" t="n">
         <v>170.3247289950965</v>
       </c>
-      <c r="L122" t="n">
+      <c r="M122" t="n">
         <v>106.2426165043574</v>
       </c>
-      <c r="M122" t="n">
+      <c r="N122" t="n">
         <v>0.62376507</v>
       </c>
     </row>
@@ -6185,46 +6553,49 @@
       <c r="A123" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="B123" s="2" t="n">
+      <c r="B123" t="n">
+        <v>121</v>
+      </c>
+      <c r="C123" s="2" t="n">
         <v>45436.43322916667</v>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
         <v>63003.06014864</v>
       </c>
-      <c r="F123" t="n">
+      <c r="G123" t="n">
         <v>0.00155548</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>100</v>
       </c>
-      <c r="H123" t="n">
+      <c r="I123" t="n">
         <v>2</v>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="J123" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J123" t="n">
+      <c r="K123" t="n">
         <v>1.0829</v>
       </c>
-      <c r="K123" t="n">
+      <c r="L123" t="n">
         <v>68226.01383496226</v>
       </c>
-      <c r="L123" t="n">
+      <c r="M123" t="n">
         <v>106.1242000000071</v>
       </c>
-      <c r="M123" t="n">
+      <c r="N123" t="n">
         <v>0.00155548</v>
       </c>
     </row>
@@ -6232,46 +6603,49 @@
       <c r="A124" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="B124" s="2" t="n">
+      <c r="B124" t="n">
+        <v>122</v>
+      </c>
+      <c r="C124" s="2" t="n">
         <v>45426.64160879629</v>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
         <v>57930.57788707</v>
       </c>
-      <c r="F124" t="n">
+      <c r="G124" t="n">
         <v>0.00084584</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>50</v>
       </c>
-      <c r="H124" t="n">
+      <c r="I124" t="n">
         <v>1</v>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="J124" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J124" t="n">
+      <c r="K124" t="n">
         <v>1.0814</v>
       </c>
-      <c r="K124" t="n">
+      <c r="L124" t="n">
         <v>62646.12692707749</v>
       </c>
-      <c r="L124" t="n">
+      <c r="M124" t="n">
         <v>52.98859999999923</v>
       </c>
-      <c r="M124" t="n">
+      <c r="N124" t="n">
         <v>0.00084584</v>
       </c>
     </row>
@@ -6279,46 +6653,49 @@
       <c r="A125" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="B125" s="2" t="n">
+      <c r="B125" t="n">
+        <v>123</v>
+      </c>
+      <c r="C125" s="2" t="n">
         <v>45425.85847222222</v>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
         <v>140.23996862</v>
       </c>
-      <c r="F125" t="n">
+      <c r="G125" t="n">
         <v>0.69880221</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>100</v>
       </c>
-      <c r="H125" t="n">
+      <c r="I125" t="n">
         <v>2</v>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="J125" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J125" t="n">
+      <c r="K125" t="n">
         <v>1.078779998333333</v>
       </c>
-      <c r="K125" t="n">
+      <c r="L125" t="n">
         <v>151.2880731141503</v>
       </c>
-      <c r="L125" t="n">
+      <c r="M125" t="n">
         <v>105.7204398388098</v>
       </c>
-      <c r="M125" t="n">
+      <c r="N125" t="n">
         <v>0.69880221</v>
       </c>
     </row>
@@ -6326,46 +6703,49 @@
       <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="B126" s="2" t="n">
+      <c r="B126" t="n">
+        <v>124</v>
+      </c>
+      <c r="C126" s="2" t="n">
         <v>45422.83993055556</v>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>RNDREUR</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
         <v>10.58084967</v>
       </c>
-      <c r="F126" t="n">
+      <c r="G126" t="n">
         <v>1.85240322</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>20</v>
       </c>
-      <c r="H126" t="n">
+      <c r="I126" t="n">
         <v>0.4</v>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="J126" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J126" t="n">
+      <c r="K126" t="n">
         <v>1.076449998333333</v>
       </c>
-      <c r="K126" t="n">
+      <c r="L126" t="n">
         <v>11.38975560963675</v>
       </c>
-      <c r="L126" t="n">
+      <c r="M126" t="n">
         <v>21.09841996630417</v>
       </c>
-      <c r="M126" t="n">
+      <c r="N126" t="n">
         <v>1.85240322</v>
       </c>
     </row>
@@ -6373,46 +6753,49 @@
       <c r="A127" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="B127" s="2" t="n">
+      <c r="B127" t="n">
+        <v>125</v>
+      </c>
+      <c r="C127" s="2" t="n">
         <v>45422.83865740741</v>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>ETHEUR</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
         <v>2752.33311287</v>
       </c>
-      <c r="F127" t="n">
+      <c r="G127" t="n">
         <v>0.00533729</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>15</v>
       </c>
-      <c r="H127" t="n">
+      <c r="I127" t="n">
         <v>0.31</v>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="J127" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J127" t="n">
+      <c r="K127" t="n">
         <v>1.0764</v>
       </c>
-      <c r="K127" t="n">
+      <c r="L127" t="n">
         <v>2962.611362693268</v>
       </c>
-      <c r="L127" t="n">
+      <c r="M127" t="n">
         <v>15.81231599998915</v>
       </c>
-      <c r="M127" t="n">
+      <c r="N127" t="n">
         <v>0.00533729</v>
       </c>
     </row>
@@ -6420,46 +6803,49 @@
       <c r="A128" s="1" t="n">
         <v>126</v>
       </c>
-      <c r="B128" s="2" t="n">
+      <c r="B128" t="n">
+        <v>126</v>
+      </c>
+      <c r="C128" s="2" t="n">
         <v>45422.83754629629</v>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
         <v>57425.23976014</v>
       </c>
-      <c r="F128" t="n">
+      <c r="G128" t="n">
         <v>0.00051197</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>30</v>
       </c>
-      <c r="H128" t="n">
+      <c r="I128" t="n">
         <v>0.6</v>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="J128" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J128" t="n">
+      <c r="K128" t="n">
         <v>1.0764</v>
       </c>
-      <c r="K128" t="n">
+      <c r="L128" t="n">
         <v>61812.5280778147</v>
       </c>
-      <c r="L128" t="n">
+      <c r="M128" t="n">
         <v>31.64615999999879</v>
       </c>
-      <c r="M128" t="n">
+      <c r="N128" t="n">
         <v>0.00051197</v>
       </c>
     </row>
@@ -6467,46 +6853,49 @@
       <c r="A129" s="1" t="n">
         <v>127</v>
       </c>
-      <c r="B129" s="2" t="n">
+      <c r="B129" t="n">
+        <v>127</v>
+      </c>
+      <c r="C129" s="2" t="n">
         <v>45422.83584490741</v>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>FETEUR</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
         <v>2.10457801</v>
       </c>
-      <c r="F129" t="n">
+      <c r="G129" t="n">
         <v>6.98002161</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>15</v>
       </c>
-      <c r="H129" t="n">
+      <c r="I129" t="n">
         <v>0.31</v>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J129" t="n">
+      <c r="K129" t="n">
         <v>1.076438331666667</v>
       </c>
-      <c r="K129" t="n">
+      <c r="L129" t="n">
         <v>2.265448441946754</v>
       </c>
-      <c r="L129" t="n">
+      <c r="M129" t="n">
         <v>15.81287908112917</v>
       </c>
-      <c r="M129" t="n">
+      <c r="N129" t="n">
         <v>6.98002161</v>
       </c>
     </row>
@@ -6514,46 +6903,49 @@
       <c r="A130" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="B130" s="2" t="n">
+      <c r="B130" t="n">
+        <v>128</v>
+      </c>
+      <c r="C130" s="2" t="n">
         <v>45422.83362268518</v>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>TRXEUR</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
         <v>0.1200639</v>
       </c>
-      <c r="F130" t="n">
+      <c r="G130" t="n">
         <v>163.24640485</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>20</v>
       </c>
-      <c r="H130" t="n">
+      <c r="I130" t="n">
         <v>0.4</v>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="J130" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J130" t="n">
+      <c r="K130" t="n">
         <v>1.0763</v>
       </c>
-      <c r="K130" t="n">
+      <c r="L130" t="n">
         <v>0.12922477557</v>
       </c>
-      <c r="L130" t="n">
+      <c r="M130" t="n">
         <v>21.09548002935061</v>
       </c>
-      <c r="M130" t="n">
+      <c r="N130" t="n">
         <v>163.24640485</v>
       </c>
     </row>
@@ -6561,46 +6953,49 @@
       <c r="A131" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="B131" s="2" t="n">
+      <c r="B131" t="n">
+        <v>129</v>
+      </c>
+      <c r="C131" s="2" t="n">
         <v>45422.83130787037</v>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
         <v>140.17980062</v>
       </c>
-      <c r="F131" t="n">
+      <c r="G131" t="n">
         <v>0.13982043</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>20</v>
       </c>
-      <c r="H131" t="n">
+      <c r="I131" t="n">
         <v>0.4</v>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="J131" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J131" t="n">
+      <c r="K131" t="n">
         <v>1.076308335</v>
       </c>
-      <c r="K131" t="n">
+      <c r="L131" t="n">
         <v>150.8766878059442</v>
       </c>
-      <c r="L131" t="n">
+      <c r="M131" t="n">
         <v>21.09564336600287</v>
       </c>
-      <c r="M131" t="n">
+      <c r="N131" t="n">
         <v>0.13982043</v>
       </c>
     </row>
@@ -6608,46 +7003,49 @@
       <c r="A132" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="B132" s="2" t="n">
+      <c r="B132" t="n">
+        <v>130</v>
+      </c>
+      <c r="C132" s="2" t="n">
         <v>45422.82967592592</v>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>TNSREUR</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
         <v>0.79988478</v>
       </c>
-      <c r="F132" t="n">
+      <c r="G132" t="n">
         <v>18.36514507</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>15</v>
       </c>
-      <c r="H132" t="n">
+      <c r="I132" t="n">
         <v>0.31</v>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="J132" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J132" t="n">
+      <c r="K132" t="n">
         <v>1.076426665</v>
       </c>
-      <c r="K132" t="n">
+      <c r="L132" t="n">
         <v>0.8610173061196587</v>
       </c>
-      <c r="L132" t="n">
+      <c r="M132" t="n">
         <v>15.81270773466813</v>
       </c>
-      <c r="M132" t="n">
+      <c r="N132" t="n">
         <v>18.36514507</v>
       </c>
     </row>
@@ -6655,46 +7053,49 @@
       <c r="A133" s="1" t="n">
         <v>131</v>
       </c>
-      <c r="B133" s="2" t="n">
+      <c r="B133" t="n">
+        <v>131</v>
+      </c>
+      <c r="C133" s="2" t="n">
         <v>45422.08221064815</v>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
         <v>143.75063899</v>
       </c>
-      <c r="F133" t="n">
+      <c r="G133" t="n">
         <v>0.13634722</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>20</v>
       </c>
-      <c r="H133" t="n">
+      <c r="I133" t="n">
         <v>0.4</v>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="J133" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J133" t="n">
+      <c r="K133" t="n">
         <v>1.077761665</v>
       </c>
-      <c r="K133" t="n">
+      <c r="L133" t="n">
         <v>154.9289280226763</v>
       </c>
-      <c r="L133" t="n">
+      <c r="M133" t="n">
         <v>21.12412863347201</v>
       </c>
-      <c r="M133" t="n">
+      <c r="N133" t="n">
         <v>0.13634722</v>
       </c>
     </row>
@@ -6702,46 +7103,49 @@
       <c r="A134" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="B134" s="2" t="n">
+      <c r="B134" t="n">
+        <v>132</v>
+      </c>
+      <c r="C134" s="2" t="n">
         <v>45422.07099537037</v>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>USDTEUR</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
         <v>0.93873598</v>
       </c>
-      <c r="F134" t="n">
+      <c r="G134" t="n">
         <v>26.08827246</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>25</v>
       </c>
-      <c r="H134" t="n">
+      <c r="I134" t="n">
         <v>0.51</v>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="J134" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J134" t="n">
+      <c r="K134" t="n">
         <v>1.0778</v>
       </c>
-      <c r="K134" t="n">
+      <c r="L134" t="n">
         <v>1.011769639244</v>
       </c>
-      <c r="L134" t="n">
+      <c r="M134" t="n">
         <v>26.39532201535338</v>
       </c>
-      <c r="M134" t="n">
+      <c r="N134" t="n">
         <v>26.08827246</v>
       </c>
     </row>
@@ -6749,46 +7153,49 @@
       <c r="A135" s="1" t="n">
         <v>133</v>
       </c>
-      <c r="B135" s="2" t="n">
+      <c r="B135" t="n">
+        <v>133</v>
+      </c>
+      <c r="C135" s="2" t="n">
         <v>45422.06987268518</v>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>MKREUR</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E135" t="n">
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
         <v>2583.15065304</v>
       </c>
-      <c r="F135" t="n">
+      <c r="G135" t="n">
         <v>0.00682887</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>18</v>
       </c>
-      <c r="H135" t="n">
+      <c r="I135" t="n">
         <v>0.36</v>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="J135" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J135" t="n">
+      <c r="K135" t="n">
         <v>1.077938331666667</v>
       </c>
-      <c r="K135" t="n">
+      <c r="L135" t="n">
         <v>2784.477105381599</v>
       </c>
-      <c r="L135" t="n">
+      <c r="M135" t="n">
         <v>19.01483217062724</v>
       </c>
-      <c r="M135" t="n">
+      <c r="N135" t="n">
         <v>0.006828869999999999</v>
       </c>
     </row>
@@ -6796,46 +7203,49 @@
       <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="B136" s="2" t="n">
+      <c r="B136" t="n">
+        <v>134</v>
+      </c>
+      <c r="C136" s="2" t="n">
         <v>45422.05619212963</v>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>FETEUR</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E136" t="n">
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
         <v>2.1432031</v>
       </c>
-      <c r="F136" t="n">
+      <c r="G136" t="n">
         <v>11.42682187</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>25</v>
       </c>
-      <c r="H136" t="n">
+      <c r="I136" t="n">
         <v>0.51</v>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="J136" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J136" t="n">
+      <c r="K136" t="n">
         <v>1.077691668333334</v>
       </c>
-      <c r="K136" t="n">
+      <c r="L136" t="n">
         <v>2.309712124416173</v>
       </c>
-      <c r="L136" t="n">
+      <c r="M136" t="n">
         <v>26.39266901668289</v>
       </c>
-      <c r="M136" t="n">
+      <c r="N136" t="n">
         <v>11.42682187</v>
       </c>
     </row>
@@ -6843,46 +7253,49 @@
       <c r="A137" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="B137" s="2" t="n">
+      <c r="B137" t="n">
+        <v>135</v>
+      </c>
+      <c r="C137" s="2" t="n">
         <v>45422.01804398148</v>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>RNDREUR</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
         <v>10.23426316</v>
       </c>
-      <c r="F137" t="n">
+      <c r="G137" t="n">
         <v>2.39294218</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>25</v>
       </c>
-      <c r="H137" t="n">
+      <c r="I137" t="n">
         <v>0.51</v>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J137" t="n">
+      <c r="K137" t="n">
         <v>1.077698335</v>
       </c>
-      <c r="K137" t="n">
+      <c r="L137" t="n">
         <v>11.02944836748384</v>
       </c>
-      <c r="L137" t="n">
+      <c r="M137" t="n">
         <v>26.39283222068422</v>
       </c>
-      <c r="M137" t="n">
+      <c r="N137" t="n">
         <v>2.39294218</v>
       </c>
     </row>
@@ -6890,46 +7303,49 @@
       <c r="A138" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="B138" s="2" t="n">
+      <c r="B138" t="n">
+        <v>136</v>
+      </c>
+      <c r="C138" s="2" t="n">
         <v>45421.93954861111</v>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>TRXEUR</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
         <v>0.11898276</v>
       </c>
-      <c r="F138" t="n">
+      <c r="G138" t="n">
         <v>205.82814242</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>25</v>
       </c>
-      <c r="H138" t="n">
+      <c r="I138" t="n">
         <v>0.51</v>
       </c>
-      <c r="I138" t="inlineStr">
+      <c r="J138" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J138" t="n">
+      <c r="K138" t="n">
         <v>1.077904998333333</v>
       </c>
-      <c r="K138" t="n">
+      <c r="L138" t="n">
         <v>0.1282521117194954</v>
       </c>
-      <c r="L138" t="n">
+      <c r="M138" t="n">
         <v>26.39789391666605</v>
       </c>
-      <c r="M138" t="n">
+      <c r="N138" t="n">
         <v>205.82814242</v>
       </c>
     </row>
@@ -6937,46 +7353,49 @@
       <c r="A139" s="1" t="n">
         <v>137</v>
       </c>
-      <c r="B139" s="2" t="n">
+      <c r="B139" t="n">
+        <v>137</v>
+      </c>
+      <c r="C139" s="2" t="n">
         <v>45421.81724537037</v>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>UMAEUR</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
         <v>3.80349912</v>
       </c>
-      <c r="F139" t="n">
+      <c r="G139" t="n">
         <v>6.43880785</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>25</v>
       </c>
-      <c r="H139" t="n">
+      <c r="I139" t="n">
         <v>0.51</v>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="J139" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J139" t="n">
+      <c r="K139" t="n">
         <v>1.077516665</v>
       </c>
-      <c r="K139" t="n">
+      <c r="L139" t="n">
         <v>4.098333687112835</v>
       </c>
-      <c r="L139" t="n">
+      <c r="M139" t="n">
         <v>26.38838311650157</v>
       </c>
-      <c r="M139" t="n">
+      <c r="N139" t="n">
         <v>6.43880785</v>
       </c>
     </row>
@@ -6984,46 +7403,49 @@
       <c r="A140" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="B140" s="2" t="n">
+      <c r="B140" t="n">
+        <v>138</v>
+      </c>
+      <c r="C140" s="2" t="n">
         <v>45418.97721064815</v>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>ETHEUR</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
         <v>2912.26895648</v>
       </c>
-      <c r="F140" t="n">
+      <c r="G140" t="n">
         <v>0.00840723</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>25</v>
       </c>
-      <c r="H140" t="n">
+      <c r="I140" t="n">
         <v>0.51</v>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="J140" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J140" t="n">
+      <c r="K140" t="n">
         <v>1.076</v>
       </c>
-      <c r="K140" t="n">
+      <c r="L140" t="n">
         <v>3133.60139717248</v>
       </c>
-      <c r="L140" t="n">
+      <c r="M140" t="n">
         <v>26.34490767435039</v>
       </c>
-      <c r="M140" t="n">
+      <c r="N140" t="n">
         <v>0.00840723</v>
       </c>
     </row>
@@ -7031,46 +7453,49 @@
       <c r="A141" s="1" t="n">
         <v>139</v>
       </c>
-      <c r="B141" s="2" t="n">
+      <c r="B141" t="n">
+        <v>139</v>
+      </c>
+      <c r="C141" s="2" t="n">
         <v>45418.96918981482</v>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
         <v>59899.71272325</v>
       </c>
-      <c r="F141" t="n">
+      <c r="G141" t="n">
         <v>0.00040885</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>25</v>
       </c>
-      <c r="H141" t="n">
+      <c r="I141" t="n">
         <v>0.51</v>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="J141" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J141" t="n">
+      <c r="K141" t="n">
         <v>1.0761</v>
       </c>
-      <c r="K141" t="n">
+      <c r="L141" t="n">
         <v>64458.08086148932</v>
       </c>
-      <c r="L141" t="n">
+      <c r="M141" t="n">
         <v>26.35368636021991</v>
       </c>
-      <c r="M141" t="n">
+      <c r="N141" t="n">
         <v>0.00040885</v>
       </c>
     </row>
@@ -7078,46 +7503,49 @@
       <c r="A142" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="B142" s="2" t="n">
+      <c r="B142" t="n">
+        <v>140</v>
+      </c>
+      <c r="C142" s="2" t="n">
         <v>45414.95027777777</v>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
         <v>131.18665751</v>
       </c>
-      <c r="F142" t="n">
+      <c r="G142" t="n">
         <v>0.18668057</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>25</v>
       </c>
-      <c r="H142" t="n">
+      <c r="I142" t="n">
         <v>0.51</v>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="J142" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J142" t="n">
+      <c r="K142" t="n">
         <v>1.070940001666667</v>
       </c>
-      <c r="K142" t="n">
+      <c r="L142" t="n">
         <v>140.4930392124039</v>
       </c>
-      <c r="L142" t="n">
+      <c r="M142" t="n">
         <v>26.22732064120391</v>
       </c>
-      <c r="M142" t="n">
+      <c r="N142" t="n">
         <v>0.18668057</v>
       </c>
     </row>

--- a/Trade History Reconstructed.xlsx
+++ b/Trade History Reconstructed.xlsx
@@ -429,71 +429,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N142"/>
+  <dimension ref="A1:O142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Date(UTC)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Fee Coin</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Pair Price</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Price in USDT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Total in USDT</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Pair Quantity</t>
         </is>
@@ -506,46 +511,49 @@
       <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>46081.50087962963</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>0.2791</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1702.7</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>475.22357</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1.617565</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.2792733316666667</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.2791</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>475.2235700000001</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1702.7</v>
       </c>
     </row>
@@ -556,46 +564,49 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>46081.50046296296</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>63986.13</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.00046</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>29.4336198</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>3.528e-05</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>63900.73367266667</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>63986.13</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>29.4336198</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>0.00046</v>
       </c>
     </row>
@@ -606,46 +617,49 @@
       <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>46081.5003125</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>594.34</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>0.75</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>445.755</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.0005343</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>594.6545034999999</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>594.34</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>445.755</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -656,46 +670,49 @@
       <c r="B5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>46054.61652777778</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>770.6900000000001</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.636</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>490.15884</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.00045314</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>753.2940488333334</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>770.6900000000001</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>490.1588400000001</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>0.636</v>
       </c>
     </row>
@@ -706,46 +723,49 @@
       <c r="B6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>46054.61582175926</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>78597.2</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.00114</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>89.600808</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>8.284e-05</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>77971.77212000001</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>78597.2</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>89.60080799999999</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>0.00114</v>
       </c>
     </row>
@@ -756,46 +776,49 @@
       <c r="B7" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>46054.61512731481</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.2859</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1399</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>399.9741</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.00036997</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.285821665</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.2859</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>399.9741</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>1399</v>
       </c>
     </row>
@@ -806,46 +829,49 @@
       <c r="B8" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>46023.11693287037</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>869.59</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>0.083</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>72.17597000000001</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>5.913e-05</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>871.1663310000001</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>869.59</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>72.17597000000001</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>0.083</v>
       </c>
     </row>
@@ -856,46 +882,49 @@
       <c r="B9" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>46023.11655092592</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>511.04</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>0.011</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>5.62144</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>4.6e-06</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>510.0416685</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>511.04</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>5.62144</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>0.011</v>
       </c>
     </row>
@@ -906,46 +935,49 @@
       <c r="B10" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>46023.11655092592</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>511.01</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>0.015</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>7.66515</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>6.27e-06</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>510.0416685</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>511.01</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>7.66515</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -956,46 +988,49 @@
       <c r="B11" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="n">
         <v>46023.11655092592</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>511.08</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>0.011</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>5.62188</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4.6e-06</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>510.0416685</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>511.08</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>5.621879999999999</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>0.011</v>
       </c>
     </row>
@@ -1006,46 +1041,49 @@
       <c r="B12" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="n">
         <v>46023.11582175926</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>87764.99000000001</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>0.00055</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>48.2707445</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>3.955e-05</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>87944.2532895</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>87764.99000000001</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>48.27074450000001</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>0.00055</v>
       </c>
     </row>
@@ -1056,46 +1094,49 @@
       <c r="B13" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" s="2" t="n">
         <v>45990.61078703704</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>0.2812</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>245.1</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>68.92212000000001</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5.596e-05</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>0.281253335</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>0.2812</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>68.92212000000001</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>245.1</v>
       </c>
     </row>
@@ -1106,46 +1147,49 @@
       <c r="B14" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2" t="n">
         <v>45990.61035879629</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>460.21</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>0.048</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>22.09008</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1.792e-05</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>459.2474745000001</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>460.21</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>22.09008</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>0.048</v>
       </c>
     </row>
@@ -1156,46 +1200,49 @@
       <c r="B15" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="n">
         <v>45990.60915509259</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>877.15</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>0.103</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>90.34645</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>7.334999999999999e-05</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>876.7868385</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>877.15</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>90.34644999999999</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -1206,46 +1253,49 @@
       <c r="B16" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" t="n">
+        <v>14</v>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>45962.06081018518</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>1088.98</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>0.136</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>148.10128</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>9.69e-05</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>1088.9890135</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>1088.98</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>148.10128</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -1256,46 +1306,49 @@
       <c r="B17" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>45962.05966435185</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>0.296</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>2624.2</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>776.7632</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>2.49299</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="K17" t="n">
-        <v>0.296</v>
       </c>
       <c r="L17" t="n">
         <v>0.296</v>
       </c>
       <c r="M17" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="N17" t="n">
         <v>776.7631999999999</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>2624.2</v>
       </c>
     </row>
@@ -1306,46 +1359,49 @@
       <c r="B18" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" s="2" t="n">
         <v>45962.05966435185</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>0.296</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>585.2</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>173.2192</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>0.55594</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="K18" t="n">
-        <v>0.296</v>
       </c>
       <c r="L18" t="n">
         <v>0.296</v>
       </c>
       <c r="M18" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="N18" t="n">
         <v>173.2192</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>585.2</v>
       </c>
     </row>
@@ -1356,46 +1412,49 @@
       <c r="B19" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" t="n">
+        <v>17</v>
+      </c>
+      <c r="D19" s="2" t="n">
         <v>45962.05902777778</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>109727.81</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>0.01002</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1099.4726562</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1.04449902</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>109764.5000986667</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>109727.81</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>1099.4726562</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>0.01002</v>
       </c>
     </row>
@@ -1406,46 +1465,49 @@
       <c r="B20" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" s="2" t="n">
         <v>45931.03042824074</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
         <v>113954.4</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>0.00396</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>451.259424</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>3.834e-05</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>113986.300759</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>113954.4</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>451.259424</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>0.00396</v>
       </c>
     </row>
@@ -1456,46 +1518,49 @@
       <c r="B21" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" s="2" t="n">
         <v>45931.02980324074</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>0.3329</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>905.7</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>301.50753</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>0.28643215</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>0.3333916683333333</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>0.3329</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>301.50753</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>905.7</v>
       </c>
     </row>
@@ -1506,46 +1571,49 @@
       <c r="B22" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" s="2" t="n">
         <v>45931.02895833334</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>0.3329</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>452</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>150.4708</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>0.14294726</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>0.3334</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>0.3329</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>150.4708</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>452</v>
       </c>
     </row>
@@ -1556,46 +1624,49 @@
       <c r="B23" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" t="n">
+        <v>21</v>
+      </c>
+      <c r="D23" s="2" t="n">
         <v>45900.93915509259</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
         <v>0.3425</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>200.6</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>68.7055</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>5.642e-05</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>0.342961665</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>0.3425</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>68.7055</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>200.6</v>
       </c>
     </row>
@@ -1606,46 +1677,49 @@
       <c r="B24" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" t="n">
+        <v>22</v>
+      </c>
+      <c r="D24" s="2" t="n">
         <v>45900.93896990741</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>109079.99</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>0.00063</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>68.7203937</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>5.645e-05</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>109075.7142211667</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>109079.99</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>68.7203937</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>0.00063</v>
       </c>
     </row>
@@ -1656,46 +1730,49 @@
       <c r="B25" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" t="n">
+        <v>23</v>
+      </c>
+      <c r="D25" s="2" t="n">
         <v>45900.93672453704</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
         <v>0.34241792</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>2022.6</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>692.57447</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>0.00056949</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>0.3431</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>0.34241792</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>692.574484992</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>2022.6</v>
       </c>
     </row>
@@ -1706,46 +1783,49 @@
       <c r="B26" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" t="n">
+        <v>24</v>
+      </c>
+      <c r="D26" s="2" t="n">
         <v>45900.93601851852</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>867.28</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>0.019</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>16.47832</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>1.353e-05</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>866.8346673333334</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>867.28</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>16.47832</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>0.019</v>
       </c>
     </row>
@@ -1756,46 +1836,49 @@
       <c r="B27" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" t="n">
+        <v>25</v>
+      </c>
+      <c r="D27" s="2" t="n">
         <v>45900.93578703704</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>ETHUSDT</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>4462.54</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>0.0693</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>309.254022</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>0.00025404</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>4467.496042999999</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>4462.54</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>309.254022</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>0.0693</v>
       </c>
     </row>
@@ -1806,46 +1889,49 @@
       <c r="B28" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D28" s="2" t="n">
         <v>45900.93532407407</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>SOLUSDT</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>204.95</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>1.79</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>366.8605</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>0.0003014</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>205.7853301666667</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>204.95</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>366.8605</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>1.79</v>
       </c>
     </row>
@@ -1856,46 +1942,49 @@
       <c r="B29" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" t="n">
+        <v>27</v>
+      </c>
+      <c r="D29" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
         <v>841.902968</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>1.648052154152757e-05</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>0.013875</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>3.3e-07</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>894.9224991666665</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>841.902968</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>0.013875</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>1.648052154152757e-05</v>
       </c>
     </row>
@@ -1906,46 +1995,49 @@
       <c r="B30" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" t="n">
+        <v>28</v>
+      </c>
+      <c r="D30" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
         <v>0.024577</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>0.5645522236237132</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>0.013875</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>3.3e-07</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>0.02457696902309403</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>0.000604028167680582</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>0.0003410054451954296</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>0.5645522236237132</v>
       </c>
     </row>
@@ -1956,46 +2048,49 @@
       <c r="B31" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" t="n">
+        <v>29</v>
+      </c>
+      <c r="D31" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>0.015385</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>0.9018524536886579</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>0.013875</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>3.3e-07</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>0.01658150016666667</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>0.015385</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>0.013875</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>0.9018524536886579</v>
       </c>
     </row>
@@ -2006,46 +2101,49 @@
       <c r="B32" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" t="n">
+        <v>30</v>
+      </c>
+      <c r="D32" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
         <v>894.9224991666665</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>2.229999999999999e-06</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>0.001995677173141666</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>4e-08</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="K32" t="n">
-        <v>894.9224991666665</v>
       </c>
       <c r="L32" t="n">
         <v>894.9224991666665</v>
       </c>
       <c r="M32" t="n">
+        <v>894.9224991666665</v>
+      </c>
+      <c r="N32" t="n">
         <v>0.001995677173141665</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>2.229999999999999e-06</v>
       </c>
     </row>
@@ -2056,46 +2154,49 @@
       <c r="B33" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C33" t="n">
+        <v>31</v>
+      </c>
+      <c r="D33" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>0.163644480872939</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>0.001995677173141666</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>4e-08</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>0.1749</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>0.163644480872939</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>0.001995677173141666</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>0.0121952</v>
       </c>
     </row>
@@ -2106,46 +2207,49 @@
       <c r="B34" t="n">
         <v>32</v>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C34" t="n">
+        <v>32</v>
+      </c>
+      <c r="D34" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>3.747533232175975</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>6.02</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>22.56015005769937</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3.28e-06</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>0.02457696902309403</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>0.09210300816020439</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>0.5544601091244304</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>6.02</v>
       </c>
     </row>
@@ -2156,46 +2260,49 @@
       <c r="B35" t="n">
         <v>33</v>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="C35" t="n">
+        <v>33</v>
+      </c>
+      <c r="D35" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
         <v>894.922499</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>0.0252090545079696</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>22.56015005769937</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>3.28e-06</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>894.9224991666665</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>894.922499</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>22.56015005769937</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>0.0252090545079696</v>
       </c>
     </row>
@@ -2206,46 +2313,49 @@
       <c r="B36" t="n">
         <v>34</v>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" t="n">
+        <v>34</v>
+      </c>
+      <c r="D36" s="2" t="n">
         <v>45891.84428240741</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>0.02457606291472106</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>8718.124</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>214.2571639223396</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>0.00026837</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>0.02457606291472106</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>0.0006039828683883277</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>5.265597540485121</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>8718.124</v>
       </c>
     </row>
@@ -2256,46 +2366,49 @@
       <c r="B37" t="n">
         <v>35</v>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C37" t="n">
+        <v>35</v>
+      </c>
+      <c r="D37" s="2" t="n">
         <v>45891.84428240741</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
         <v>0.3650036864094372</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>586.9999999999999</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>214.2571639223396</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>0.00026837</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>0.3659</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>0.3650036864094372</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>214.2571639223396</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>586.9999999999999</v>
       </c>
     </row>
@@ -2306,46 +2419,49 @@
       <c r="B38" t="n">
         <v>36</v>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C38" t="n">
+        <v>36</v>
+      </c>
+      <c r="D38" s="2" t="n">
         <v>45891.84357638889</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
         <v>0.02458361491986309</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>8724.144000000002</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>214.4709966014341</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>0.00026861</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>0.02458361491986309</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>0.000604354122528115</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>5.272472391928921</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>8724.144000000002</v>
       </c>
     </row>
@@ -2356,46 +2472,49 @@
       <c r="B39" t="n">
         <v>37</v>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C39" t="n">
+        <v>37</v>
+      </c>
+      <c r="D39" s="2" t="n">
         <v>45891.84357638889</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>0.01676602537534663</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>12792</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>214.4709966014341</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>0.00026861</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>0.01655750016666666</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>0.01676602537534663</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>214.4709966014341</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>12792</v>
       </c>
     </row>
@@ -2406,46 +2525,49 @@
       <c r="B40" t="n">
         <v>38</v>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C40" t="n">
+        <v>38</v>
+      </c>
+      <c r="D40" s="2" t="n">
         <v>45878.0263425926</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
         <v>794.6106690000001</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>0.01898484</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>1.423e-05</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="K40" t="n">
-        <v>794.6106690000001</v>
       </c>
       <c r="L40" t="n">
         <v>794.6106690000001</v>
       </c>
       <c r="M40" t="n">
+        <v>794.6106690000001</v>
+      </c>
+      <c r="N40" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>0.01898484</v>
       </c>
     </row>
@@ -2456,46 +2578,49 @@
       <c r="B41" t="n">
         <v>39</v>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C41" t="n">
+        <v>39</v>
+      </c>
+      <c r="D41" s="2" t="n">
         <v>45878.0263425926</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>0.1296010001139</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>116.4</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>1.423e-05</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>0.13021333</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>0.1296010001139</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>116.4</v>
       </c>
     </row>
@@ -2506,46 +2631,49 @@
       <c r="B42" t="n">
         <v>40</v>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" t="n">
+        <v>40</v>
+      </c>
+      <c r="D42" s="2" t="n">
         <v>45560.6427662037</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
         <v>1.1803</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>57</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>67.2771</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>0.057</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>1.179691675</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>1.1803</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>67.27709999999999</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>56.99999999999999</v>
       </c>
     </row>
@@ -2556,46 +2684,49 @@
       <c r="B43" t="n">
         <v>41</v>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C43" t="n">
+        <v>41</v>
+      </c>
+      <c r="D43" s="2" t="n">
         <v>45560.6427662037</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
         <v>1.1803</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>34</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>40.1302</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>0.034</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>1.179691675</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>1.1803</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>40.13019999999999</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>34</v>
       </c>
     </row>
@@ -2606,46 +2737,49 @@
       <c r="B44" t="n">
         <v>42</v>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C44" t="n">
+        <v>42</v>
+      </c>
+      <c r="D44" s="2" t="n">
         <v>45560.6427662037</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
         <v>1.1802</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>94</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>110.9388</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>0.094</v>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>1.179691675</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>1.1802</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>110.9388</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>94</v>
       </c>
     </row>
@@ -2656,46 +2790,49 @@
       <c r="B45" t="n">
         <v>43</v>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C45" t="n">
+        <v>43</v>
+      </c>
+      <c r="D45" s="2" t="n">
         <v>45560.64236111111</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>0.1508</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>1456.1</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>219.57988</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>0.21957988</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>0.1508000016666667</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>0.1508</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>219.57988</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>1456.1</v>
       </c>
     </row>
@@ -2706,46 +2843,49 @@
       <c r="B46" t="n">
         <v>44</v>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" t="n">
+        <v>44</v>
+      </c>
+      <c r="D46" s="2" t="n">
         <v>45553.90638888889</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>60330.29408616667</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>0.00132203</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>79.75845869073494</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>0.073</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
-      </c>
-      <c r="K46" t="n">
-        <v>60330.29408616667</v>
       </c>
       <c r="L46" t="n">
         <v>60330.29408616667</v>
       </c>
       <c r="M46" t="n">
+        <v>60330.29408616667</v>
+      </c>
+      <c r="N46" t="n">
         <v>79.75845869073493</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>0.00132203</v>
       </c>
     </row>
@@ -2756,46 +2896,49 @@
       <c r="B47" t="n">
         <v>45</v>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" t="n">
+        <v>45</v>
+      </c>
+      <c r="D47" s="2" t="n">
         <v>45553.90638888889</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
         <v>1.092581625900479</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>73</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>79.75845869073494</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>0.073</v>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>1.091139995</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>1.092581625900479</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>79.75845869073497</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>73</v>
       </c>
     </row>
@@ -2806,46 +2949,49 @@
       <c r="B48" t="n">
         <v>46</v>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" t="n">
+        <v>46</v>
+      </c>
+      <c r="D48" s="2" t="n">
         <v>45529.90896990741</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>64353.81012600001</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>0.0025413</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>0.985</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="K48" t="n">
-        <v>64353.81012600001</v>
       </c>
       <c r="L48" t="n">
         <v>64353.81012600001</v>
       </c>
       <c r="M48" t="n">
+        <v>64353.81012600001</v>
+      </c>
+      <c r="N48" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>0.0025413</v>
       </c>
     </row>
@@ -2856,46 +3002,49 @@
       <c r="B49" t="n">
         <v>47</v>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" t="n">
+        <v>47</v>
+      </c>
+      <c r="D49" s="2" t="n">
         <v>45529.90896990741</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
         <v>0.16603283012508</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>985</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>0.985</v>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>0.1655</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>0.16603283012508</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>985</v>
       </c>
     </row>
@@ -2906,46 +3055,49 @@
       <c r="B50" t="n">
         <v>48</v>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" t="n">
+        <v>48</v>
+      </c>
+      <c r="D50" s="2" t="n">
         <v>45529.90652777778</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
         <v>0.1655</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>453</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>74.97150000000001</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>9.736e-05</v>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>0.1654599983333334</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>0.1655</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>74.97150000000001</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>453</v>
       </c>
     </row>
@@ -2956,46 +3108,49 @@
       <c r="B51" t="n">
         <v>49</v>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C51" t="n">
+        <v>49</v>
+      </c>
+      <c r="D51" s="2" t="n">
         <v>45529.90614583333</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>0.343</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>218.6</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>74.9798</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>9.734999999999999e-05</v>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>0.3429850016666667</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>0.343</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>74.9798</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>218.6</v>
       </c>
     </row>
@@ -3006,46 +3161,49 @@
       <c r="B52" t="n">
         <v>50</v>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C52" t="n">
+        <v>50</v>
+      </c>
+      <c r="D52" s="2" t="n">
         <v>45528.99840277778</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>580.5</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>0.1015056</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>58.92400079999999</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>0.371</v>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="K52" t="n">
-        <v>580.5</v>
       </c>
       <c r="L52" t="n">
         <v>580.5</v>
       </c>
       <c r="M52" t="n">
+        <v>580.5</v>
+      </c>
+      <c r="N52" t="n">
         <v>58.9240008</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>0.1015056</v>
       </c>
     </row>
@@ -3056,46 +3214,49 @@
       <c r="B53" t="n">
         <v>51</v>
       </c>
-      <c r="C53" s="2" t="n">
+      <c r="C53" t="n">
+        <v>51</v>
+      </c>
+      <c r="D53" s="2" t="n">
         <v>45528.99840277778</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
         <v>0.1588248</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>370.9999999999999</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>58.92400079999999</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>0.371</v>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>0.1589</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>0.1588248</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>58.92400079999998</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>370.9999999999999</v>
       </c>
     </row>
@@ -3106,46 +3267,49 @@
       <c r="B54" t="n">
         <v>52</v>
       </c>
-      <c r="C54" s="2" t="n">
+      <c r="C54" t="n">
+        <v>52</v>
+      </c>
+      <c r="D54" s="2" t="n">
         <v>45500.56033564815</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
         <v>68797.23868549999</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>0.00031044</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>2.709e-05</v>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="K54" t="n">
-        <v>68797.23868549999</v>
       </c>
       <c r="L54" t="n">
         <v>68797.23868549999</v>
       </c>
       <c r="M54" t="n">
+        <v>68797.23868549999</v>
+      </c>
+      <c r="N54" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>0.00031044</v>
       </c>
     </row>
@@ -3156,46 +3320,49 @@
       <c r="B55" t="n">
         <v>53</v>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C55" t="n">
+        <v>53</v>
+      </c>
+      <c r="D55" s="2" t="n">
         <v>45500.56033564815</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>0.136906504984145</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>156</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>2.709e-05</v>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>0.137311665</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>0.136906504984145</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>156</v>
       </c>
     </row>
@@ -3206,46 +3373,49 @@
       <c r="B56" t="n">
         <v>54</v>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C56" t="n">
+        <v>54</v>
+      </c>
+      <c r="D56" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
         <v>68786.2337</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>0.0002774880000000001</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>19.0873544169456</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>2.447e-05</v>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="K56" t="n">
-        <v>68786.2337</v>
       </c>
       <c r="L56" t="n">
         <v>68786.2337</v>
       </c>
       <c r="M56" t="n">
+        <v>68786.2337</v>
+      </c>
+      <c r="N56" t="n">
         <v>19.08735441694561</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>0.0002774880000000001</v>
       </c>
     </row>
@@ -3256,46 +3426,49 @@
       <c r="B57" t="n">
         <v>55</v>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C57" t="n">
+        <v>55</v>
+      </c>
+      <c r="D57" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>MKRUSDT</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>0.0072</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>19.0873544169456</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>2.447e-05</v>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>2650.85005</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>19.0873544169456</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>0.007199999999999999</v>
       </c>
     </row>
@@ -3306,46 +3479,49 @@
       <c r="B58" t="n">
         <v>56</v>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C58" t="n">
+        <v>56</v>
+      </c>
+      <c r="D58" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
         <v>68786.2337</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>0.001452958</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>0.00012672</v>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="K58" t="n">
-        <v>68786.2337</v>
       </c>
       <c r="L58" t="n">
         <v>68786.2337</v>
       </c>
       <c r="M58" t="n">
+        <v>68786.2337</v>
+      </c>
+      <c r="N58" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>0.001452958</v>
       </c>
     </row>
@@ -3356,46 +3532,49 @@
       <c r="B59" t="n">
         <v>57</v>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C59" t="n">
+        <v>57</v>
+      </c>
+      <c r="D59" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>MKRUSDT</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>0.0377</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>0.00012672</v>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>2650.85005</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>0.0377</v>
       </c>
     </row>
@@ -3406,46 +3585,49 @@
       <c r="B60" t="n">
         <v>58</v>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C60" t="n">
+        <v>58</v>
+      </c>
+      <c r="D60" s="2" t="n">
         <v>45488.03726851852</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>OMEUR</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
         <v>1.00660569</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>194.71378022</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>200</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>4</v>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>1.0889</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>1.096092935841</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>213.424399010039</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>194.71378022</v>
       </c>
     </row>
@@ -3456,46 +3638,49 @@
       <c r="B61" t="n">
         <v>59</v>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="C61" t="n">
+        <v>59</v>
+      </c>
+      <c r="D61" s="2" t="n">
         <v>45479.77708333333</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>BNBEUR</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
         <v>485.5</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>0.1</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>48.55</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>7.499999999999999e-05</v>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>1.080199998333333</v>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
         <v>524.4370991908332</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>52.44370991908333</v>
       </c>
-      <c r="N61" t="n">
+      <c r="O61" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3506,46 +3691,49 @@
       <c r="B62" t="n">
         <v>60</v>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C62" t="n">
+        <v>60</v>
+      </c>
+      <c r="D62" s="2" t="n">
         <v>45479.76871527778</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
         <v>0.398</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>34.0688</v>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>4.857e-05</v>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>0.39797001</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
         <v>0.398</v>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
         <v>34.0688</v>
       </c>
-      <c r="N62" t="n">
+      <c r="O62" t="n">
         <v>85.59999999999998</v>
       </c>
     </row>
@@ -3556,46 +3744,49 @@
       <c r="B63" t="n">
         <v>61</v>
       </c>
-      <c r="C63" s="2" t="n">
+      <c r="C63" t="n">
+        <v>61</v>
+      </c>
+      <c r="D63" s="2" t="n">
         <v>45479.76849537037</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>524.6</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>0.065</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>34.099</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>4.873e-05</v>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
         <v>524.5999999999999</v>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
         <v>524.6</v>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
         <v>34.099</v>
       </c>
-      <c r="N63" t="n">
+      <c r="O63" t="n">
         <v>0.065</v>
       </c>
     </row>
@@ -3606,46 +3797,49 @@
       <c r="B64" t="n">
         <v>62</v>
       </c>
-      <c r="C64" s="2" t="n">
+      <c r="C64" t="n">
+        <v>62</v>
+      </c>
+      <c r="D64" s="2" t="n">
         <v>45479.673125</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
         <v>0.02414</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>1976.8</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>47.719952</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>6.879e-05</v>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
         <v>0.02414200066666666</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
         <v>0.02414</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
         <v>47.719952</v>
       </c>
-      <c r="N64" t="n">
+      <c r="O64" t="n">
         <v>1976.8</v>
       </c>
     </row>
@@ -3656,46 +3850,49 @@
       <c r="B65" t="n">
         <v>63</v>
       </c>
-      <c r="C65" s="2" t="n">
+      <c r="C65" t="n">
+        <v>63</v>
+      </c>
+      <c r="D65" s="2" t="n">
         <v>45479.67239583333</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>PEPEUSDT</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>9.21e-06</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>5181574</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>47.72229654</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>6.889e-05</v>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
         <v>9.215000333333332e-06</v>
       </c>
-      <c r="L65" t="n">
+      <c r="M65" t="n">
         <v>9.21e-06</v>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
         <v>47.72229654</v>
       </c>
-      <c r="N65" t="n">
+      <c r="O65" t="n">
         <v>5181574</v>
       </c>
     </row>
@@ -3706,46 +3903,49 @@
       <c r="B66" t="n">
         <v>64</v>
       </c>
-      <c r="C66" s="2" t="n">
+      <c r="C66" t="n">
+        <v>64</v>
+      </c>
+      <c r="D66" s="2" t="n">
         <v>45459.61185185185</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>NOTUSDT</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>0.020114</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>2036</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>40.952104</v>
       </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
         <v>0.0409521</v>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
         <v>0.02009346653333333</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
         <v>0.020114</v>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
         <v>40.952104</v>
       </c>
-      <c r="N66" t="n">
+      <c r="O66" t="n">
         <v>2036</v>
       </c>
     </row>
@@ -3756,46 +3956,49 @@
       <c r="B67" t="n">
         <v>65</v>
       </c>
-      <c r="C67" s="2" t="n">
+      <c r="C67" t="n">
+        <v>65</v>
+      </c>
+      <c r="D67" s="2" t="n">
         <v>45457.95482638889</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>NOTUSDT</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
         <v>0.019619</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>88</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>1.726472</v>
       </c>
-      <c r="I67" t="n">
+      <c r="J67" t="n">
         <v>2.2e-06</v>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" t="n">
         <v>0.01962085005</v>
       </c>
-      <c r="L67" t="n">
+      <c r="M67" t="n">
         <v>0.019619</v>
       </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
         <v>1.726472</v>
       </c>
-      <c r="N67" t="n">
+      <c r="O67" t="n">
         <v>88</v>
       </c>
     </row>
@@ -3806,46 +4009,49 @@
       <c r="B68" t="n">
         <v>66</v>
       </c>
-      <c r="C68" s="2" t="n">
+      <c r="C68" t="n">
+        <v>66</v>
+      </c>
+      <c r="D68" s="2" t="n">
         <v>45457.95482638889</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>NOTUSDT</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
         <v>0.019619</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>1950</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>38.25705</v>
       </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
         <v>1.95</v>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>0.01962085005</v>
       </c>
-      <c r="L68" t="n">
+      <c r="M68" t="n">
         <v>0.019619</v>
       </c>
-      <c r="M68" t="n">
+      <c r="N68" t="n">
         <v>38.25705</v>
       </c>
-      <c r="N68" t="n">
+      <c r="O68" t="n">
         <v>1950</v>
       </c>
     </row>
@@ -3856,46 +4062,49 @@
       <c r="B69" t="n">
         <v>67</v>
       </c>
-      <c r="C69" s="2" t="n">
+      <c r="C69" t="n">
+        <v>67</v>
+      </c>
+      <c r="D69" s="2" t="n">
         <v>45457.95456018519</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>0.5085</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>9.5</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>4.83075</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
         <v>6.02e-06</v>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
         <v>0.5088133366666666</v>
       </c>
-      <c r="L69" t="n">
+      <c r="M69" t="n">
         <v>0.5085</v>
       </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
         <v>4.830749999999999</v>
       </c>
-      <c r="N69" t="n">
+      <c r="O69" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -3906,46 +4115,49 @@
       <c r="B70" t="n">
         <v>68</v>
       </c>
-      <c r="C70" s="2" t="n">
+      <c r="C70" t="n">
+        <v>68</v>
+      </c>
+      <c r="D70" s="2" t="n">
         <v>45457.95456018519</v>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F70" t="n">
+      <c r="G70" t="n">
         <v>0.5086000000000001</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>29.8</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>15.15628</v>
       </c>
-      <c r="I70" t="n">
+      <c r="J70" t="n">
         <v>1.891e-05</v>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
         <v>0.5088133366666666</v>
       </c>
-      <c r="L70" t="n">
+      <c r="M70" t="n">
         <v>0.5086000000000001</v>
       </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
         <v>15.15628</v>
       </c>
-      <c r="N70" t="n">
+      <c r="O70" t="n">
         <v>29.8</v>
       </c>
     </row>
@@ -3956,46 +4168,49 @@
       <c r="B71" t="n">
         <v>69</v>
       </c>
-      <c r="C71" s="2" t="n">
+      <c r="C71" t="n">
+        <v>69</v>
+      </c>
+      <c r="D71" s="2" t="n">
         <v>45457.95416666667</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>PEPEUSDT</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F71" t="n">
+      <c r="G71" t="n">
         <v>1.145e-05</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>1746724</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>19.9999898</v>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
         <v>2.433e-05</v>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
         <v>1.14600005e-05</v>
       </c>
-      <c r="L71" t="n">
+      <c r="M71" t="n">
         <v>1.145e-05</v>
       </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
         <v>19.9999898</v>
       </c>
-      <c r="N71" t="n">
+      <c r="O71" t="n">
         <v>1746724</v>
       </c>
     </row>
@@ -4006,46 +4221,49 @@
       <c r="B72" t="n">
         <v>70</v>
       </c>
-      <c r="C72" s="2" t="n">
+      <c r="C72" t="n">
+        <v>70</v>
+      </c>
+      <c r="D72" s="2" t="n">
         <v>45455.6309837963</v>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
         <v>0.037824</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>3465.2</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>131.0677248</v>
       </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
         <v>3.4652</v>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>JASMY</t>
         </is>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>0.03777478451666667</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" t="n">
         <v>0.037824</v>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
         <v>131.0677248</v>
       </c>
-      <c r="N72" t="n">
+      <c r="O72" t="n">
         <v>3465.2</v>
       </c>
     </row>
@@ -4056,46 +4274,49 @@
       <c r="B73" t="n">
         <v>71</v>
       </c>
-      <c r="C73" s="2" t="n">
+      <c r="C73" t="n">
+        <v>71</v>
+      </c>
+      <c r="D73" s="2" t="n">
         <v>45455.630625</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F73" t="n">
+      <c r="G73" t="n">
         <v>69787.49000000001</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>0.00188</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>131.2004812</v>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>0.13120048</v>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
         <v>69787.75104183334</v>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" t="n">
         <v>69787.49000000001</v>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
         <v>131.2004812</v>
       </c>
-      <c r="N73" t="n">
+      <c r="O73" t="n">
         <v>0.00188</v>
       </c>
     </row>
@@ -4106,46 +4327,49 @@
       <c r="B74" t="n">
         <v>72</v>
       </c>
-      <c r="C74" s="2" t="n">
+      <c r="C74" t="n">
+        <v>72</v>
+      </c>
+      <c r="D74" s="2" t="n">
         <v>45455.03658564815</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
         <v>67225.22887250001</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>0.0001384</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
         <v>1.176e-05</v>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="K74" t="n">
-        <v>67225.22887250001</v>
       </c>
       <c r="L74" t="n">
         <v>67225.22887250001</v>
       </c>
       <c r="M74" t="n">
+        <v>67225.22887250001</v>
+      </c>
+      <c r="N74" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="N74" t="n">
+      <c r="O74" t="n">
         <v>0.0001384</v>
       </c>
     </row>
@@ -4156,46 +4380,49 @@
       <c r="B75" t="n">
         <v>73</v>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="C75" t="n">
+        <v>73</v>
+      </c>
+      <c r="D75" s="2" t="n">
         <v>45455.03658564815</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F75" t="n">
+      <c r="G75" t="n">
         <v>0.116299645949425</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>80</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
         <v>1.176e-05</v>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
         <v>0.11652</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" t="n">
         <v>0.116299645949425</v>
       </c>
-      <c r="M75" t="n">
+      <c r="N75" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="N75" t="n">
+      <c r="O75" t="n">
         <v>80</v>
       </c>
     </row>
@@ -4206,46 +4433,49 @@
       <c r="B76" t="n">
         <v>74</v>
       </c>
-      <c r="C76" s="2" t="n">
+      <c r="C76" t="n">
+        <v>74</v>
+      </c>
+      <c r="D76" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>0.001252093</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>1.25e-06</v>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="K76" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="L76" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="M76" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="N76" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="N76" t="n">
+      <c r="O76" t="n">
         <v>0.001252093</v>
       </c>
     </row>
@@ -4256,46 +4486,49 @@
       <c r="B77" t="n">
         <v>75</v>
       </c>
-      <c r="C77" s="2" t="n">
+      <c r="C77" t="n">
+        <v>75</v>
+      </c>
+      <c r="D77" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>0.127</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
         <v>1.25e-06</v>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="M77" t="n">
+      <c r="N77" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="N77" t="n">
+      <c r="O77" t="n">
         <v>0.127</v>
       </c>
     </row>
@@ -4306,46 +4539,49 @@
       <c r="B78" t="n">
         <v>76</v>
       </c>
-      <c r="C78" s="2" t="n">
+      <c r="C78" t="n">
+        <v>76</v>
+      </c>
+      <c r="D78" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>0.0029577</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
         <v>2.96e-06</v>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="K78" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="L78" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="M78" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="N78" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="N78" t="n">
+      <c r="O78" t="n">
         <v>0.0029577</v>
       </c>
     </row>
@@ -4356,46 +4592,49 @@
       <c r="B79" t="n">
         <v>77</v>
       </c>
-      <c r="C79" s="2" t="n">
+      <c r="C79" t="n">
+        <v>77</v>
+      </c>
+      <c r="D79" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>0.3</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
         <v>2.96e-06</v>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="M79" t="n">
+      <c r="N79" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="N79" t="n">
+      <c r="O79" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -4406,46 +4645,49 @@
       <c r="B80" t="n">
         <v>78</v>
       </c>
-      <c r="C80" s="2" t="n">
+      <c r="C80" t="n">
+        <v>78</v>
+      </c>
+      <c r="D80" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>0.002464749999999999</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
         <v>2.46e-06</v>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="K80" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="L80" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="M80" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="N80" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="N80" t="n">
+      <c r="O80" t="n">
         <v>0.002464749999999999</v>
       </c>
     </row>
@@ -4456,46 +4698,49 @@
       <c r="B81" t="n">
         <v>79</v>
       </c>
-      <c r="C81" s="2" t="n">
+      <c r="C81" t="n">
+        <v>79</v>
+      </c>
+      <c r="D81" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F81" t="n">
+      <c r="G81" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>0.25</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
         <v>2.46e-06</v>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="M81" t="n">
+      <c r="N81" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="N81" t="n">
+      <c r="O81" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -4506,46 +4751,49 @@
       <c r="B82" t="n">
         <v>80</v>
       </c>
-      <c r="C82" s="2" t="n">
+      <c r="C82" t="n">
+        <v>80</v>
+      </c>
+      <c r="D82" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>0.004929499999999999</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="I82" t="n">
+      <c r="J82" t="n">
         <v>0.000375</v>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="K82" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="L82" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="M82" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="N82" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="N82" t="n">
+      <c r="O82" t="n">
         <v>0.004929499999999999</v>
       </c>
     </row>
@@ -4556,46 +4804,49 @@
       <c r="B83" t="n">
         <v>81</v>
       </c>
-      <c r="C83" s="2" t="n">
+      <c r="C83" t="n">
+        <v>81</v>
+      </c>
+      <c r="D83" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F83" t="n">
+      <c r="G83" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>0.5</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="I83" t="n">
+      <c r="J83" t="n">
         <v>0.000375</v>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="L83" t="n">
+      <c r="M83" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="M83" t="n">
+      <c r="N83" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="N83" t="n">
+      <c r="O83" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4606,46 +4857,49 @@
       <c r="B84" t="n">
         <v>82</v>
       </c>
-      <c r="C84" s="2" t="n">
+      <c r="C84" t="n">
+        <v>82</v>
+      </c>
+      <c r="D84" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>0.000808438</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="I84" t="n">
+      <c r="J84" t="n">
         <v>6.161e-05</v>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="K84" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="L84" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="M84" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="N84" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="N84" t="n">
+      <c r="O84" t="n">
         <v>0.000808438</v>
       </c>
     </row>
@@ -4656,46 +4910,49 @@
       <c r="B85" t="n">
         <v>83</v>
       </c>
-      <c r="C85" s="2" t="n">
+      <c r="C85" t="n">
+        <v>83</v>
+      </c>
+      <c r="D85" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F85" t="n">
+      <c r="G85" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>0.082</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
         <v>6.161e-05</v>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K85" t="n">
+      <c r="L85" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="L85" t="n">
+      <c r="M85" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="M85" t="n">
+      <c r="N85" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="N85" t="n">
+      <c r="O85" t="n">
         <v>0.082</v>
       </c>
     </row>
@@ -4706,46 +4963,49 @@
       <c r="B86" t="n">
         <v>84</v>
       </c>
-      <c r="C86" s="2" t="n">
+      <c r="C86" t="n">
+        <v>84</v>
+      </c>
+      <c r="D86" s="2" t="n">
         <v>45451.5195949074</v>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
         <v>683.8948187155901</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>1.121</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>766.6460917801764</v>
       </c>
-      <c r="I86" t="n">
+      <c r="J86" t="n">
         <v>0.00084075</v>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" t="n">
         <v>683.7183116666666</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
         <v>683.8948187155901</v>
       </c>
-      <c r="M86" t="n">
+      <c r="N86" t="n">
         <v>766.6460917801764</v>
       </c>
-      <c r="N86" t="n">
+      <c r="O86" t="n">
         <v>1.121</v>
       </c>
     </row>
@@ -4756,46 +5016,49 @@
       <c r="B87" t="n">
         <v>85</v>
       </c>
-      <c r="C87" s="2" t="n">
+      <c r="C87" t="n">
+        <v>85</v>
+      </c>
+      <c r="D87" s="2" t="n">
         <v>45451.5195949074</v>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F87" t="n">
+      <c r="G87" t="n">
         <v>69360.5292815</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>0.01105306</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>766.6460917801764</v>
       </c>
-      <c r="I87" t="n">
+      <c r="J87" t="n">
         <v>0.00084075</v>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="K87" t="n">
-        <v>69360.5292815</v>
       </c>
       <c r="L87" t="n">
         <v>69360.5292815</v>
       </c>
       <c r="M87" t="n">
+        <v>69360.5292815</v>
+      </c>
+      <c r="N87" t="n">
         <v>766.6460917801763</v>
       </c>
-      <c r="N87" t="n">
+      <c r="O87" t="n">
         <v>0.01105306</v>
       </c>
     </row>
@@ -4806,46 +5069,49 @@
       <c r="B88" t="n">
         <v>86</v>
       </c>
-      <c r="C88" s="2" t="n">
+      <c r="C88" t="n">
+        <v>86</v>
+      </c>
+      <c r="D88" s="2" t="n">
         <v>45451.50400462963</v>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F88" t="n">
+      <c r="G88" t="n">
         <v>681.2</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>0.015</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
         <v>10.218</v>
       </c>
-      <c r="I88" t="n">
+      <c r="J88" t="n">
         <v>1.124e-05</v>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="K88" t="n">
+      <c r="L88" t="n">
         <v>681.9633216666666</v>
       </c>
-      <c r="L88" t="n">
+      <c r="M88" t="n">
         <v>681.2</v>
       </c>
-      <c r="M88" t="n">
+      <c r="N88" t="n">
         <v>10.218</v>
       </c>
-      <c r="N88" t="n">
+      <c r="O88" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -4856,46 +5122,49 @@
       <c r="B89" t="n">
         <v>87</v>
       </c>
-      <c r="C89" s="2" t="n">
+      <c r="C89" t="n">
+        <v>87</v>
+      </c>
+      <c r="D89" s="2" t="n">
         <v>45450.92207175926</v>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
         <v>0.041304</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>1210.5</v>
       </c>
-      <c r="H89" t="n">
+      <c r="I89" t="n">
         <v>49.998492</v>
       </c>
-      <c r="I89" t="n">
+      <c r="J89" t="n">
         <v>1.2105</v>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>JASMY</t>
         </is>
       </c>
-      <c r="K89" t="n">
+      <c r="L89" t="n">
         <v>0.04132561585</v>
       </c>
-      <c r="L89" t="n">
+      <c r="M89" t="n">
         <v>0.041304</v>
       </c>
-      <c r="M89" t="n">
+      <c r="N89" t="n">
         <v>49.998492</v>
       </c>
-      <c r="N89" t="n">
+      <c r="O89" t="n">
         <v>1210.5</v>
       </c>
     </row>
@@ -4906,46 +5175,49 @@
       <c r="B90" t="n">
         <v>88</v>
       </c>
-      <c r="C90" s="2" t="n">
+      <c r="C90" t="n">
+        <v>88</v>
+      </c>
+      <c r="D90" s="2" t="n">
         <v>45450.92207175926</v>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
         <v>0.041305</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>1082.2</v>
       </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
         <v>44.700271</v>
       </c>
-      <c r="I90" t="n">
+      <c r="J90" t="n">
         <v>1.0822</v>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>JASMY</t>
         </is>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
         <v>0.04132561585</v>
       </c>
-      <c r="L90" t="n">
+      <c r="M90" t="n">
         <v>0.041305</v>
       </c>
-      <c r="M90" t="n">
+      <c r="N90" t="n">
         <v>44.700271</v>
       </c>
-      <c r="N90" t="n">
+      <c r="O90" t="n">
         <v>1082.2</v>
       </c>
     </row>
@@ -4956,46 +5228,49 @@
       <c r="B91" t="n">
         <v>89</v>
       </c>
-      <c r="C91" s="2" t="n">
+      <c r="C91" t="n">
+        <v>89</v>
+      </c>
+      <c r="D91" s="2" t="n">
         <v>45450.92138888889</v>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>ENSUSDT</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F91" t="n">
+      <c r="G91" t="n">
         <v>21.97</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>2.01</v>
       </c>
-      <c r="H91" t="n">
+      <c r="I91" t="n">
         <v>44.1597</v>
       </c>
-      <c r="I91" t="n">
+      <c r="J91" t="n">
         <v>0.0441597</v>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="K91" t="n">
+      <c r="L91" t="n">
         <v>21.95600116666667</v>
       </c>
-      <c r="L91" t="n">
+      <c r="M91" t="n">
         <v>21.97</v>
       </c>
-      <c r="M91" t="n">
+      <c r="N91" t="n">
         <v>44.15969999999999</v>
       </c>
-      <c r="N91" t="n">
+      <c r="O91" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -5006,46 +5281,49 @@
       <c r="B92" t="n">
         <v>90</v>
       </c>
-      <c r="C92" s="2" t="n">
+      <c r="C92" t="n">
+        <v>90</v>
+      </c>
+      <c r="D92" s="2" t="n">
         <v>45450.92039351852</v>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>ARUSDT</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F92" t="n">
+      <c r="G92" t="n">
         <v>39.245</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>1.3</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>51.0185</v>
       </c>
-      <c r="I92" t="n">
+      <c r="J92" t="n">
         <v>0.0510185</v>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="K92" t="n">
+      <c r="L92" t="n">
         <v>39.20989994999999</v>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" t="n">
         <v>39.245</v>
       </c>
-      <c r="M92" t="n">
+      <c r="N92" t="n">
         <v>51.0185</v>
       </c>
-      <c r="N92" t="n">
+      <c r="O92" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -5056,46 +5334,49 @@
       <c r="B93" t="n">
         <v>91</v>
       </c>
-      <c r="C93" s="2" t="n">
+      <c r="C93" t="n">
+        <v>91</v>
+      </c>
+      <c r="D93" s="2" t="n">
         <v>45447.9729050926</v>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
         <v>70502.70711650001</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>5.1689e-05</v>
       </c>
-      <c r="H93" t="n">
+      <c r="I93" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="I93" t="n">
+      <c r="J93" t="n">
         <v>5e-08</v>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="K93" t="n">
-        <v>70502.70711650001</v>
       </c>
       <c r="L93" t="n">
         <v>70502.70711650001</v>
       </c>
       <c r="M93" t="n">
+        <v>70502.70711650001</v>
+      </c>
+      <c r="N93" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="N93" t="n">
+      <c r="O93" t="n">
         <v>5.1689e-05</v>
       </c>
     </row>
@@ -5106,46 +5387,49 @@
       <c r="B94" t="n">
         <v>92</v>
       </c>
-      <c r="C94" s="2" t="n">
+      <c r="C94" t="n">
+        <v>92</v>
+      </c>
+      <c r="D94" s="2" t="n">
         <v>45447.9729050926</v>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>UMAUSDT</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F94" t="n">
+      <c r="G94" t="n">
         <v>3.312922207404335</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>1.1</v>
       </c>
-      <c r="H94" t="n">
+      <c r="I94" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="I94" t="n">
+      <c r="J94" t="n">
         <v>5e-08</v>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="K94" t="n">
+      <c r="L94" t="n">
         <v>3.312983350000001</v>
       </c>
-      <c r="L94" t="n">
+      <c r="M94" t="n">
         <v>3.312922207404335</v>
       </c>
-      <c r="M94" t="n">
+      <c r="N94" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="N94" t="n">
+      <c r="O94" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -5156,46 +5440,49 @@
       <c r="B95" t="n">
         <v>93</v>
       </c>
-      <c r="C95" s="2" t="n">
+      <c r="C95" t="n">
+        <v>93</v>
+      </c>
+      <c r="D95" s="2" t="n">
         <v>45447.94982638889</v>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
         <v>70534.99716683332</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>0.0002490470000000001</v>
       </c>
-      <c r="H95" t="n">
+      <c r="I95" t="n">
         <v>17.56652943940834</v>
       </c>
-      <c r="I95" t="n">
+      <c r="J95" t="n">
         <v>2.5e-07</v>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="K95" t="n">
-        <v>70534.99716683332</v>
       </c>
       <c r="L95" t="n">
         <v>70534.99716683332</v>
       </c>
       <c r="M95" t="n">
+        <v>70534.99716683332</v>
+      </c>
+      <c r="N95" t="n">
         <v>17.56652943940835</v>
       </c>
-      <c r="N95" t="n">
+      <c r="O95" t="n">
         <v>0.0002490470000000001</v>
       </c>
     </row>
@@ -5206,46 +5493,49 @@
       <c r="B96" t="n">
         <v>94</v>
       </c>
-      <c r="C96" s="2" t="n">
+      <c r="C96" t="n">
+        <v>94</v>
+      </c>
+      <c r="D96" s="2" t="n">
         <v>45447.94982638889</v>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>UMAUSDT</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F96" t="n">
+      <c r="G96" t="n">
         <v>3.314439516869498</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>5.3</v>
       </c>
-      <c r="H96" t="n">
+      <c r="I96" t="n">
         <v>17.56652943940834</v>
       </c>
-      <c r="I96" t="n">
+      <c r="J96" t="n">
         <v>2.5e-07</v>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="K96" t="n">
+      <c r="L96" t="n">
         <v>3.311750016666666</v>
       </c>
-      <c r="L96" t="n">
+      <c r="M96" t="n">
         <v>3.314439516869498</v>
       </c>
-      <c r="M96" t="n">
+      <c r="N96" t="n">
         <v>17.56652943940834</v>
       </c>
-      <c r="N96" t="n">
+      <c r="O96" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -5256,46 +5546,49 @@
       <c r="B97" t="n">
         <v>95</v>
       </c>
-      <c r="C97" s="2" t="n">
+      <c r="C97" t="n">
+        <v>95</v>
+      </c>
+      <c r="D97" s="2" t="n">
         <v>45446.50150462963</v>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>ETHUSDT</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
         <v>3810.458332166667</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>0.01363</v>
       </c>
-      <c r="H97" t="n">
+      <c r="I97" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="I97" t="n">
+      <c r="J97" t="n">
         <v>1.363e-05</v>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
-      </c>
-      <c r="K97" t="n">
-        <v>3810.458332166667</v>
       </c>
       <c r="L97" t="n">
         <v>3810.458332166667</v>
       </c>
       <c r="M97" t="n">
+        <v>3810.458332166667</v>
+      </c>
+      <c r="N97" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="N97" t="n">
+      <c r="O97" t="n">
         <v>0.01363</v>
       </c>
     </row>
@@ -5306,46 +5599,49 @@
       <c r="B98" t="n">
         <v>96</v>
       </c>
-      <c r="C98" s="2" t="n">
+      <c r="C98" t="n">
+        <v>96</v>
+      </c>
+      <c r="D98" s="2" t="n">
         <v>45446.50150462963</v>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>XRPUSDT</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F98" t="n">
+      <c r="G98" t="n">
         <v>0.5193654706743167</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>100</v>
       </c>
-      <c r="H98" t="n">
+      <c r="I98" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="I98" t="n">
+      <c r="J98" t="n">
         <v>1.363e-05</v>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="K98" t="n">
+      <c r="L98" t="n">
         <v>0.5193833316666667</v>
       </c>
-      <c r="L98" t="n">
+      <c r="M98" t="n">
         <v>0.5193654706743167</v>
       </c>
-      <c r="M98" t="n">
+      <c r="N98" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="N98" t="n">
+      <c r="O98" t="n">
         <v>100</v>
       </c>
     </row>
@@ -5356,46 +5652,49 @@
       <c r="B99" t="n">
         <v>97</v>
       </c>
-      <c r="C99" s="2" t="n">
+      <c r="C99" t="n">
+        <v>97</v>
+      </c>
+      <c r="D99" s="2" t="n">
         <v>45446.49649305556</v>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
         <v>69129.98950016667</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>0.00069092</v>
       </c>
-      <c r="H99" t="n">
+      <c r="I99" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="I99" t="n">
+      <c r="J99" t="n">
         <v>6.9e-07</v>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="K99" t="n">
-        <v>69129.98950016667</v>
       </c>
       <c r="L99" t="n">
         <v>69129.98950016667</v>
       </c>
       <c r="M99" t="n">
+        <v>69129.98950016667</v>
+      </c>
+      <c r="N99" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="N99" t="n">
+      <c r="O99" t="n">
         <v>0.00069092</v>
       </c>
     </row>
@@ -5406,46 +5705,49 @@
       <c r="B100" t="n">
         <v>98</v>
       </c>
-      <c r="C100" s="2" t="n">
+      <c r="C100" t="n">
+        <v>98</v>
+      </c>
+      <c r="D100" s="2" t="n">
         <v>45446.49649305556</v>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>XRPUSDT</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F100" t="n">
+      <c r="G100" t="n">
         <v>0.5191662211462518</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>92</v>
       </c>
-      <c r="H100" t="n">
+      <c r="I100" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="I100" t="n">
+      <c r="J100" t="n">
         <v>6.9e-07</v>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="K100" t="n">
+      <c r="L100" t="n">
         <v>0.5193049983333333</v>
       </c>
-      <c r="L100" t="n">
+      <c r="M100" t="n">
         <v>0.5191662211462518</v>
       </c>
-      <c r="M100" t="n">
+      <c r="N100" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="N100" t="n">
+      <c r="O100" t="n">
         <v>92</v>
       </c>
     </row>
@@ -5456,46 +5758,49 @@
       <c r="B101" t="n">
         <v>99</v>
       </c>
-      <c r="C101" s="2" t="n">
+      <c r="C101" t="n">
+        <v>99</v>
+      </c>
+      <c r="D101" s="2" t="n">
         <v>45446.42081018518</v>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
         <v>69115.08947183334</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>0.0006642089999999999</v>
       </c>
-      <c r="H101" t="n">
+      <c r="I101" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="I101" t="n">
+      <c r="J101" t="n">
         <v>6.6e-07</v>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="K101" t="n">
-        <v>69115.08947183334</v>
       </c>
       <c r="L101" t="n">
         <v>69115.08947183334</v>
       </c>
       <c r="M101" t="n">
+        <v>69115.08947183334</v>
+      </c>
+      <c r="N101" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="N101" t="n">
+      <c r="O101" t="n">
         <v>0.0006642089999999999</v>
       </c>
     </row>
@@ -5506,46 +5811,49 @@
       <c r="B102" t="n">
         <v>100</v>
       </c>
-      <c r="C102" s="2" t="n">
+      <c r="C102" t="n">
+        <v>100</v>
+      </c>
+      <c r="D102" s="2" t="n">
         <v>45446.42081018518</v>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>NEARUSDT</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F102" t="n">
+      <c r="G102" t="n">
         <v>7.28680388301539</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>6.3</v>
       </c>
-      <c r="H102" t="n">
+      <c r="I102" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="I102" t="n">
+      <c r="J102" t="n">
         <v>6.6e-07</v>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="K102" t="n">
+      <c r="L102" t="n">
         <v>7.287033316666666</v>
       </c>
-      <c r="L102" t="n">
+      <c r="M102" t="n">
         <v>7.28680388301539</v>
       </c>
-      <c r="M102" t="n">
+      <c r="N102" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="N102" t="n">
+      <c r="O102" t="n">
         <v>6.299999999999999</v>
       </c>
     </row>
@@ -5556,46 +5864,49 @@
       <c r="B103" t="n">
         <v>101</v>
       </c>
-      <c r="C103" s="2" t="n">
+      <c r="C103" t="n">
+        <v>101</v>
+      </c>
+      <c r="D103" s="2" t="n">
         <v>45442.00921296296</v>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
         <v>67749.86920016666</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>0.00093258</v>
       </c>
-      <c r="H103" t="n">
+      <c r="I103" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="I103" t="n">
+      <c r="J103" t="n">
         <v>9.3e-07</v>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="K103" t="n">
-        <v>67749.86920016666</v>
       </c>
       <c r="L103" t="n">
         <v>67749.86920016666</v>
       </c>
       <c r="M103" t="n">
+        <v>67749.86920016666</v>
+      </c>
+      <c r="N103" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="N103" t="n">
+      <c r="O103" t="n">
         <v>0.00093258</v>
       </c>
     </row>
@@ -5606,46 +5917,49 @@
       <c r="B104" t="n">
         <v>102</v>
       </c>
-      <c r="C104" s="2" t="n">
+      <c r="C104" t="n">
+        <v>102</v>
+      </c>
+      <c r="D104" s="2" t="n">
         <v>45442.00921296296</v>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>LPTUSDT</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F104" t="n">
+      <c r="G104" t="n">
         <v>21.27345892885233</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>2.97</v>
       </c>
-      <c r="H104" t="n">
+      <c r="I104" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="I104" t="n">
+      <c r="J104" t="n">
         <v>9.3e-07</v>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="K104" t="n">
+      <c r="L104" t="n">
         <v>21.26066758333333</v>
       </c>
-      <c r="L104" t="n">
+      <c r="M104" t="n">
         <v>21.27345892885233</v>
       </c>
-      <c r="M104" t="n">
+      <c r="N104" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="N104" t="n">
+      <c r="O104" t="n">
         <v>2.97</v>
       </c>
     </row>
@@ -5656,46 +5970,49 @@
       <c r="B105" t="n">
         <v>103</v>
       </c>
-      <c r="C105" s="2" t="n">
+      <c r="C105" t="n">
+        <v>103</v>
+      </c>
+      <c r="D105" s="2" t="n">
         <v>45441.90847222223</v>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
         <v>67695.03782550001</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>0.0007335899999999999</v>
       </c>
-      <c r="H105" t="n">
+      <c r="I105" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="I105" t="n">
+      <c r="J105" t="n">
         <v>7.3e-07</v>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="K105" t="n">
-        <v>67695.03782550001</v>
       </c>
       <c r="L105" t="n">
         <v>67695.03782550001</v>
       </c>
       <c r="M105" t="n">
+        <v>67695.03782550001</v>
+      </c>
+      <c r="N105" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="N105" t="n">
+      <c r="O105" t="n">
         <v>0.0007335899999999999</v>
       </c>
     </row>
@@ -5706,46 +6023,49 @@
       <c r="B106" t="n">
         <v>104</v>
       </c>
-      <c r="C106" s="2" t="n">
+      <c r="C106" t="n">
+        <v>104</v>
+      </c>
+      <c r="D106" s="2" t="n">
         <v>45441.90847222223</v>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>NEARUSDT</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F106" t="n">
+      <c r="G106" t="n">
         <v>7.640061968985931</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>6.5</v>
       </c>
-      <c r="H106" t="n">
+      <c r="I106" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="I106" t="n">
+      <c r="J106" t="n">
         <v>7.3e-07</v>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="K106" t="n">
+      <c r="L106" t="n">
         <v>7.64060005</v>
       </c>
-      <c r="L106" t="n">
+      <c r="M106" t="n">
         <v>7.640061968985931</v>
       </c>
-      <c r="M106" t="n">
+      <c r="N106" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="N106" t="n">
+      <c r="O106" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -5756,46 +6076,49 @@
       <c r="B107" t="n">
         <v>105</v>
       </c>
-      <c r="C107" s="2" t="n">
+      <c r="C107" t="n">
+        <v>105</v>
+      </c>
+      <c r="D107" s="2" t="n">
         <v>45440.88619212963</v>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
         <v>64131.08918148</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>0.00076406</v>
       </c>
-      <c r="H107" t="n">
+      <c r="I107" t="n">
         <v>50</v>
       </c>
-      <c r="I107" t="n">
+      <c r="J107" t="n">
         <v>1</v>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K107" t="n">
+      <c r="L107" t="n">
         <v>1.086388331666667</v>
       </c>
-      <c r="L107" t="n">
+      <c r="M107" t="n">
         <v>69671.26698383428</v>
       </c>
-      <c r="M107" t="n">
+      <c r="N107" t="n">
         <v>53.23302825166842</v>
       </c>
-      <c r="N107" t="n">
+      <c r="O107" t="n">
         <v>0.00076406</v>
       </c>
     </row>
@@ -5806,46 +6129,49 @@
       <c r="B108" t="n">
         <v>106</v>
       </c>
-      <c r="C108" s="2" t="n">
+      <c r="C108" t="n">
+        <v>106</v>
+      </c>
+      <c r="D108" s="2" t="n">
         <v>45439.96682870371</v>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
         <v>69531.81351050001</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>0.0004004640000000001</v>
       </c>
-      <c r="H108" t="n">
+      <c r="I108" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="I108" t="n">
+      <c r="J108" t="n">
         <v>4e-07</v>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="K108" t="n">
-        <v>69531.81351050001</v>
       </c>
       <c r="L108" t="n">
         <v>69531.81351050001</v>
       </c>
       <c r="M108" t="n">
+        <v>69531.81351050001</v>
+      </c>
+      <c r="N108" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="N108" t="n">
+      <c r="O108" t="n">
         <v>0.0004004640000000001</v>
       </c>
     </row>
@@ -5856,46 +6182,49 @@
       <c r="B109" t="n">
         <v>107</v>
       </c>
-      <c r="C109" s="2" t="n">
+      <c r="C109" t="n">
+        <v>107</v>
+      </c>
+      <c r="D109" s="2" t="n">
         <v>45439.96682870371</v>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>INJUSDT</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F109" t="n">
+      <c r="G109" t="n">
         <v>25.7823964496934</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>1.08</v>
       </c>
-      <c r="H109" t="n">
+      <c r="I109" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="I109" t="n">
+      <c r="J109" t="n">
         <v>4e-07</v>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="K109" t="n">
+      <c r="L109" t="n">
         <v>25.7770005</v>
       </c>
-      <c r="L109" t="n">
+      <c r="M109" t="n">
         <v>25.7823964496934</v>
       </c>
-      <c r="M109" t="n">
+      <c r="N109" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="N109" t="n">
+      <c r="O109" t="n">
         <v>1.08</v>
       </c>
     </row>
@@ -5906,46 +6235,49 @@
       <c r="B110" t="n">
         <v>108</v>
       </c>
-      <c r="C110" s="2" t="n">
+      <c r="C110" t="n">
+        <v>108</v>
+      </c>
+      <c r="D110" s="2" t="n">
         <v>45439.96547453704</v>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
         <v>69520.8794125</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>0.000231</v>
       </c>
-      <c r="H110" t="n">
+      <c r="I110" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="I110" t="n">
+      <c r="J110" t="n">
         <v>2.3e-07</v>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="K110" t="n">
-        <v>69520.8794125</v>
       </c>
       <c r="L110" t="n">
         <v>69520.8794125</v>
       </c>
       <c r="M110" t="n">
+        <v>69520.8794125</v>
+      </c>
+      <c r="N110" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="N110" t="n">
+      <c r="O110" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -5956,46 +6288,49 @@
       <c r="B111" t="n">
         <v>109</v>
       </c>
-      <c r="C111" s="2" t="n">
+      <c r="C111" t="n">
+        <v>109</v>
+      </c>
+      <c r="D111" s="2" t="n">
         <v>45439.96547453704</v>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>FETUSDT</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F111" t="n">
+      <c r="G111" t="n">
         <v>2.2941890206125</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>7</v>
       </c>
-      <c r="H111" t="n">
+      <c r="I111" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="I111" t="n">
+      <c r="J111" t="n">
         <v>2.3e-07</v>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="K111" t="n">
+      <c r="L111" t="n">
         <v>2.2945667</v>
       </c>
-      <c r="L111" t="n">
+      <c r="M111" t="n">
         <v>2.2941890206125</v>
       </c>
-      <c r="M111" t="n">
+      <c r="N111" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="N111" t="n">
+      <c r="O111" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6006,46 +6341,49 @@
       <c r="B112" t="n">
         <v>110</v>
       </c>
-      <c r="C112" s="2" t="n">
+      <c r="C112" t="n">
+        <v>110</v>
+      </c>
+      <c r="D112" s="2" t="n">
         <v>45438.41358796296</v>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
         <v>64764.05726993</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>0.00302637</v>
       </c>
-      <c r="H112" t="n">
+      <c r="I112" t="n">
         <v>200</v>
       </c>
-      <c r="I112" t="n">
+      <c r="J112" t="n">
         <v>4</v>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K112" t="n">
+      <c r="L112" t="n">
         <v>1.084943331666667</v>
       </c>
-      <c r="L112" t="n">
+      <c r="M112" t="n">
         <v>70265.33206668869</v>
       </c>
-      <c r="M112" t="n">
+      <c r="N112" t="n">
         <v>212.6488930066647</v>
       </c>
-      <c r="N112" t="n">
+      <c r="O112" t="n">
         <v>0.00302637</v>
       </c>
     </row>
@@ -6056,46 +6394,49 @@
       <c r="B113" t="n">
         <v>111</v>
       </c>
-      <c r="C113" s="2" t="n">
+      <c r="C113" t="n">
+        <v>111</v>
+      </c>
+      <c r="D113" s="2" t="n">
         <v>45438.06670138889</v>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>ENSEUR</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
         <v>21.88048003</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>3.35870145</v>
       </c>
-      <c r="H113" t="n">
+      <c r="I113" t="n">
         <v>75</v>
       </c>
-      <c r="I113" t="n">
+      <c r="J113" t="n">
         <v>1</v>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K113" t="n">
+      <c r="L113" t="n">
         <v>1.084505001666667</v>
       </c>
-      <c r="L113" t="n">
+      <c r="M113" t="n">
         <v>23.72949003140263</v>
       </c>
-      <c r="M113" t="n">
+      <c r="N113" t="n">
         <v>79.70027257623255</v>
       </c>
-      <c r="N113" t="n">
+      <c r="O113" t="n">
         <v>3.35870145</v>
       </c>
     </row>
@@ -6106,46 +6447,49 @@
       <c r="B114" t="n">
         <v>112</v>
       </c>
-      <c r="C114" s="2" t="n">
+      <c r="C114" t="n">
+        <v>112</v>
+      </c>
+      <c r="D114" s="2" t="n">
         <v>45438.06428240741</v>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>LPTEUR</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
         <v>21.40068094</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>4.57929354</v>
       </c>
-      <c r="H114" t="n">
+      <c r="I114" t="n">
         <v>100</v>
       </c>
-      <c r="I114" t="n">
+      <c r="J114" t="n">
         <v>2</v>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K114" t="n">
+      <c r="L114" t="n">
         <v>1.084456668333333</v>
       </c>
-      <c r="L114" t="n">
+      <c r="M114" t="n">
         <v>23.20811115225706</v>
       </c>
-      <c r="M114" t="n">
+      <c r="N114" t="n">
         <v>106.2767534751327</v>
       </c>
-      <c r="N114" t="n">
+      <c r="O114" t="n">
         <v>4.57929354</v>
       </c>
     </row>
@@ -6156,46 +6500,49 @@
       <c r="B115" t="n">
         <v>113</v>
       </c>
-      <c r="C115" s="2" t="n">
+      <c r="C115" t="n">
+        <v>113</v>
+      </c>
+      <c r="D115" s="2" t="n">
         <v>45438.06288194445</v>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>JASMYEUR</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
         <v>0.02039718</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>4804.58606935</v>
       </c>
-      <c r="H115" t="n">
+      <c r="I115" t="n">
         <v>100</v>
       </c>
-      <c r="I115" t="n">
+      <c r="J115" t="n">
         <v>2</v>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K115" t="n">
+      <c r="L115" t="n">
         <v>1.084644998333333</v>
       </c>
-      <c r="L115" t="n">
+      <c r="M115" t="n">
         <v>0.0221236992671047</v>
       </c>
-      <c r="M115" t="n">
+      <c r="N115" t="n">
         <v>106.29521730122</v>
       </c>
-      <c r="N115" t="n">
+      <c r="O115" t="n">
         <v>4804.58606935</v>
       </c>
     </row>
@@ -6206,46 +6553,49 @@
       <c r="B116" t="n">
         <v>114</v>
       </c>
-      <c r="C116" s="2" t="n">
+      <c r="C116" t="n">
+        <v>114</v>
+      </c>
+      <c r="D116" s="2" t="n">
         <v>45438.01670138889</v>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>BBEUR</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
         <v>0.5091575699999999</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>288.7121952</v>
       </c>
-      <c r="H116" t="n">
+      <c r="I116" t="n">
         <v>150</v>
       </c>
-      <c r="I116" t="n">
+      <c r="J116" t="n">
         <v>3</v>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="K116" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K116" t="n">
+      <c r="L116" t="n">
         <v>1.084505001666667</v>
       </c>
-      <c r="L116" t="n">
+      <c r="M116" t="n">
         <v>0.5521839313014461</v>
       </c>
-      <c r="M116" t="n">
+      <c r="N116" t="n">
         <v>159.4222349602065</v>
       </c>
-      <c r="N116" t="n">
+      <c r="O116" t="n">
         <v>288.7121952</v>
       </c>
     </row>
@@ -6256,46 +6606,49 @@
       <c r="B117" t="n">
         <v>115</v>
       </c>
-      <c r="C117" s="2" t="n">
+      <c r="C117" t="n">
+        <v>115</v>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>45438.01179398148</v>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>XRPEUR</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
         <v>0.50817649</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>192.84638819</v>
       </c>
-      <c r="H117" t="n">
+      <c r="I117" t="n">
         <v>100</v>
       </c>
-      <c r="I117" t="n">
+      <c r="J117" t="n">
         <v>2</v>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K117" t="n">
+      <c r="L117" t="n">
         <v>1.0845</v>
       </c>
-      <c r="L117" t="n">
+      <c r="M117" t="n">
         <v>0.551117403405</v>
       </c>
-      <c r="M117" t="n">
+      <c r="N117" t="n">
         <v>106.2810007153055</v>
       </c>
-      <c r="N117" t="n">
+      <c r="O117" t="n">
         <v>192.84638819</v>
       </c>
     </row>
@@ -6306,46 +6659,49 @@
       <c r="B118" t="n">
         <v>116</v>
       </c>
-      <c r="C118" s="2" t="n">
+      <c r="C118" t="n">
+        <v>116</v>
+      </c>
+      <c r="D118" s="2" t="n">
         <v>45437.93450231481</v>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>PEPEEUR</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
         <v>1.414e-05</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>6928298.24</v>
       </c>
-      <c r="H118" t="n">
+      <c r="I118" t="n">
         <v>100</v>
       </c>
-      <c r="I118" t="n">
+      <c r="J118" t="n">
         <v>2</v>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K118" t="n">
+      <c r="L118" t="n">
         <v>1.0845</v>
       </c>
-      <c r="L118" t="n">
+      <c r="M118" t="n">
         <v>1.533483e-05</v>
       </c>
-      <c r="M118" t="n">
+      <c r="N118" t="n">
         <v>106.2442756996992</v>
       </c>
-      <c r="N118" t="n">
+      <c r="O118" t="n">
         <v>6928298.24</v>
       </c>
     </row>
@@ -6356,46 +6712,49 @@
       <c r="B119" t="n">
         <v>117</v>
       </c>
-      <c r="C119" s="2" t="n">
+      <c r="C119" t="n">
+        <v>117</v>
+      </c>
+      <c r="D119" s="2" t="n">
         <v>45437.92731481481</v>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>NEAREUR</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
         <v>7.62742061</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>12.8483802</v>
       </c>
-      <c r="H119" t="n">
+      <c r="I119" t="n">
         <v>100</v>
       </c>
-      <c r="I119" t="n">
+      <c r="J119" t="n">
         <v>2</v>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K119" t="n">
+      <c r="L119" t="n">
         <v>1.0846</v>
       </c>
-      <c r="L119" t="n">
+      <c r="M119" t="n">
         <v>8.272700393606</v>
       </c>
-      <c r="M119" t="n">
+      <c r="N119" t="n">
         <v>106.2907999377395</v>
       </c>
-      <c r="N119" t="n">
+      <c r="O119" t="n">
         <v>12.8483802</v>
       </c>
     </row>
@@ -6406,46 +6765,49 @@
       <c r="B120" t="n">
         <v>118</v>
       </c>
-      <c r="C120" s="2" t="n">
+      <c r="C120" t="n">
+        <v>118</v>
+      </c>
+      <c r="D120" s="2" t="n">
         <v>45436.94775462963</v>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="E120" t="inlineStr">
         <is>
           <t>MKREUR</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
         <v>2571.01241222</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>0.03811728</v>
       </c>
-      <c r="H120" t="n">
+      <c r="I120" t="n">
         <v>100</v>
       </c>
-      <c r="I120" t="n">
+      <c r="J120" t="n">
         <v>2</v>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="K120" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K120" t="n">
+      <c r="L120" t="n">
         <v>1.084</v>
       </c>
-      <c r="L120" t="n">
+      <c r="M120" t="n">
         <v>2786.97745484648</v>
       </c>
-      <c r="M120" t="n">
+      <c r="N120" t="n">
         <v>106.2320000000707</v>
       </c>
-      <c r="N120" t="n">
+      <c r="O120" t="n">
         <v>0.03811728</v>
       </c>
     </row>
@@ -6456,46 +6818,49 @@
       <c r="B121" t="n">
         <v>119</v>
       </c>
-      <c r="C121" s="2" t="n">
+      <c r="C121" t="n">
+        <v>119</v>
+      </c>
+      <c r="D121" s="2" t="n">
         <v>45436.93561342593</v>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>ETHEUR</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
         <v>3502.04619556</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>0.04197546</v>
       </c>
-      <c r="H121" t="n">
+      <c r="I121" t="n">
         <v>150</v>
       </c>
-      <c r="I121" t="n">
+      <c r="J121" t="n">
         <v>3</v>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="K121" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K121" t="n">
+      <c r="L121" t="n">
         <v>1.084</v>
       </c>
-      <c r="L121" t="n">
+      <c r="M121" t="n">
         <v>3796.21807598704</v>
       </c>
-      <c r="M121" t="n">
+      <c r="N121" t="n">
         <v>159.347999999871</v>
       </c>
-      <c r="N121" t="n">
+      <c r="O121" t="n">
         <v>0.04197546</v>
       </c>
     </row>
@@ -6506,46 +6871,49 @@
       <c r="B122" t="n">
         <v>120</v>
       </c>
-      <c r="C122" s="2" t="n">
+      <c r="C122" t="n">
+        <v>120</v>
+      </c>
+      <c r="D122" s="2" t="n">
         <v>45436.93466435185</v>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
         <v>157.11043262</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>0.62376507</v>
       </c>
-      <c r="H122" t="n">
+      <c r="I122" t="n">
         <v>100</v>
       </c>
-      <c r="I122" t="n">
+      <c r="J122" t="n">
         <v>2</v>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="K122" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K122" t="n">
+      <c r="L122" t="n">
         <v>1.084108331666667</v>
       </c>
-      <c r="L122" t="n">
+      <c r="M122" t="n">
         <v>170.3247289950965</v>
       </c>
-      <c r="M122" t="n">
+      <c r="N122" t="n">
         <v>106.2426165043574</v>
       </c>
-      <c r="N122" t="n">
+      <c r="O122" t="n">
         <v>0.62376507</v>
       </c>
     </row>
@@ -6556,46 +6924,49 @@
       <c r="B123" t="n">
         <v>121</v>
       </c>
-      <c r="C123" s="2" t="n">
+      <c r="C123" t="n">
+        <v>121</v>
+      </c>
+      <c r="D123" s="2" t="n">
         <v>45436.43322916667</v>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
         <v>63003.06014864</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>0.00155548</v>
       </c>
-      <c r="H123" t="n">
+      <c r="I123" t="n">
         <v>100</v>
       </c>
-      <c r="I123" t="n">
+      <c r="J123" t="n">
         <v>2</v>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="K123" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K123" t="n">
+      <c r="L123" t="n">
         <v>1.0829</v>
       </c>
-      <c r="L123" t="n">
+      <c r="M123" t="n">
         <v>68226.01383496226</v>
       </c>
-      <c r="M123" t="n">
+      <c r="N123" t="n">
         <v>106.1242000000071</v>
       </c>
-      <c r="N123" t="n">
+      <c r="O123" t="n">
         <v>0.00155548</v>
       </c>
     </row>
@@ -6606,46 +6977,49 @@
       <c r="B124" t="n">
         <v>122</v>
       </c>
-      <c r="C124" s="2" t="n">
+      <c r="C124" t="n">
+        <v>122</v>
+      </c>
+      <c r="D124" s="2" t="n">
         <v>45426.64160879629</v>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
         <v>57930.57788707</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>0.00084584</v>
       </c>
-      <c r="H124" t="n">
+      <c r="I124" t="n">
         <v>50</v>
       </c>
-      <c r="I124" t="n">
+      <c r="J124" t="n">
         <v>1</v>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="K124" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K124" t="n">
+      <c r="L124" t="n">
         <v>1.0814</v>
       </c>
-      <c r="L124" t="n">
+      <c r="M124" t="n">
         <v>62646.12692707749</v>
       </c>
-      <c r="M124" t="n">
+      <c r="N124" t="n">
         <v>52.98859999999923</v>
       </c>
-      <c r="N124" t="n">
+      <c r="O124" t="n">
         <v>0.00084584</v>
       </c>
     </row>
@@ -6656,46 +7030,49 @@
       <c r="B125" t="n">
         <v>123</v>
       </c>
-      <c r="C125" s="2" t="n">
+      <c r="C125" t="n">
+        <v>123</v>
+      </c>
+      <c r="D125" s="2" t="n">
         <v>45425.85847222222</v>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
         <v>140.23996862</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>0.69880221</v>
       </c>
-      <c r="H125" t="n">
+      <c r="I125" t="n">
         <v>100</v>
       </c>
-      <c r="I125" t="n">
+      <c r="J125" t="n">
         <v>2</v>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="K125" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K125" t="n">
+      <c r="L125" t="n">
         <v>1.078779998333333</v>
       </c>
-      <c r="L125" t="n">
+      <c r="M125" t="n">
         <v>151.2880731141503</v>
       </c>
-      <c r="M125" t="n">
+      <c r="N125" t="n">
         <v>105.7204398388098</v>
       </c>
-      <c r="N125" t="n">
+      <c r="O125" t="n">
         <v>0.69880221</v>
       </c>
     </row>
@@ -6706,46 +7083,49 @@
       <c r="B126" t="n">
         <v>124</v>
       </c>
-      <c r="C126" s="2" t="n">
+      <c r="C126" t="n">
+        <v>124</v>
+      </c>
+      <c r="D126" s="2" t="n">
         <v>45422.83993055556</v>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>RNDREUR</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
         <v>10.58084967</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>1.85240322</v>
       </c>
-      <c r="H126" t="n">
+      <c r="I126" t="n">
         <v>20</v>
       </c>
-      <c r="I126" t="n">
+      <c r="J126" t="n">
         <v>0.4</v>
       </c>
-      <c r="J126" t="inlineStr">
+      <c r="K126" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K126" t="n">
+      <c r="L126" t="n">
         <v>1.076449998333333</v>
       </c>
-      <c r="L126" t="n">
+      <c r="M126" t="n">
         <v>11.38975560963675</v>
       </c>
-      <c r="M126" t="n">
+      <c r="N126" t="n">
         <v>21.09841996630417</v>
       </c>
-      <c r="N126" t="n">
+      <c r="O126" t="n">
         <v>1.85240322</v>
       </c>
     </row>
@@ -6756,46 +7136,49 @@
       <c r="B127" t="n">
         <v>125</v>
       </c>
-      <c r="C127" s="2" t="n">
+      <c r="C127" t="n">
+        <v>125</v>
+      </c>
+      <c r="D127" s="2" t="n">
         <v>45422.83865740741</v>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>ETHEUR</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
         <v>2752.33311287</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>0.00533729</v>
       </c>
-      <c r="H127" t="n">
+      <c r="I127" t="n">
         <v>15</v>
       </c>
-      <c r="I127" t="n">
+      <c r="J127" t="n">
         <v>0.31</v>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="K127" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K127" t="n">
+      <c r="L127" t="n">
         <v>1.0764</v>
       </c>
-      <c r="L127" t="n">
+      <c r="M127" t="n">
         <v>2962.611362693268</v>
       </c>
-      <c r="M127" t="n">
+      <c r="N127" t="n">
         <v>15.81231599998915</v>
       </c>
-      <c r="N127" t="n">
+      <c r="O127" t="n">
         <v>0.00533729</v>
       </c>
     </row>
@@ -6806,46 +7189,49 @@
       <c r="B128" t="n">
         <v>126</v>
       </c>
-      <c r="C128" s="2" t="n">
+      <c r="C128" t="n">
+        <v>126</v>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>45422.83754629629</v>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
         <v>57425.23976014</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>0.00051197</v>
       </c>
-      <c r="H128" t="n">
+      <c r="I128" t="n">
         <v>30</v>
       </c>
-      <c r="I128" t="n">
+      <c r="J128" t="n">
         <v>0.6</v>
       </c>
-      <c r="J128" t="inlineStr">
+      <c r="K128" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K128" t="n">
+      <c r="L128" t="n">
         <v>1.0764</v>
       </c>
-      <c r="L128" t="n">
+      <c r="M128" t="n">
         <v>61812.5280778147</v>
       </c>
-      <c r="M128" t="n">
+      <c r="N128" t="n">
         <v>31.64615999999879</v>
       </c>
-      <c r="N128" t="n">
+      <c r="O128" t="n">
         <v>0.00051197</v>
       </c>
     </row>
@@ -6856,46 +7242,49 @@
       <c r="B129" t="n">
         <v>127</v>
       </c>
-      <c r="C129" s="2" t="n">
+      <c r="C129" t="n">
+        <v>127</v>
+      </c>
+      <c r="D129" s="2" t="n">
         <v>45422.83584490741</v>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>FETEUR</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
         <v>2.10457801</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>6.98002161</v>
       </c>
-      <c r="H129" t="n">
+      <c r="I129" t="n">
         <v>15</v>
       </c>
-      <c r="I129" t="n">
+      <c r="J129" t="n">
         <v>0.31</v>
       </c>
-      <c r="J129" t="inlineStr">
+      <c r="K129" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K129" t="n">
+      <c r="L129" t="n">
         <v>1.076438331666667</v>
       </c>
-      <c r="L129" t="n">
+      <c r="M129" t="n">
         <v>2.265448441946754</v>
       </c>
-      <c r="M129" t="n">
+      <c r="N129" t="n">
         <v>15.81287908112917</v>
       </c>
-      <c r="N129" t="n">
+      <c r="O129" t="n">
         <v>6.98002161</v>
       </c>
     </row>
@@ -6906,46 +7295,49 @@
       <c r="B130" t="n">
         <v>128</v>
       </c>
-      <c r="C130" s="2" t="n">
+      <c r="C130" t="n">
+        <v>128</v>
+      </c>
+      <c r="D130" s="2" t="n">
         <v>45422.83362268518</v>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>TRXEUR</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F130" t="n">
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
         <v>0.1200639</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>163.24640485</v>
       </c>
-      <c r="H130" t="n">
+      <c r="I130" t="n">
         <v>20</v>
       </c>
-      <c r="I130" t="n">
+      <c r="J130" t="n">
         <v>0.4</v>
       </c>
-      <c r="J130" t="inlineStr">
+      <c r="K130" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K130" t="n">
+      <c r="L130" t="n">
         <v>1.0763</v>
       </c>
-      <c r="L130" t="n">
+      <c r="M130" t="n">
         <v>0.12922477557</v>
       </c>
-      <c r="M130" t="n">
+      <c r="N130" t="n">
         <v>21.09548002935061</v>
       </c>
-      <c r="N130" t="n">
+      <c r="O130" t="n">
         <v>163.24640485</v>
       </c>
     </row>
@@ -6956,46 +7348,49 @@
       <c r="B131" t="n">
         <v>129</v>
       </c>
-      <c r="C131" s="2" t="n">
+      <c r="C131" t="n">
+        <v>129</v>
+      </c>
+      <c r="D131" s="2" t="n">
         <v>45422.83130787037</v>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
         <v>140.17980062</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>0.13982043</v>
       </c>
-      <c r="H131" t="n">
+      <c r="I131" t="n">
         <v>20</v>
       </c>
-      <c r="I131" t="n">
+      <c r="J131" t="n">
         <v>0.4</v>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="K131" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K131" t="n">
+      <c r="L131" t="n">
         <v>1.076308335</v>
       </c>
-      <c r="L131" t="n">
+      <c r="M131" t="n">
         <v>150.8766878059442</v>
       </c>
-      <c r="M131" t="n">
+      <c r="N131" t="n">
         <v>21.09564336600287</v>
       </c>
-      <c r="N131" t="n">
+      <c r="O131" t="n">
         <v>0.13982043</v>
       </c>
     </row>
@@ -7006,46 +7401,49 @@
       <c r="B132" t="n">
         <v>130</v>
       </c>
-      <c r="C132" s="2" t="n">
+      <c r="C132" t="n">
+        <v>130</v>
+      </c>
+      <c r="D132" s="2" t="n">
         <v>45422.82967592592</v>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>TNSREUR</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F132" t="n">
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
         <v>0.79988478</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>18.36514507</v>
       </c>
-      <c r="H132" t="n">
+      <c r="I132" t="n">
         <v>15</v>
       </c>
-      <c r="I132" t="n">
+      <c r="J132" t="n">
         <v>0.31</v>
       </c>
-      <c r="J132" t="inlineStr">
+      <c r="K132" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K132" t="n">
+      <c r="L132" t="n">
         <v>1.076426665</v>
       </c>
-      <c r="L132" t="n">
+      <c r="M132" t="n">
         <v>0.8610173061196587</v>
       </c>
-      <c r="M132" t="n">
+      <c r="N132" t="n">
         <v>15.81270773466813</v>
       </c>
-      <c r="N132" t="n">
+      <c r="O132" t="n">
         <v>18.36514507</v>
       </c>
     </row>
@@ -7056,46 +7454,49 @@
       <c r="B133" t="n">
         <v>131</v>
       </c>
-      <c r="C133" s="2" t="n">
+      <c r="C133" t="n">
+        <v>131</v>
+      </c>
+      <c r="D133" s="2" t="n">
         <v>45422.08221064815</v>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F133" t="n">
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
         <v>143.75063899</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>0.13634722</v>
       </c>
-      <c r="H133" t="n">
+      <c r="I133" t="n">
         <v>20</v>
       </c>
-      <c r="I133" t="n">
+      <c r="J133" t="n">
         <v>0.4</v>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="K133" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K133" t="n">
+      <c r="L133" t="n">
         <v>1.077761665</v>
       </c>
-      <c r="L133" t="n">
+      <c r="M133" t="n">
         <v>154.9289280226763</v>
       </c>
-      <c r="M133" t="n">
+      <c r="N133" t="n">
         <v>21.12412863347201</v>
       </c>
-      <c r="N133" t="n">
+      <c r="O133" t="n">
         <v>0.13634722</v>
       </c>
     </row>
@@ -7106,46 +7507,49 @@
       <c r="B134" t="n">
         <v>132</v>
       </c>
-      <c r="C134" s="2" t="n">
+      <c r="C134" t="n">
+        <v>132</v>
+      </c>
+      <c r="D134" s="2" t="n">
         <v>45422.07099537037</v>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>USDTEUR</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F134" t="n">
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
         <v>0.93873598</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>26.08827246</v>
       </c>
-      <c r="H134" t="n">
+      <c r="I134" t="n">
         <v>25</v>
       </c>
-      <c r="I134" t="n">
+      <c r="J134" t="n">
         <v>0.51</v>
       </c>
-      <c r="J134" t="inlineStr">
+      <c r="K134" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K134" t="n">
+      <c r="L134" t="n">
         <v>1.0778</v>
       </c>
-      <c r="L134" t="n">
+      <c r="M134" t="n">
         <v>1.011769639244</v>
       </c>
-      <c r="M134" t="n">
+      <c r="N134" t="n">
         <v>26.39532201535338</v>
       </c>
-      <c r="N134" t="n">
+      <c r="O134" t="n">
         <v>26.08827246</v>
       </c>
     </row>
@@ -7156,46 +7560,49 @@
       <c r="B135" t="n">
         <v>133</v>
       </c>
-      <c r="C135" s="2" t="n">
+      <c r="C135" t="n">
+        <v>133</v>
+      </c>
+      <c r="D135" s="2" t="n">
         <v>45422.06987268518</v>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>MKREUR</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F135" t="n">
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
         <v>2583.15065304</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>0.00682887</v>
       </c>
-      <c r="H135" t="n">
+      <c r="I135" t="n">
         <v>18</v>
       </c>
-      <c r="I135" t="n">
+      <c r="J135" t="n">
         <v>0.36</v>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="K135" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K135" t="n">
+      <c r="L135" t="n">
         <v>1.077938331666667</v>
       </c>
-      <c r="L135" t="n">
+      <c r="M135" t="n">
         <v>2784.477105381599</v>
       </c>
-      <c r="M135" t="n">
+      <c r="N135" t="n">
         <v>19.01483217062724</v>
       </c>
-      <c r="N135" t="n">
+      <c r="O135" t="n">
         <v>0.006828869999999999</v>
       </c>
     </row>
@@ -7206,46 +7613,49 @@
       <c r="B136" t="n">
         <v>134</v>
       </c>
-      <c r="C136" s="2" t="n">
+      <c r="C136" t="n">
+        <v>134</v>
+      </c>
+      <c r="D136" s="2" t="n">
         <v>45422.05619212963</v>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="E136" t="inlineStr">
         <is>
           <t>FETEUR</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F136" t="n">
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
         <v>2.1432031</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>11.42682187</v>
       </c>
-      <c r="H136" t="n">
+      <c r="I136" t="n">
         <v>25</v>
       </c>
-      <c r="I136" t="n">
+      <c r="J136" t="n">
         <v>0.51</v>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="K136" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K136" t="n">
+      <c r="L136" t="n">
         <v>1.077691668333334</v>
       </c>
-      <c r="L136" t="n">
+      <c r="M136" t="n">
         <v>2.309712124416173</v>
       </c>
-      <c r="M136" t="n">
+      <c r="N136" t="n">
         <v>26.39266901668289</v>
       </c>
-      <c r="N136" t="n">
+      <c r="O136" t="n">
         <v>11.42682187</v>
       </c>
     </row>
@@ -7256,46 +7666,49 @@
       <c r="B137" t="n">
         <v>135</v>
       </c>
-      <c r="C137" s="2" t="n">
+      <c r="C137" t="n">
+        <v>135</v>
+      </c>
+      <c r="D137" s="2" t="n">
         <v>45422.01804398148</v>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>RNDREUR</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F137" t="n">
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
         <v>10.23426316</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>2.39294218</v>
       </c>
-      <c r="H137" t="n">
+      <c r="I137" t="n">
         <v>25</v>
       </c>
-      <c r="I137" t="n">
+      <c r="J137" t="n">
         <v>0.51</v>
       </c>
-      <c r="J137" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K137" t="n">
+      <c r="L137" t="n">
         <v>1.077698335</v>
       </c>
-      <c r="L137" t="n">
+      <c r="M137" t="n">
         <v>11.02944836748384</v>
       </c>
-      <c r="M137" t="n">
+      <c r="N137" t="n">
         <v>26.39283222068422</v>
       </c>
-      <c r="N137" t="n">
+      <c r="O137" t="n">
         <v>2.39294218</v>
       </c>
     </row>
@@ -7306,46 +7719,49 @@
       <c r="B138" t="n">
         <v>136</v>
       </c>
-      <c r="C138" s="2" t="n">
+      <c r="C138" t="n">
+        <v>136</v>
+      </c>
+      <c r="D138" s="2" t="n">
         <v>45421.93954861111</v>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>TRXEUR</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F138" t="n">
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
         <v>0.11898276</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>205.82814242</v>
       </c>
-      <c r="H138" t="n">
+      <c r="I138" t="n">
         <v>25</v>
       </c>
-      <c r="I138" t="n">
+      <c r="J138" t="n">
         <v>0.51</v>
       </c>
-      <c r="J138" t="inlineStr">
+      <c r="K138" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K138" t="n">
+      <c r="L138" t="n">
         <v>1.077904998333333</v>
       </c>
-      <c r="L138" t="n">
+      <c r="M138" t="n">
         <v>0.1282521117194954</v>
       </c>
-      <c r="M138" t="n">
+      <c r="N138" t="n">
         <v>26.39789391666605</v>
       </c>
-      <c r="N138" t="n">
+      <c r="O138" t="n">
         <v>205.82814242</v>
       </c>
     </row>
@@ -7356,46 +7772,49 @@
       <c r="B139" t="n">
         <v>137</v>
       </c>
-      <c r="C139" s="2" t="n">
+      <c r="C139" t="n">
+        <v>137</v>
+      </c>
+      <c r="D139" s="2" t="n">
         <v>45421.81724537037</v>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>UMAEUR</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F139" t="n">
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
         <v>3.80349912</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>6.43880785</v>
       </c>
-      <c r="H139" t="n">
+      <c r="I139" t="n">
         <v>25</v>
       </c>
-      <c r="I139" t="n">
+      <c r="J139" t="n">
         <v>0.51</v>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="K139" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K139" t="n">
+      <c r="L139" t="n">
         <v>1.077516665</v>
       </c>
-      <c r="L139" t="n">
+      <c r="M139" t="n">
         <v>4.098333687112835</v>
       </c>
-      <c r="M139" t="n">
+      <c r="N139" t="n">
         <v>26.38838311650157</v>
       </c>
-      <c r="N139" t="n">
+      <c r="O139" t="n">
         <v>6.43880785</v>
       </c>
     </row>
@@ -7406,46 +7825,49 @@
       <c r="B140" t="n">
         <v>138</v>
       </c>
-      <c r="C140" s="2" t="n">
+      <c r="C140" t="n">
+        <v>138</v>
+      </c>
+      <c r="D140" s="2" t="n">
         <v>45418.97721064815</v>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>ETHEUR</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F140" t="n">
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
         <v>2912.26895648</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>0.00840723</v>
       </c>
-      <c r="H140" t="n">
+      <c r="I140" t="n">
         <v>25</v>
       </c>
-      <c r="I140" t="n">
+      <c r="J140" t="n">
         <v>0.51</v>
       </c>
-      <c r="J140" t="inlineStr">
+      <c r="K140" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K140" t="n">
+      <c r="L140" t="n">
         <v>1.076</v>
       </c>
-      <c r="L140" t="n">
+      <c r="M140" t="n">
         <v>3133.60139717248</v>
       </c>
-      <c r="M140" t="n">
+      <c r="N140" t="n">
         <v>26.34490767435039</v>
       </c>
-      <c r="N140" t="n">
+      <c r="O140" t="n">
         <v>0.00840723</v>
       </c>
     </row>
@@ -7456,46 +7878,49 @@
       <c r="B141" t="n">
         <v>139</v>
       </c>
-      <c r="C141" s="2" t="n">
+      <c r="C141" t="n">
+        <v>139</v>
+      </c>
+      <c r="D141" s="2" t="n">
         <v>45418.96918981482</v>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F141" t="n">
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
         <v>59899.71272325</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>0.00040885</v>
       </c>
-      <c r="H141" t="n">
+      <c r="I141" t="n">
         <v>25</v>
       </c>
-      <c r="I141" t="n">
+      <c r="J141" t="n">
         <v>0.51</v>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="K141" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K141" t="n">
+      <c r="L141" t="n">
         <v>1.0761</v>
       </c>
-      <c r="L141" t="n">
+      <c r="M141" t="n">
         <v>64458.08086148932</v>
       </c>
-      <c r="M141" t="n">
+      <c r="N141" t="n">
         <v>26.35368636021991</v>
       </c>
-      <c r="N141" t="n">
+      <c r="O141" t="n">
         <v>0.00040885</v>
       </c>
     </row>
@@ -7506,46 +7931,49 @@
       <c r="B142" t="n">
         <v>140</v>
       </c>
-      <c r="C142" s="2" t="n">
+      <c r="C142" t="n">
+        <v>140</v>
+      </c>
+      <c r="D142" s="2" t="n">
         <v>45414.95027777777</v>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="F142" t="n">
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
         <v>131.18665751</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>0.18668057</v>
       </c>
-      <c r="H142" t="n">
+      <c r="I142" t="n">
         <v>25</v>
       </c>
-      <c r="I142" t="n">
+      <c r="J142" t="n">
         <v>0.51</v>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="K142" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="K142" t="n">
+      <c r="L142" t="n">
         <v>1.070940001666667</v>
       </c>
-      <c r="L142" t="n">
+      <c r="M142" t="n">
         <v>140.4930392124039</v>
       </c>
-      <c r="M142" t="n">
+      <c r="N142" t="n">
         <v>26.22732064120391</v>
       </c>
-      <c r="N142" t="n">
+      <c r="O142" t="n">
         <v>0.18668057</v>
       </c>
     </row>

--- a/Trade History Reconstructed.xlsx
+++ b/Trade History Reconstructed.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niroo\Desktop\Jupyter\Projets\Risk Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niroo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438653B6-9BD5-42A4-BC77-2C61D3398494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59B7CB0-6161-4F75-976A-94F0310EB06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Trade History Reconstructed.xlsx
+++ b/Trade History Reconstructed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niroo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59B7CB0-6161-4F75-976A-94F0310EB06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1585E1-FFD7-40C8-892D-A4D56064D2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Trade History Reconstructed.xlsx
+++ b/Trade History Reconstructed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niroo\Desktop\Jupyter\Projets\Risk Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614ADC82-95A0-465B-8C37-C6167F14D617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEC5AC6-4609-4689-A6B2-663A8804366B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -235,7 +235,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -291,7 +291,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -645,7 +645,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>0.60832175925925924</v>
+        <v>46113.60832175926</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>

--- a/Trade History Reconstructed.xlsx
+++ b/Trade History Reconstructed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niroo\Desktop\Jupyter\Projets\Risk Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E146DE-90E7-4289-9A76-A98C14F97E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61AB3D5-65C2-4077-BC8F-0EF97D0D79C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="4230" windowWidth="21600" windowHeight="11250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="70">
   <si>
     <t>Date(UTC)</t>
   </si>
@@ -230,19 +230,10 @@
     <t>UMAEUR</t>
   </si>
   <si>
-    <t>616.53</t>
-  </si>
-  <si>
-    <t>0.706</t>
-  </si>
-  <si>
     <t>435.27018</t>
   </si>
   <si>
     <t>BCH</t>
-  </si>
-  <si>
-    <t>0.168</t>
   </si>
   <si>
     <t>DOGEUSDT</t>
@@ -259,7 +250,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -315,7 +306,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -696,7 +687,7 @@
         <v>46143.53056712963</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -714,7 +705,7 @@
         <v>6.0229999999999995E-4</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -722,7 +713,7 @@
         <v>46143.530150462961</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -793,7 +784,7 @@
         <v>3.8475E-4</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -809,8 +800,8 @@
       <c r="D7">
         <v>443.2</v>
       </c>
-      <c r="E7" t="s">
-        <v>69</v>
+      <c r="E7">
+        <v>0.16800000000000001</v>
       </c>
       <c r="F7">
         <v>74.457599999999999</v>
@@ -819,7 +810,7 @@
         <v>1.596E-4</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -858,14 +849,14 @@
       <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9">
+        <v>616.53</v>
+      </c>
+      <c r="E9">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="F9" t="s">
         <v>65</v>
-      </c>
-      <c r="E9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" t="s">
-        <v>67</v>
       </c>
       <c r="G9">
         <f>0.0001033+0.00039969</f>

--- a/Trade History Reconstructed.xlsx
+++ b/Trade History Reconstructed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niroo\Desktop\Jupyter\Projets\Risk Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61AB3D5-65C2-4077-BC8F-0EF97D0D79C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B444DD9-C094-4257-AE57-39C5A9905418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4230" windowWidth="21600" windowHeight="11250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="69">
   <si>
     <t>Date(UTC)</t>
   </si>
@@ -228,9 +228,6 @@
   </si>
   <si>
     <t>UMAEUR</t>
-  </si>
-  <si>
-    <t>435.27018</t>
   </si>
   <si>
     <t>BCH</t>
@@ -687,7 +684,7 @@
         <v>46143.53056712963</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -705,7 +702,7 @@
         <v>6.0229999999999995E-4</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -713,7 +710,7 @@
         <v>46143.530150462961</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -784,7 +781,7 @@
         <v>3.8475E-4</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -810,7 +807,7 @@
         <v>1.596E-4</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -855,8 +852,8 @@
       <c r="E9">
         <v>0.70599999999999996</v>
       </c>
-      <c r="F9" t="s">
-        <v>65</v>
+      <c r="F9">
+        <v>435.27017999999998</v>
       </c>
       <c r="G9">
         <f>0.0001033+0.00039969</f>

--- a/Trade History Reconstructed.xlsx
+++ b/Trade History Reconstructed.xlsx
@@ -429,66 +429,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M153"/>
+  <dimension ref="A1:N153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Date(UTC)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Fee Coin</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Pair Price</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Price in USDT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Total in USDT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Pair Quantity</t>
         </is>
@@ -498,46 +503,49 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>46143.53075231481</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>0.326</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>186</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>60.636</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.1767</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.326728335</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.326</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>60.636</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>186</v>
       </c>
     </row>
@@ -545,46 +553,49 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>46143.53056712963</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>LTCUSDT</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>55.13</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.634</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>34.95242</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0.0006022999999999999</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>LTC</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>55.31983316666667</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>55.13</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>34.95242</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0.634</v>
       </c>
     </row>
@@ -592,46 +603,49 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>46143.53015046296</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>DOGEUSDT</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>0.108</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>185</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>19.98</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>2.307e-05</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.1089833326666667</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0.108</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>19.98</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>185</v>
       </c>
     </row>
@@ -639,46 +653,49 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>46143.52908564815</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>BCHUSDT</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>443.2</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.013</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>5.7616</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>6.64e-06</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>444.7116649999999</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>443.2</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>5.7616</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -686,46 +703,49 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>46143.52908564815</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>BCHUSDT</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>443.2</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.405</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>179.496</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.00038475</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>BCH</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>444.7116649999999</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>443.2</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>179.496</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.405</v>
       </c>
     </row>
@@ -733,46 +753,49 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>46143.52908564815</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>BCHUSDT</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>443.2</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.168</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>74.4576</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.0001596</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>BCH</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>444.7116649999999</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>443.2</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>74.4576</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0.168</v>
       </c>
     </row>
@@ -780,46 +803,49 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>46143.52851851852</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>0.3258</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>184.1</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>59.97978</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>0.174895</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>0.3267</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>0.3258</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>59.97977999999999</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>184.1</v>
       </c>
     </row>
@@ -827,46 +853,49 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>46143.52815972222</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>616.53</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.706</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>435.27018</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>0.00050299</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>620.5679926666667</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>616.53</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>435.27018</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.706</v>
       </c>
     </row>
@@ -874,46 +903,49 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>46113.60832175926</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>BCHUSDT</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>460</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.142</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>65.31999999999999</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>7.585e-05</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>459.495005</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>460</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>65.31999999999999</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>0.142</v>
       </c>
     </row>
@@ -921,46 +953,49 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>46113.60811342593</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>614.14</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.707</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>434.21819</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>0.00050373</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>612.0343310000001</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>614.14</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>434.1969799999999</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0.707</v>
       </c>
     </row>
@@ -968,46 +1003,49 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>46113.60709490741</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.3155</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>1584.7</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>499.97285</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>0.46148194</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>0.3158216683333334</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>0.3155</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>499.97285</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1584.7</v>
       </c>
     </row>
@@ -1015,46 +1053,49 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2" t="n">
         <v>46081.50087962963</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>0.2791</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>1702.7</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>475.22357</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>1.617565</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>0.2792733316666667</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>0.2791</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>475.2235700000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1702.7</v>
       </c>
     </row>
@@ -1062,46 +1103,49 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>46081.50046296296</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>63986.13</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>0.00046</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>29.4336198</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>3.528e-05</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>63900.73367266667</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>63986.13</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>29.4336198</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>0.00046</v>
       </c>
     </row>
@@ -1109,46 +1153,49 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>46081.5003125</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>594.34</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>0.75</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>445.755</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>0.0005343</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>594.6545034999999</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>594.34</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>445.755</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -1156,46 +1203,49 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2" t="n">
         <v>46054.61652777778</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>770.6900000000001</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.636</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>490.15884</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>0.00045314</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>753.2940488333334</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>770.6900000000001</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>490.1588400000001</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>0.636</v>
       </c>
     </row>
@@ -1203,46 +1253,49 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2" t="n">
         <v>46054.61582175926</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>78597.2</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.00114</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>89.600808</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>8.284e-05</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>77971.77212000001</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>78597.2</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>89.60080799999999</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>0.00114</v>
       </c>
     </row>
@@ -1250,46 +1303,49 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="n">
         <v>46054.61512731481</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>0.2859</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>1399</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>399.9741</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>0.00036997</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>0.285821665</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>0.2859</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>399.9741</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>1399</v>
       </c>
     </row>
@@ -1297,46 +1353,49 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2" t="n">
         <v>46023.11693287037</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>869.59</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>0.083</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>72.17597000000001</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>5.913e-05</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>871.1663310000001</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>869.59</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>72.17597000000001</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>0.083</v>
       </c>
     </row>
@@ -1344,46 +1403,49 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2" t="n">
         <v>46023.11655092592</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>511.04</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.011</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>5.62144</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>4.6e-06</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>510.0416685</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>511.04</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>5.62144</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>0.011</v>
       </c>
     </row>
@@ -1391,46 +1453,49 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" s="2" t="n">
         <v>46023.11655092592</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>511.01</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>0.015</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>7.66515</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>6.27e-06</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>510.0416685</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>511.01</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>7.66515</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -1438,46 +1503,49 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="2" t="n">
         <v>46023.11655092592</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>511.08</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>0.011</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>5.62188</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>4.6e-06</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>510.0416685</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>511.08</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>5.621879999999999</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>0.011</v>
       </c>
     </row>
@@ -1485,46 +1553,49 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="2" t="n">
         <v>46023.11582175926</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>87764.99000000001</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>0.00055</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>48.2707445</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>3.955e-05</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>87944.2532895</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>87764.99000000001</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>48.27074450000001</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>0.00055</v>
       </c>
     </row>
@@ -1532,46 +1603,49 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" s="2" t="n">
         <v>45990.61078703704</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>0.2812</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>245.1</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>68.92212000000001</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>5.596e-05</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>0.281253335</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>0.2812</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>68.92212000000001</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>245.1</v>
       </c>
     </row>
@@ -1579,46 +1653,49 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" s="2" t="n">
         <v>45990.61035879629</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>460.21</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>0.048</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>22.09008</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>1.792e-05</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>459.2474745000001</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>460.21</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>22.09008</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>0.048</v>
       </c>
     </row>
@@ -1626,46 +1703,49 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" s="2" t="n">
         <v>45990.60915509259</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>877.15</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>0.103</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>90.34645</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>7.334999999999999e-05</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>876.7868385</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>877.15</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>90.34644999999999</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -1673,46 +1753,49 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" s="2" t="n">
         <v>45962.06081018518</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>1088.98</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>0.136</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>148.10128</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>9.69e-05</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>1088.9890135</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>1088.98</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>148.10128</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -1720,46 +1803,49 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" s="2" t="n">
         <v>45962.05966435185</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>0.296</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>2624.2</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>776.7632</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>2.49299</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="J28" t="n">
-        <v>0.296</v>
       </c>
       <c r="K28" t="n">
         <v>0.296</v>
       </c>
       <c r="L28" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="M28" t="n">
         <v>776.7631999999999</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2624.2</v>
       </c>
     </row>
@@ -1767,46 +1853,49 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" s="2" t="n">
         <v>45962.05966435185</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>0.296</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>585.2</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>173.2192</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>0.55594</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="J29" t="n">
-        <v>0.296</v>
       </c>
       <c r="K29" t="n">
         <v>0.296</v>
       </c>
       <c r="L29" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="M29" t="n">
         <v>173.2192</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>585.2</v>
       </c>
     </row>
@@ -1814,46 +1903,49 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" s="2" t="n">
         <v>45962.05902777778</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>109727.81</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>0.01002</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>1099.4726562</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>1.04449902</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>109764.5000986667</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>109727.81</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>1099.4726562</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>0.01002</v>
       </c>
     </row>
@@ -1861,46 +1953,49 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" s="2" t="n">
         <v>45931.03042824074</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>113954.4</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>0.00396</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>451.259424</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>3.834e-05</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>113986.300759</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>113954.4</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>451.259424</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>0.00396</v>
       </c>
     </row>
@@ -1908,46 +2003,49 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" s="2" t="n">
         <v>45931.02980324074</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>0.3329</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>905.7</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>301.50753</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>0.28643215</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>0.3333916683333333</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>0.3329</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>301.50753</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>905.7</v>
       </c>
     </row>
@@ -1955,46 +2053,49 @@
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" s="2" t="n">
         <v>45931.02895833334</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>0.3329</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>452</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>150.4708</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>0.14294726</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>USDC</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>0.3334</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>0.3329</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>150.4708</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>452</v>
       </c>
     </row>
@@ -2002,46 +2103,49 @@
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" s="2" t="n">
         <v>45900.93915509259</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0.3425</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>200.6</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>68.7055</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>5.642e-05</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>0.342961665</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>0.3425</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>68.7055</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>200.6</v>
       </c>
     </row>
@@ -2049,46 +2153,49 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="2" t="n">
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" s="2" t="n">
         <v>45900.93896990741</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>109079.99</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>0.00063</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>68.7203937</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>5.645e-05</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>109075.7142211667</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>109079.99</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>68.7203937</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>0.00063</v>
       </c>
     </row>
@@ -2096,46 +2203,49 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" s="2" t="n">
         <v>45900.93672453704</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>0.34241792</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>2022.6</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>692.57447</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>0.00056949</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>0.3431</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>0.34241792</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>692.574484992</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>2022.6</v>
       </c>
     </row>
@@ -2143,46 +2253,49 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" s="2" t="n">
         <v>45900.93601851852</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>867.28</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>0.019</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>16.47832</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>1.353e-05</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>866.8346673333334</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>867.28</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>16.47832</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>0.019</v>
       </c>
     </row>
@@ -2190,46 +2303,49 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" s="2" t="n">
         <v>45900.93578703704</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>ETHUSDT</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>4462.54</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>0.0693</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>309.254022</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>0.00025404</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>4467.496042999999</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>4462.54</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>309.254022</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>0.0693</v>
       </c>
     </row>
@@ -2237,46 +2353,49 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" s="2" t="n">
         <v>45900.93532407407</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>SOLUSDT</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>204.95</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>1.79</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>366.8605</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>0.0003014</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>205.7853301666667</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>204.95</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>366.8605</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>1.79</v>
       </c>
     </row>
@@ -2284,46 +2403,49 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>841.902968</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>1.648052154152757e-05</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>0.013875</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>3.3e-07</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>894.9224991666665</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>841.902968</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>0.013875</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1.648052154152757e-05</v>
       </c>
     </row>
@@ -2331,46 +2453,49 @@
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B41" t="n">
+        <v>39</v>
+      </c>
+      <c r="C41" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0.024577</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>0.5645522236237132</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>0.013875</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>3.3e-07</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>0.02457696902309403</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>0.000604028167680582</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>0.0003410054451954296</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>0.5645522236237132</v>
       </c>
     </row>
@@ -2378,46 +2503,49 @@
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B42" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>0.015385</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>0.9018524536886579</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>0.013875</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>3.3e-07</v>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>0.01658150016666667</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>0.015385</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>0.013875</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>0.9018524536886579</v>
       </c>
     </row>
@@ -2425,46 +2553,49 @@
       <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
         <v>894.9224991666665</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>2.229999999999999e-06</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>0.001995677173141666</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>4e-08</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J43" t="n">
-        <v>894.9224991666665</v>
       </c>
       <c r="K43" t="n">
         <v>894.9224991666665</v>
       </c>
       <c r="L43" t="n">
+        <v>894.9224991666665</v>
+      </c>
+      <c r="M43" t="n">
         <v>0.001995677173141665</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2.229999999999999e-06</v>
       </c>
     </row>
@@ -2472,46 +2603,49 @@
       <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B44" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>0.163644480872939</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>0.001995677173141666</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>4e-08</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>0.1749</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>0.163644480872939</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>0.001995677173141666</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>0.0121952</v>
       </c>
     </row>
@@ -2519,46 +2653,49 @@
       <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B45" t="n">
+        <v>43</v>
+      </c>
+      <c r="C45" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>3.747533232175975</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>6.02</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>22.56015005769937</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>3.28e-06</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>0.02457696902309403</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>0.09210300816020439</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>0.5544601091244304</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>6.02</v>
       </c>
     </row>
@@ -2566,46 +2703,49 @@
       <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B46" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" s="2" t="n">
         <v>45891.8459375</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
         <v>894.922499</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>0.0252090545079696</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>22.56015005769937</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>3.28e-06</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>894.9224991666665</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>894.922499</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>22.56015005769937</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>0.0252090545079696</v>
       </c>
     </row>
@@ -2613,46 +2753,49 @@
       <c r="A47" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B47" t="n">
+        <v>45</v>
+      </c>
+      <c r="C47" s="2" t="n">
         <v>45891.84428240741</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>0.02457606291472106</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>8718.124</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>214.2571639223396</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>0.00026837</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>0.02457606291472106</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>0.0006039828683883277</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>5.265597540485121</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>8718.124</v>
       </c>
     </row>
@@ -2660,46 +2803,49 @@
       <c r="A48" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="2" t="n">
+      <c r="B48" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" s="2" t="n">
         <v>45891.84428240741</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
         <v>0.3650036864094372</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>586.9999999999999</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>214.2571639223396</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>0.00026837</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>0.3659</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>0.3650036864094372</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>214.2571639223396</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>586.9999999999999</v>
       </c>
     </row>
@@ -2707,46 +2853,49 @@
       <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="2" t="n">
+      <c r="B49" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" s="2" t="n">
         <v>45891.84357638889</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>USDTTRY</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
         <v>0.02458361491986309</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>8724.144000000002</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>214.4709966014341</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>0.00026861</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>0.02458361491986309</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>0.000604354122528115</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>5.272472391928921</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>8724.144000000002</v>
       </c>
     </row>
@@ -2754,46 +2903,49 @@
       <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="2" t="n">
+      <c r="B50" t="n">
+        <v>48</v>
+      </c>
+      <c r="C50" s="2" t="n">
         <v>45891.84357638889</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>0.01676602537534663</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>12792</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>214.4709966014341</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>0.00026861</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>0.01655750016666666</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>0.01676602537534663</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>214.4709966014341</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>12792</v>
       </c>
     </row>
@@ -2801,46 +2953,49 @@
       <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="2" t="n">
+      <c r="B51" t="n">
+        <v>49</v>
+      </c>
+      <c r="C51" s="2" t="n">
         <v>45878.0263425926</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
         <v>794.6106690000001</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>0.01898484</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>1.423e-05</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J51" t="n">
-        <v>794.6106690000001</v>
       </c>
       <c r="K51" t="n">
         <v>794.6106690000001</v>
       </c>
       <c r="L51" t="n">
+        <v>794.6106690000001</v>
+      </c>
+      <c r="M51" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>0.01898484</v>
       </c>
     </row>
@@ -2848,46 +3003,49 @@
       <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" s="2" t="n">
         <v>45878.0263425926</v>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>0.1296010001139</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>116.4</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>1.423e-05</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>0.13021333</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>0.1296010001139</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>15.08555641325796</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>116.4</v>
       </c>
     </row>
@@ -2895,46 +3053,49 @@
       <c r="A53" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="2" t="n">
+      <c r="B53" t="n">
+        <v>51</v>
+      </c>
+      <c r="C53" s="2" t="n">
         <v>45560.6427662037</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
         <v>1.1803</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>57</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>67.2771</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>0.057</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>1.179691675</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>1.1803</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>67.27709999999999</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>56.99999999999999</v>
       </c>
     </row>
@@ -2942,46 +3103,49 @@
       <c r="A54" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B54" t="n">
+        <v>52</v>
+      </c>
+      <c r="C54" s="2" t="n">
         <v>45560.6427662037</v>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
         <v>1.1803</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>34</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>40.1302</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>0.034</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>1.179691675</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>1.1803</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>40.13019999999999</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>34</v>
       </c>
     </row>
@@ -2989,46 +3153,49 @@
       <c r="A55" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B55" t="n">
+        <v>53</v>
+      </c>
+      <c r="C55" s="2" t="n">
         <v>45560.6427662037</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
         <v>1.1802</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>94</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>110.9388</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>0.094</v>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>1.179691675</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>1.1802</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>110.9388</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>94</v>
       </c>
     </row>
@@ -3036,46 +3203,49 @@
       <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" t="n">
+        <v>54</v>
+      </c>
+      <c r="C56" s="2" t="n">
         <v>45560.64236111111</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>0.1508</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>1456.1</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>219.57988</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>0.21957988</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>0.1508000016666667</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>0.1508</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>219.57988</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>1456.1</v>
       </c>
     </row>
@@ -3083,46 +3253,49 @@
       <c r="A57" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="B57" t="n">
+        <v>55</v>
+      </c>
+      <c r="C57" s="2" t="n">
         <v>45553.90638888889</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>60330.29408616667</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>0.00132203</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>79.75845869073494</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>0.073</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
-      </c>
-      <c r="J57" t="n">
-        <v>60330.29408616667</v>
       </c>
       <c r="K57" t="n">
         <v>60330.29408616667</v>
       </c>
       <c r="L57" t="n">
+        <v>60330.29408616667</v>
+      </c>
+      <c r="M57" t="n">
         <v>79.75845869073493</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>0.00132203</v>
       </c>
     </row>
@@ -3130,46 +3303,49 @@
       <c r="A58" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" t="n">
+        <v>56</v>
+      </c>
+      <c r="C58" s="2" t="n">
         <v>45553.90638888889</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>OMUSDT</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
         <v>1.092581625900479</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>73</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>79.75845869073494</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>0.073</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>OM</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>1.091139995</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>1.092581625900479</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>79.75845869073497</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>73</v>
       </c>
     </row>
@@ -3177,46 +3353,49 @@
       <c r="A59" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="2" t="n">
+      <c r="B59" t="n">
+        <v>57</v>
+      </c>
+      <c r="C59" s="2" t="n">
         <v>45529.90896990741</v>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>64353.81012600001</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>0.0025413</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>0.985</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="J59" t="n">
-        <v>64353.81012600001</v>
       </c>
       <c r="K59" t="n">
         <v>64353.81012600001</v>
       </c>
       <c r="L59" t="n">
+        <v>64353.81012600001</v>
+      </c>
+      <c r="M59" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>0.0025413</v>
       </c>
     </row>
@@ -3224,46 +3403,49 @@
       <c r="A60" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" t="n">
+        <v>58</v>
+      </c>
+      <c r="C60" s="2" t="n">
         <v>45529.90896990741</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
         <v>0.16603283012508</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>985</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>0.985</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>0.1655</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>0.16603283012508</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>163.5423376732038</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>985</v>
       </c>
     </row>
@@ -3271,46 +3453,49 @@
       <c r="A61" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="2" t="n">
+      <c r="B61" t="n">
+        <v>59</v>
+      </c>
+      <c r="C61" s="2" t="n">
         <v>45529.90652777778</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
         <v>0.1655</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>453</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>74.97150000000001</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>9.736e-05</v>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>0.1654599983333334</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>0.1655</v>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
         <v>74.97150000000001</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>453</v>
       </c>
     </row>
@@ -3318,46 +3503,49 @@
       <c r="A62" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B62" t="n">
+        <v>60</v>
+      </c>
+      <c r="C62" s="2" t="n">
         <v>45529.90614583333</v>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>0.343</v>
       </c>
-      <c r="F62" t="n">
+      <c r="G62" t="n">
         <v>218.6</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>74.9798</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>9.734999999999999e-05</v>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
         <v>0.3429850016666667</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>0.343</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
         <v>74.9798</v>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
         <v>218.6</v>
       </c>
     </row>
@@ -3365,46 +3553,49 @@
       <c r="A63" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="2" t="n">
+      <c r="B63" t="n">
+        <v>61</v>
+      </c>
+      <c r="C63" s="2" t="n">
         <v>45528.99840277778</v>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>580.5</v>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>0.1015056</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>58.92400079999999</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>0.371</v>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
-      </c>
-      <c r="J63" t="n">
-        <v>580.5</v>
       </c>
       <c r="K63" t="n">
         <v>580.5</v>
       </c>
       <c r="L63" t="n">
+        <v>580.5</v>
+      </c>
+      <c r="M63" t="n">
         <v>58.9240008</v>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
         <v>0.1015056</v>
       </c>
     </row>
@@ -3412,46 +3603,49 @@
       <c r="A64" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="2" t="n">
+      <c r="B64" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" s="2" t="n">
         <v>45528.99840277778</v>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
         <v>0.1588248</v>
       </c>
-      <c r="F64" t="n">
+      <c r="G64" t="n">
         <v>370.9999999999999</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>58.92400079999999</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>0.371</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>TRX</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
         <v>0.1589</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
         <v>0.1588248</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
         <v>58.92400079999998</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
         <v>370.9999999999999</v>
       </c>
     </row>
@@ -3459,46 +3653,49 @@
       <c r="A65" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="2" t="n">
+      <c r="B65" t="n">
+        <v>63</v>
+      </c>
+      <c r="C65" s="2" t="n">
         <v>45500.56033564815</v>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
         <v>68797.23868549999</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>0.00031044</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>2.709e-05</v>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J65" t="n">
-        <v>68797.23868549999</v>
       </c>
       <c r="K65" t="n">
         <v>68797.23868549999</v>
       </c>
       <c r="L65" t="n">
+        <v>68797.23868549999</v>
+      </c>
+      <c r="M65" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
         <v>0.00031044</v>
       </c>
     </row>
@@ -3506,46 +3703,49 @@
       <c r="A66" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" t="n">
+        <v>64</v>
+      </c>
+      <c r="C66" s="2" t="n">
         <v>45500.56033564815</v>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>0.136906504984145</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>156</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>2.709e-05</v>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="K66" t="n">
         <v>0.137311665</v>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
         <v>0.136906504984145</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
         <v>21.35741477752662</v>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
         <v>156</v>
       </c>
     </row>
@@ -3553,46 +3753,49 @@
       <c r="A67" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="B67" s="2" t="n">
+      <c r="B67" t="n">
+        <v>65</v>
+      </c>
+      <c r="C67" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
         <v>68786.2337</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>0.0002774880000000001</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>19.0873544169456</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>2.447e-05</v>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J67" t="n">
-        <v>68786.2337</v>
       </c>
       <c r="K67" t="n">
         <v>68786.2337</v>
       </c>
       <c r="L67" t="n">
+        <v>68786.2337</v>
+      </c>
+      <c r="M67" t="n">
         <v>19.08735441694561</v>
       </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
         <v>0.0002774880000000001</v>
       </c>
     </row>
@@ -3600,46 +3803,49 @@
       <c r="A68" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="B68" s="2" t="n">
+      <c r="B68" t="n">
+        <v>66</v>
+      </c>
+      <c r="C68" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>MKRUSDT</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E68" t="n">
+      <c r="F68" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="F68" t="n">
+      <c r="G68" t="n">
         <v>0.0072</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>19.0873544169456</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>2.447e-05</v>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J68" t="n">
+      <c r="K68" t="n">
         <v>2650.85005</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="L68" t="n">
+      <c r="M68" t="n">
         <v>19.0873544169456</v>
       </c>
-      <c r="M68" t="n">
+      <c r="N68" t="n">
         <v>0.007199999999999999</v>
       </c>
     </row>
@@ -3647,46 +3853,49 @@
       <c r="A69" s="1" t="n">
         <v>67</v>
       </c>
-      <c r="B69" s="2" t="n">
+      <c r="B69" t="n">
+        <v>67</v>
+      </c>
+      <c r="C69" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
         <v>68786.2337</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>0.001452958</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>0.00012672</v>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J69" t="n">
-        <v>68786.2337</v>
       </c>
       <c r="K69" t="n">
         <v>68786.2337</v>
       </c>
       <c r="L69" t="n">
+        <v>68786.2337</v>
+      </c>
+      <c r="M69" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
         <v>0.001452958</v>
       </c>
     </row>
@@ -3694,46 +3903,49 @@
       <c r="A70" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="B70" s="2" t="n">
+      <c r="B70" t="n">
+        <v>68</v>
+      </c>
+      <c r="C70" s="2" t="n">
         <v>45500.55922453704</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>MKRUSDT</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="F70" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="F70" t="n">
+      <c r="G70" t="n">
         <v>0.0377</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>0.00012672</v>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="K70" t="n">
         <v>2650.85005</v>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
         <v>2651.021446798</v>
       </c>
-      <c r="L70" t="n">
+      <c r="M70" t="n">
         <v>99.9435085442846</v>
       </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
         <v>0.0377</v>
       </c>
     </row>
@@ -3741,46 +3953,49 @@
       <c r="A71" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="B71" s="2" t="n">
+      <c r="B71" t="n">
+        <v>69</v>
+      </c>
+      <c r="C71" s="2" t="n">
         <v>45488.03726851852</v>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>OMEUR</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
         <v>1.00660569</v>
       </c>
-      <c r="F71" t="n">
+      <c r="G71" t="n">
         <v>194.71378022</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>200</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>4</v>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" t="n">
         <v>1.0889</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
         <v>1.096092935841</v>
       </c>
-      <c r="L71" t="n">
+      <c r="M71" t="n">
         <v>213.424399010039</v>
       </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
         <v>194.71378022</v>
       </c>
     </row>
@@ -3788,46 +4003,49 @@
       <c r="A72" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="B72" s="2" t="n">
+      <c r="B72" t="n">
+        <v>70</v>
+      </c>
+      <c r="C72" s="2" t="n">
         <v>45479.77708333333</v>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>BNBEUR</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
         <v>485.5</v>
       </c>
-      <c r="F72" t="n">
+      <c r="G72" t="n">
         <v>0.1</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>48.55</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>7.499999999999999e-05</v>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J72" t="n">
+      <c r="K72" t="n">
         <v>1.080199998333333</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>524.4370991908332</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" t="n">
         <v>52.44370991908333</v>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3835,46 +4053,49 @@
       <c r="A73" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="B73" s="2" t="n">
+      <c r="B73" t="n">
+        <v>71</v>
+      </c>
+      <c r="C73" s="2" t="n">
         <v>45479.76871527778</v>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
         <v>0.398</v>
       </c>
-      <c r="F73" t="n">
+      <c r="G73" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>34.0688</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>4.857e-05</v>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
         <v>0.39797001</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
         <v>0.398</v>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" t="n">
         <v>34.0688</v>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
         <v>85.59999999999998</v>
       </c>
     </row>
@@ -3882,46 +4103,49 @@
       <c r="A74" s="1" t="n">
         <v>72</v>
       </c>
-      <c r="B74" s="2" t="n">
+      <c r="B74" t="n">
+        <v>72</v>
+      </c>
+      <c r="C74" s="2" t="n">
         <v>45479.76849537037</v>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="F74" t="n">
         <v>524.6</v>
       </c>
-      <c r="F74" t="n">
+      <c r="G74" t="n">
         <v>0.065</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>34.099</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>4.873e-05</v>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="K74" t="n">
         <v>524.5999999999999</v>
       </c>
-      <c r="K74" t="n">
+      <c r="L74" t="n">
         <v>524.6</v>
       </c>
-      <c r="L74" t="n">
+      <c r="M74" t="n">
         <v>34.099</v>
       </c>
-      <c r="M74" t="n">
+      <c r="N74" t="n">
         <v>0.065</v>
       </c>
     </row>
@@ -3929,46 +4153,49 @@
       <c r="A75" s="1" t="n">
         <v>73</v>
       </c>
-      <c r="B75" s="2" t="n">
+      <c r="B75" t="n">
+        <v>73</v>
+      </c>
+      <c r="C75" s="2" t="n">
         <v>45479.673125</v>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
         <v>0.02414</v>
       </c>
-      <c r="F75" t="n">
+      <c r="G75" t="n">
         <v>1976.8</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>47.719952</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>6.879e-05</v>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
         <v>0.02414200066666666</v>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
         <v>0.02414</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" t="n">
         <v>47.719952</v>
       </c>
-      <c r="M75" t="n">
+      <c r="N75" t="n">
         <v>1976.8</v>
       </c>
     </row>
@@ -3976,46 +4203,49 @@
       <c r="A76" s="1" t="n">
         <v>74</v>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B76" t="n">
+        <v>74</v>
+      </c>
+      <c r="C76" s="2" t="n">
         <v>45479.67239583333</v>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>PEPEUSDT</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E76" t="n">
+      <c r="F76" t="n">
         <v>9.21e-06</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G76" t="n">
         <v>5181574</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>47.72229654</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>6.889e-05</v>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J76" t="n">
+      <c r="K76" t="n">
         <v>9.215000333333332e-06</v>
       </c>
-      <c r="K76" t="n">
+      <c r="L76" t="n">
         <v>9.21e-06</v>
       </c>
-      <c r="L76" t="n">
+      <c r="M76" t="n">
         <v>47.72229654</v>
       </c>
-      <c r="M76" t="n">
+      <c r="N76" t="n">
         <v>5181574</v>
       </c>
     </row>
@@ -4023,46 +4253,49 @@
       <c r="A77" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="B77" s="2" t="n">
+      <c r="B77" t="n">
+        <v>75</v>
+      </c>
+      <c r="C77" s="2" t="n">
         <v>45459.61185185185</v>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>NOTUSDT</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>0.020114</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>2036</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>40.952104</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>0.0409521</v>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
         <v>0.02009346653333333</v>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
         <v>0.020114</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
         <v>40.952104</v>
       </c>
-      <c r="M77" t="n">
+      <c r="N77" t="n">
         <v>2036</v>
       </c>
     </row>
@@ -4070,46 +4303,49 @@
       <c r="A78" s="1" t="n">
         <v>76</v>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B78" t="n">
+        <v>76</v>
+      </c>
+      <c r="C78" s="2" t="n">
         <v>45457.95482638889</v>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>NOTUSDT</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
         <v>0.019619</v>
       </c>
-      <c r="F78" t="n">
+      <c r="G78" t="n">
         <v>88</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>1.726472</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>2.2e-06</v>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J78" t="n">
+      <c r="K78" t="n">
         <v>0.01962085005</v>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" t="n">
         <v>0.019619</v>
       </c>
-      <c r="L78" t="n">
+      <c r="M78" t="n">
         <v>1.726472</v>
       </c>
-      <c r="M78" t="n">
+      <c r="N78" t="n">
         <v>88</v>
       </c>
     </row>
@@ -4117,46 +4353,49 @@
       <c r="A79" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="B79" s="2" t="n">
+      <c r="B79" t="n">
+        <v>77</v>
+      </c>
+      <c r="C79" s="2" t="n">
         <v>45457.95482638889</v>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>NOTUSDT</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
         <v>0.019619</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>1950</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>38.25705</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>1.95</v>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>NOT</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="K79" t="n">
         <v>0.01962085005</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
         <v>0.019619</v>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" t="n">
         <v>38.25705</v>
       </c>
-      <c r="M79" t="n">
+      <c r="N79" t="n">
         <v>1950</v>
       </c>
     </row>
@@ -4164,46 +4403,49 @@
       <c r="A80" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="B80" s="2" t="n">
+      <c r="B80" t="n">
+        <v>78</v>
+      </c>
+      <c r="C80" s="2" t="n">
         <v>45457.95456018519</v>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E80" t="n">
+      <c r="F80" t="n">
         <v>0.5085</v>
       </c>
-      <c r="F80" t="n">
+      <c r="G80" t="n">
         <v>9.5</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>4.83075</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>6.02e-06</v>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J80" t="n">
+      <c r="K80" t="n">
         <v>0.5088133366666666</v>
       </c>
-      <c r="K80" t="n">
+      <c r="L80" t="n">
         <v>0.5085</v>
       </c>
-      <c r="L80" t="n">
+      <c r="M80" t="n">
         <v>4.830749999999999</v>
       </c>
-      <c r="M80" t="n">
+      <c r="N80" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -4211,46 +4453,49 @@
       <c r="A81" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="B81" s="2" t="n">
+      <c r="B81" t="n">
+        <v>79</v>
+      </c>
+      <c r="C81" s="2" t="n">
         <v>45457.95456018519</v>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="F81" t="n">
         <v>0.5086000000000001</v>
       </c>
-      <c r="F81" t="n">
+      <c r="G81" t="n">
         <v>29.8</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>15.15628</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>1.891e-05</v>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
         <v>0.5088133366666666</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
         <v>0.5086000000000001</v>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" t="n">
         <v>15.15628</v>
       </c>
-      <c r="M81" t="n">
+      <c r="N81" t="n">
         <v>29.8</v>
       </c>
     </row>
@@ -4258,46 +4503,49 @@
       <c r="A82" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="B82" s="2" t="n">
+      <c r="B82" t="n">
+        <v>80</v>
+      </c>
+      <c r="C82" s="2" t="n">
         <v>45457.95416666667</v>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>PEPEUSDT</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E82" t="n">
+      <c r="F82" t="n">
         <v>1.145e-05</v>
       </c>
-      <c r="F82" t="n">
+      <c r="G82" t="n">
         <v>1746724</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>19.9999898</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>2.433e-05</v>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J82" t="n">
+      <c r="K82" t="n">
         <v>1.14600005e-05</v>
       </c>
-      <c r="K82" t="n">
+      <c r="L82" t="n">
         <v>1.145e-05</v>
       </c>
-      <c r="L82" t="n">
+      <c r="M82" t="n">
         <v>19.9999898</v>
       </c>
-      <c r="M82" t="n">
+      <c r="N82" t="n">
         <v>1746724</v>
       </c>
     </row>
@@ -4305,46 +4553,49 @@
       <c r="A83" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="B83" s="2" t="n">
+      <c r="B83" t="n">
+        <v>81</v>
+      </c>
+      <c r="C83" s="2" t="n">
         <v>45455.6309837963</v>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
         <v>0.037824</v>
       </c>
-      <c r="F83" t="n">
+      <c r="G83" t="n">
         <v>3465.2</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>131.0677248</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>3.4652</v>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>JASMY</t>
         </is>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" t="n">
         <v>0.03777478451666667</v>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" t="n">
         <v>0.037824</v>
       </c>
-      <c r="L83" t="n">
+      <c r="M83" t="n">
         <v>131.0677248</v>
       </c>
-      <c r="M83" t="n">
+      <c r="N83" t="n">
         <v>3465.2</v>
       </c>
     </row>
@@ -4352,46 +4603,49 @@
       <c r="A84" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="B84" s="2" t="n">
+      <c r="B84" t="n">
+        <v>82</v>
+      </c>
+      <c r="C84" s="2" t="n">
         <v>45455.630625</v>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E84" t="n">
+      <c r="F84" t="n">
         <v>69787.49000000001</v>
       </c>
-      <c r="F84" t="n">
+      <c r="G84" t="n">
         <v>0.00188</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>131.2004812</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>0.13120048</v>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J84" t="n">
+      <c r="K84" t="n">
         <v>69787.75104183334</v>
       </c>
-      <c r="K84" t="n">
+      <c r="L84" t="n">
         <v>69787.49000000001</v>
       </c>
-      <c r="L84" t="n">
+      <c r="M84" t="n">
         <v>131.2004812</v>
       </c>
-      <c r="M84" t="n">
+      <c r="N84" t="n">
         <v>0.00188</v>
       </c>
     </row>
@@ -4399,46 +4653,49 @@
       <c r="A85" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="B85" s="2" t="n">
+      <c r="B85" t="n">
+        <v>83</v>
+      </c>
+      <c r="C85" s="2" t="n">
         <v>45455.03658564815</v>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
         <v>67225.22887250001</v>
       </c>
-      <c r="F85" t="n">
+      <c r="G85" t="n">
         <v>0.0001384</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>1.176e-05</v>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J85" t="n">
-        <v>67225.22887250001</v>
       </c>
       <c r="K85" t="n">
         <v>67225.22887250001</v>
       </c>
       <c r="L85" t="n">
+        <v>67225.22887250001</v>
+      </c>
+      <c r="M85" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="M85" t="n">
+      <c r="N85" t="n">
         <v>0.0001384</v>
       </c>
     </row>
@@ -4446,46 +4703,49 @@
       <c r="A86" s="1" t="n">
         <v>84</v>
       </c>
-      <c r="B86" s="2" t="n">
+      <c r="B86" t="n">
+        <v>84</v>
+      </c>
+      <c r="C86" s="2" t="n">
         <v>45455.03658564815</v>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>TRXUSDT</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E86" t="n">
+      <c r="F86" t="n">
         <v>0.116299645949425</v>
       </c>
-      <c r="F86" t="n">
+      <c r="G86" t="n">
         <v>80</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>1.176e-05</v>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J86" t="n">
+      <c r="K86" t="n">
         <v>0.11652</v>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" t="n">
         <v>0.116299645949425</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
         <v>9.303971675954001</v>
       </c>
-      <c r="M86" t="n">
+      <c r="N86" t="n">
         <v>80</v>
       </c>
     </row>
@@ -4493,46 +4753,49 @@
       <c r="A87" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="B87" s="2" t="n">
+      <c r="B87" t="n">
+        <v>85</v>
+      </c>
+      <c r="C87" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F87" t="n">
+      <c r="G87" t="n">
         <v>0.001252093</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>1.25e-06</v>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J87" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K87" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L87" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M87" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="M87" t="n">
+      <c r="N87" t="n">
         <v>0.001252093</v>
       </c>
     </row>
@@ -4540,46 +4803,49 @@
       <c r="A88" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="B88" s="2" t="n">
+      <c r="B88" t="n">
+        <v>86</v>
+      </c>
+      <c r="C88" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E88" t="n">
+      <c r="F88" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F88" t="n">
+      <c r="G88" t="n">
         <v>0.127</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
         <v>1.25e-06</v>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="K88" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K88" t="n">
+      <c r="L88" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L88" t="n">
+      <c r="M88" t="n">
         <v>86.83509313344669</v>
       </c>
-      <c r="M88" t="n">
+      <c r="N88" t="n">
         <v>0.127</v>
       </c>
     </row>
@@ -4587,46 +4853,49 @@
       <c r="A89" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="B89" s="2" t="n">
+      <c r="B89" t="n">
+        <v>87</v>
+      </c>
+      <c r="C89" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F89" t="n">
+      <c r="G89" t="n">
         <v>0.0029577</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="H89" t="n">
+      <c r="I89" t="n">
         <v>2.96e-06</v>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J89" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K89" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L89" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M89" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="M89" t="n">
+      <c r="N89" t="n">
         <v>0.0029577</v>
       </c>
     </row>
@@ -4634,46 +4903,49 @@
       <c r="A90" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="B90" s="2" t="n">
+      <c r="B90" t="n">
+        <v>88</v>
+      </c>
+      <c r="C90" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E90" t="n">
+      <c r="F90" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F90" t="n">
+      <c r="G90" t="n">
         <v>0.3</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
         <v>2.96e-06</v>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J90" t="n">
+      <c r="K90" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K90" t="n">
+      <c r="L90" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L90" t="n">
+      <c r="M90" t="n">
         <v>205.1222672443623</v>
       </c>
-      <c r="M90" t="n">
+      <c r="N90" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -4681,46 +4953,49 @@
       <c r="A91" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="B91" s="2" t="n">
+      <c r="B91" t="n">
+        <v>89</v>
+      </c>
+      <c r="C91" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F91" t="n">
+      <c r="G91" t="n">
         <v>0.002464749999999999</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="H91" t="n">
+      <c r="I91" t="n">
         <v>2.46e-06</v>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J91" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K91" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L91" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M91" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="M91" t="n">
+      <c r="N91" t="n">
         <v>0.002464749999999999</v>
       </c>
     </row>
@@ -4728,46 +5003,49 @@
       <c r="A92" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="B92" s="2" t="n">
+      <c r="B92" t="n">
+        <v>90</v>
+      </c>
+      <c r="C92" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E92" t="n">
+      <c r="F92" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F92" t="n">
+      <c r="G92" t="n">
         <v>0.25</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>2.46e-06</v>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J92" t="n">
+      <c r="K92" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K92" t="n">
+      <c r="L92" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" t="n">
         <v>170.9352227036352</v>
       </c>
-      <c r="M92" t="n">
+      <c r="N92" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -4775,46 +5053,49 @@
       <c r="A93" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="B93" s="2" t="n">
+      <c r="B93" t="n">
+        <v>91</v>
+      </c>
+      <c r="C93" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F93" t="n">
+      <c r="G93" t="n">
         <v>0.004929499999999999</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="H93" t="n">
+      <c r="I93" t="n">
         <v>0.000375</v>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J93" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K93" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L93" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M93" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="M93" t="n">
+      <c r="N93" t="n">
         <v>0.004929499999999999</v>
       </c>
     </row>
@@ -4822,46 +5103,49 @@
       <c r="A94" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="B94" s="2" t="n">
+      <c r="B94" t="n">
+        <v>92</v>
+      </c>
+      <c r="C94" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E94" t="n">
+      <c r="F94" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F94" t="n">
+      <c r="G94" t="n">
         <v>0.5</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="H94" t="n">
+      <c r="I94" t="n">
         <v>0.000375</v>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J94" t="n">
+      <c r="K94" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K94" t="n">
+      <c r="L94" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L94" t="n">
+      <c r="M94" t="n">
         <v>341.8704454072704</v>
       </c>
-      <c r="M94" t="n">
+      <c r="N94" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4869,46 +5153,49 @@
       <c r="A95" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="B95" s="2" t="n">
+      <c r="B95" t="n">
+        <v>93</v>
+      </c>
+      <c r="C95" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
         <v>69351.95159899999</v>
       </c>
-      <c r="F95" t="n">
+      <c r="G95" t="n">
         <v>0.000808438</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="H95" t="n">
+      <c r="I95" t="n">
         <v>6.161e-05</v>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J95" t="n">
-        <v>69351.95159899999</v>
       </c>
       <c r="K95" t="n">
         <v>69351.95159899999</v>
       </c>
       <c r="L95" t="n">
+        <v>69351.95159899999</v>
+      </c>
+      <c r="M95" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="M95" t="n">
+      <c r="N95" t="n">
         <v>0.000808438</v>
       </c>
     </row>
@@ -4916,46 +5203,49 @@
       <c r="A96" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="B96" s="2" t="n">
+      <c r="B96" t="n">
+        <v>94</v>
+      </c>
+      <c r="C96" s="2" t="n">
         <v>45451.51984953704</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E96" t="n">
+      <c r="F96" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="F96" t="n">
+      <c r="G96" t="n">
         <v>0.082</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="H96" t="n">
+      <c r="I96" t="n">
         <v>6.161e-05</v>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J96" t="n">
+      <c r="K96" t="n">
         <v>682.6583350000001</v>
       </c>
-      <c r="K96" t="n">
+      <c r="L96" t="n">
         <v>683.7408908145409</v>
       </c>
-      <c r="L96" t="n">
+      <c r="M96" t="n">
         <v>56.06675304679236</v>
       </c>
-      <c r="M96" t="n">
+      <c r="N96" t="n">
         <v>0.082</v>
       </c>
     </row>
@@ -4963,46 +5253,49 @@
       <c r="A97" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="B97" s="2" t="n">
+      <c r="B97" t="n">
+        <v>95</v>
+      </c>
+      <c r="C97" s="2" t="n">
         <v>45451.5195949074</v>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
         <v>683.8948187155901</v>
       </c>
-      <c r="F97" t="n">
+      <c r="G97" t="n">
         <v>1.121</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>766.6460917801764</v>
       </c>
-      <c r="H97" t="n">
+      <c r="I97" t="n">
         <v>0.00084075</v>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J97" t="n">
+      <c r="K97" t="n">
         <v>683.7183116666666</v>
       </c>
-      <c r="K97" t="n">
+      <c r="L97" t="n">
         <v>683.8948187155901</v>
       </c>
-      <c r="L97" t="n">
+      <c r="M97" t="n">
         <v>766.6460917801764</v>
       </c>
-      <c r="M97" t="n">
+      <c r="N97" t="n">
         <v>1.121</v>
       </c>
     </row>
@@ -5010,46 +5303,49 @@
       <c r="A98" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="B98" s="2" t="n">
+      <c r="B98" t="n">
+        <v>96</v>
+      </c>
+      <c r="C98" s="2" t="n">
         <v>45451.5195949074</v>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E98" t="n">
+      <c r="F98" t="n">
         <v>69360.5292815</v>
       </c>
-      <c r="F98" t="n">
+      <c r="G98" t="n">
         <v>0.01105306</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>766.6460917801764</v>
       </c>
-      <c r="H98" t="n">
+      <c r="I98" t="n">
         <v>0.00084075</v>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
-      </c>
-      <c r="J98" t="n">
-        <v>69360.5292815</v>
       </c>
       <c r="K98" t="n">
         <v>69360.5292815</v>
       </c>
       <c r="L98" t="n">
+        <v>69360.5292815</v>
+      </c>
+      <c r="M98" t="n">
         <v>766.6460917801763</v>
       </c>
-      <c r="M98" t="n">
+      <c r="N98" t="n">
         <v>0.01105306</v>
       </c>
     </row>
@@ -5057,46 +5353,49 @@
       <c r="A99" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="B99" s="2" t="n">
+      <c r="B99" t="n">
+        <v>97</v>
+      </c>
+      <c r="C99" s="2" t="n">
         <v>45451.50400462963</v>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>BNBUSDT</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E99" t="n">
+      <c r="F99" t="n">
         <v>681.2</v>
       </c>
-      <c r="F99" t="n">
+      <c r="G99" t="n">
         <v>0.015</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>10.218</v>
       </c>
-      <c r="H99" t="n">
+      <c r="I99" t="n">
         <v>1.124e-05</v>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>BNB</t>
         </is>
       </c>
-      <c r="J99" t="n">
+      <c r="K99" t="n">
         <v>681.9633216666666</v>
       </c>
-      <c r="K99" t="n">
+      <c r="L99" t="n">
         <v>681.2</v>
       </c>
-      <c r="L99" t="n">
+      <c r="M99" t="n">
         <v>10.218</v>
       </c>
-      <c r="M99" t="n">
+      <c r="N99" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -5104,46 +5403,49 @@
       <c r="A100" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="B100" s="2" t="n">
+      <c r="B100" t="n">
+        <v>98</v>
+      </c>
+      <c r="C100" s="2" t="n">
         <v>45450.92207175926</v>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
         <v>0.041304</v>
       </c>
-      <c r="F100" t="n">
+      <c r="G100" t="n">
         <v>1210.5</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>49.998492</v>
       </c>
-      <c r="H100" t="n">
+      <c r="I100" t="n">
         <v>1.2105</v>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>JASMY</t>
         </is>
       </c>
-      <c r="J100" t="n">
+      <c r="K100" t="n">
         <v>0.04132561585</v>
       </c>
-      <c r="K100" t="n">
+      <c r="L100" t="n">
         <v>0.041304</v>
       </c>
-      <c r="L100" t="n">
+      <c r="M100" t="n">
         <v>49.998492</v>
       </c>
-      <c r="M100" t="n">
+      <c r="N100" t="n">
         <v>1210.5</v>
       </c>
     </row>
@@ -5151,46 +5453,49 @@
       <c r="A101" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="B101" s="2" t="n">
+      <c r="B101" t="n">
+        <v>99</v>
+      </c>
+      <c r="C101" s="2" t="n">
         <v>45450.92207175926</v>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
         <v>0.041305</v>
       </c>
-      <c r="F101" t="n">
+      <c r="G101" t="n">
         <v>1082.2</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>44.700271</v>
       </c>
-      <c r="H101" t="n">
+      <c r="I101" t="n">
         <v>1.0822</v>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>JASMY</t>
         </is>
       </c>
-      <c r="J101" t="n">
+      <c r="K101" t="n">
         <v>0.04132561585</v>
       </c>
-      <c r="K101" t="n">
+      <c r="L101" t="n">
         <v>0.041305</v>
       </c>
-      <c r="L101" t="n">
+      <c r="M101" t="n">
         <v>44.700271</v>
       </c>
-      <c r="M101" t="n">
+      <c r="N101" t="n">
         <v>1082.2</v>
       </c>
     </row>
@@ -5198,46 +5503,49 @@
       <c r="A102" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B102" s="2" t="n">
+      <c r="B102" t="n">
+        <v>100</v>
+      </c>
+      <c r="C102" s="2" t="n">
         <v>45450.92138888889</v>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>ENSUSDT</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E102" t="n">
+      <c r="F102" t="n">
         <v>21.97</v>
       </c>
-      <c r="F102" t="n">
+      <c r="G102" t="n">
         <v>2.01</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>44.1597</v>
       </c>
-      <c r="H102" t="n">
+      <c r="I102" t="n">
         <v>0.0441597</v>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J102" t="n">
+      <c r="K102" t="n">
         <v>21.95600116666667</v>
       </c>
-      <c r="K102" t="n">
+      <c r="L102" t="n">
         <v>21.97</v>
       </c>
-      <c r="L102" t="n">
+      <c r="M102" t="n">
         <v>44.15969999999999</v>
       </c>
-      <c r="M102" t="n">
+      <c r="N102" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -5245,46 +5553,49 @@
       <c r="A103" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="B103" s="2" t="n">
+      <c r="B103" t="n">
+        <v>101</v>
+      </c>
+      <c r="C103" s="2" t="n">
         <v>45450.92039351852</v>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>ARUSDT</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E103" t="n">
+      <c r="F103" t="n">
         <v>39.245</v>
       </c>
-      <c r="F103" t="n">
+      <c r="G103" t="n">
         <v>1.3</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>51.0185</v>
       </c>
-      <c r="H103" t="n">
+      <c r="I103" t="n">
         <v>0.0510185</v>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>USDT</t>
         </is>
       </c>
-      <c r="J103" t="n">
+      <c r="K103" t="n">
         <v>39.20989994999999</v>
       </c>
-      <c r="K103" t="n">
+      <c r="L103" t="n">
         <v>39.245</v>
       </c>
-      <c r="L103" t="n">
+      <c r="M103" t="n">
         <v>51.0185</v>
       </c>
-      <c r="M103" t="n">
+      <c r="N103" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -5292,46 +5603,49 @@
       <c r="A104" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="B104" s="2" t="n">
+      <c r="B104" t="n">
+        <v>102</v>
+      </c>
+      <c r="C104" s="2" t="n">
         <v>45447.9729050926</v>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
         <v>70502.70711650001</v>
       </c>
-      <c r="F104" t="n">
+      <c r="G104" t="n">
         <v>5.1689e-05</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="H104" t="n">
+      <c r="I104" t="n">
         <v>5e-08</v>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J104" t="n">
-        <v>70502.70711650001</v>
       </c>
       <c r="K104" t="n">
         <v>70502.70711650001</v>
       </c>
       <c r="L104" t="n">
+        <v>70502.70711650001</v>
+      </c>
+      <c r="M104" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="M104" t="n">
+      <c r="N104" t="n">
         <v>5.1689e-05</v>
       </c>
     </row>
@@ -5339,46 +5653,49 @@
       <c r="A105" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="B105" s="2" t="n">
+      <c r="B105" t="n">
+        <v>103</v>
+      </c>
+      <c r="C105" s="2" t="n">
         <v>45447.9729050926</v>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>UMAUSDT</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E105" t="n">
+      <c r="F105" t="n">
         <v>3.312922207404335</v>
       </c>
-      <c r="F105" t="n">
+      <c r="G105" t="n">
         <v>1.1</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="H105" t="n">
+      <c r="I105" t="n">
         <v>5e-08</v>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J105" t="n">
+      <c r="K105" t="n">
         <v>3.312983350000001</v>
       </c>
-      <c r="K105" t="n">
+      <c r="L105" t="n">
         <v>3.312922207404335</v>
       </c>
-      <c r="L105" t="n">
+      <c r="M105" t="n">
         <v>3.644214428144769</v>
       </c>
-      <c r="M105" t="n">
+      <c r="N105" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -5386,46 +5703,49 @@
       <c r="A106" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B106" s="2" t="n">
+      <c r="B106" t="n">
+        <v>104</v>
+      </c>
+      <c r="C106" s="2" t="n">
         <v>45447.94982638889</v>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
         <v>70534.99716683332</v>
       </c>
-      <c r="F106" t="n">
+      <c r="G106" t="n">
         <v>0.0002490470000000001</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>17.56652943940834</v>
       </c>
-      <c r="H106" t="n">
+      <c r="I106" t="n">
         <v>2.5e-07</v>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J106" t="n">
-        <v>70534.99716683332</v>
       </c>
       <c r="K106" t="n">
         <v>70534.99716683332</v>
       </c>
       <c r="L106" t="n">
+        <v>70534.99716683332</v>
+      </c>
+      <c r="M106" t="n">
         <v>17.56652943940835</v>
       </c>
-      <c r="M106" t="n">
+      <c r="N106" t="n">
         <v>0.0002490470000000001</v>
       </c>
     </row>
@@ -5433,46 +5753,49 @@
       <c r="A107" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="B107" s="2" t="n">
+      <c r="B107" t="n">
+        <v>105</v>
+      </c>
+      <c r="C107" s="2" t="n">
         <v>45447.94982638889</v>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>UMAUSDT</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E107" t="n">
+      <c r="F107" t="n">
         <v>3.314439516869498</v>
       </c>
-      <c r="F107" t="n">
+      <c r="G107" t="n">
         <v>5.3</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>17.56652943940834</v>
       </c>
-      <c r="H107" t="n">
+      <c r="I107" t="n">
         <v>2.5e-07</v>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J107" t="n">
+      <c r="K107" t="n">
         <v>3.311750016666666</v>
       </c>
-      <c r="K107" t="n">
+      <c r="L107" t="n">
         <v>3.314439516869498</v>
       </c>
-      <c r="L107" t="n">
+      <c r="M107" t="n">
         <v>17.56652943940834</v>
       </c>
-      <c r="M107" t="n">
+      <c r="N107" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -5480,46 +5803,49 @@
       <c r="A108" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="B108" s="2" t="n">
+      <c r="B108" t="n">
+        <v>106</v>
+      </c>
+      <c r="C108" s="2" t="n">
         <v>45446.50150462963</v>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>ETHUSDT</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
         <v>3810.458332166667</v>
       </c>
-      <c r="F108" t="n">
+      <c r="G108" t="n">
         <v>0.01363</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="H108" t="n">
+      <c r="I108" t="n">
         <v>1.363e-05</v>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
-      </c>
-      <c r="J108" t="n">
-        <v>3810.458332166667</v>
       </c>
       <c r="K108" t="n">
         <v>3810.458332166667</v>
       </c>
       <c r="L108" t="n">
+        <v>3810.458332166667</v>
+      </c>
+      <c r="M108" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="M108" t="n">
+      <c r="N108" t="n">
         <v>0.01363</v>
       </c>
     </row>
@@ -5527,46 +5853,49 @@
       <c r="A109" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="B109" s="2" t="n">
+      <c r="B109" t="n">
+        <v>107</v>
+      </c>
+      <c r="C109" s="2" t="n">
         <v>45446.50150462963</v>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>XRPUSDT</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E109" t="n">
+      <c r="F109" t="n">
         <v>0.5193654706743167</v>
       </c>
-      <c r="F109" t="n">
+      <c r="G109" t="n">
         <v>100</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="H109" t="n">
+      <c r="I109" t="n">
         <v>1.363e-05</v>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="J109" t="n">
+      <c r="K109" t="n">
         <v>0.5193833316666667</v>
       </c>
-      <c r="K109" t="n">
+      <c r="L109" t="n">
         <v>0.5193654706743167</v>
       </c>
-      <c r="L109" t="n">
+      <c r="M109" t="n">
         <v>51.93654706743167</v>
       </c>
-      <c r="M109" t="n">
+      <c r="N109" t="n">
         <v>100</v>
       </c>
     </row>
@@ -5574,46 +5903,49 @@
       <c r="A110" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="B110" s="2" t="n">
+      <c r="B110" t="n">
+        <v>108</v>
+      </c>
+      <c r="C110" s="2" t="n">
         <v>45446.49649305556</v>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
         <v>69129.98950016667</v>
       </c>
-      <c r="F110" t="n">
+      <c r="G110" t="n">
         <v>0.00069092</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="H110" t="n">
+      <c r="I110" t="n">
         <v>6.9e-07</v>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J110" t="n">
-        <v>69129.98950016667</v>
       </c>
       <c r="K110" t="n">
         <v>69129.98950016667</v>
       </c>
       <c r="L110" t="n">
+        <v>69129.98950016667</v>
+      </c>
+      <c r="M110" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="M110" t="n">
+      <c r="N110" t="n">
         <v>0.00069092</v>
       </c>
     </row>
@@ -5621,46 +5953,49 @@
       <c r="A111" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B111" s="2" t="n">
+      <c r="B111" t="n">
+        <v>109</v>
+      </c>
+      <c r="C111" s="2" t="n">
         <v>45446.49649305556</v>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>XRPUSDT</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E111" t="n">
+      <c r="F111" t="n">
         <v>0.5191662211462518</v>
       </c>
-      <c r="F111" t="n">
+      <c r="G111" t="n">
         <v>92</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="H111" t="n">
+      <c r="I111" t="n">
         <v>6.9e-07</v>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J111" t="n">
+      <c r="K111" t="n">
         <v>0.5193049983333333</v>
       </c>
-      <c r="K111" t="n">
+      <c r="L111" t="n">
         <v>0.5191662211462518</v>
       </c>
-      <c r="L111" t="n">
+      <c r="M111" t="n">
         <v>47.76329234545516</v>
       </c>
-      <c r="M111" t="n">
+      <c r="N111" t="n">
         <v>92</v>
       </c>
     </row>
@@ -5668,46 +6003,49 @@
       <c r="A112" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="B112" s="2" t="n">
+      <c r="B112" t="n">
+        <v>110</v>
+      </c>
+      <c r="C112" s="2" t="n">
         <v>45446.42081018518</v>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
         <v>69115.08947183334</v>
       </c>
-      <c r="F112" t="n">
+      <c r="G112" t="n">
         <v>0.0006642089999999999</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="H112" t="n">
+      <c r="I112" t="n">
         <v>6.6e-07</v>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J112" t="n">
-        <v>69115.08947183334</v>
       </c>
       <c r="K112" t="n">
         <v>69115.08947183334</v>
       </c>
       <c r="L112" t="n">
+        <v>69115.08947183334</v>
+      </c>
+      <c r="M112" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="M112" t="n">
+      <c r="N112" t="n">
         <v>0.0006642089999999999</v>
       </c>
     </row>
@@ -5715,46 +6053,49 @@
       <c r="A113" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="B113" s="2" t="n">
+      <c r="B113" t="n">
+        <v>111</v>
+      </c>
+      <c r="C113" s="2" t="n">
         <v>45446.42081018518</v>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>NEARUSDT</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E113" t="n">
+      <c r="F113" t="n">
         <v>7.28680388301539</v>
       </c>
-      <c r="F113" t="n">
+      <c r="G113" t="n">
         <v>6.3</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="H113" t="n">
+      <c r="I113" t="n">
         <v>6.6e-07</v>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J113" t="n">
+      <c r="K113" t="n">
         <v>7.287033316666666</v>
       </c>
-      <c r="K113" t="n">
+      <c r="L113" t="n">
         <v>7.28680388301539</v>
       </c>
-      <c r="L113" t="n">
+      <c r="M113" t="n">
         <v>45.90686446299695</v>
       </c>
-      <c r="M113" t="n">
+      <c r="N113" t="n">
         <v>6.299999999999999</v>
       </c>
     </row>
@@ -5762,46 +6103,49 @@
       <c r="A114" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="B114" s="2" t="n">
+      <c r="B114" t="n">
+        <v>112</v>
+      </c>
+      <c r="C114" s="2" t="n">
         <v>45442.00921296296</v>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
         <v>67749.86920016666</v>
       </c>
-      <c r="F114" t="n">
+      <c r="G114" t="n">
         <v>0.00093258</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="H114" t="n">
+      <c r="I114" t="n">
         <v>9.3e-07</v>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J114" t="n">
-        <v>67749.86920016666</v>
       </c>
       <c r="K114" t="n">
         <v>67749.86920016666</v>
       </c>
       <c r="L114" t="n">
+        <v>67749.86920016666</v>
+      </c>
+      <c r="M114" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="M114" t="n">
+      <c r="N114" t="n">
         <v>0.00093258</v>
       </c>
     </row>
@@ -5809,46 +6153,49 @@
       <c r="A115" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="B115" s="2" t="n">
+      <c r="B115" t="n">
+        <v>113</v>
+      </c>
+      <c r="C115" s="2" t="n">
         <v>45442.00921296296</v>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>LPTUSDT</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E115" t="n">
+      <c r="F115" t="n">
         <v>21.27345892885233</v>
       </c>
-      <c r="F115" t="n">
+      <c r="G115" t="n">
         <v>2.97</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="H115" t="n">
+      <c r="I115" t="n">
         <v>9.3e-07</v>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J115" t="n">
+      <c r="K115" t="n">
         <v>21.26066758333333</v>
       </c>
-      <c r="K115" t="n">
+      <c r="L115" t="n">
         <v>21.27345892885233</v>
       </c>
-      <c r="L115" t="n">
+      <c r="M115" t="n">
         <v>63.18217301869143</v>
       </c>
-      <c r="M115" t="n">
+      <c r="N115" t="n">
         <v>2.97</v>
       </c>
     </row>
@@ -5856,46 +6203,49 @@
       <c r="A116" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="B116" s="2" t="n">
+      <c r="B116" t="n">
+        <v>114</v>
+      </c>
+      <c r="C116" s="2" t="n">
         <v>45441.90847222223</v>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
         <v>67695.03782550001</v>
       </c>
-      <c r="F116" t="n">
+      <c r="G116" t="n">
         <v>0.0007335899999999999</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="H116" t="n">
+      <c r="I116" t="n">
         <v>7.3e-07</v>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J116" t="n">
-        <v>67695.03782550001</v>
       </c>
       <c r="K116" t="n">
         <v>67695.03782550001</v>
       </c>
       <c r="L116" t="n">
+        <v>67695.03782550001</v>
+      </c>
+      <c r="M116" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="M116" t="n">
+      <c r="N116" t="n">
         <v>0.0007335899999999999</v>
       </c>
     </row>
@@ -5903,46 +6253,49 @@
       <c r="A117" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="B117" s="2" t="n">
+      <c r="B117" t="n">
+        <v>115</v>
+      </c>
+      <c r="C117" s="2" t="n">
         <v>45441.90847222223</v>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>NEARUSDT</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E117" t="n">
+      <c r="F117" t="n">
         <v>7.640061968985931</v>
       </c>
-      <c r="F117" t="n">
+      <c r="G117" t="n">
         <v>6.5</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="H117" t="n">
+      <c r="I117" t="n">
         <v>7.3e-07</v>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J117" t="n">
+      <c r="K117" t="n">
         <v>7.64060005</v>
       </c>
-      <c r="K117" t="n">
+      <c r="L117" t="n">
         <v>7.640061968985931</v>
       </c>
-      <c r="L117" t="n">
+      <c r="M117" t="n">
         <v>49.66040279840855</v>
       </c>
-      <c r="M117" t="n">
+      <c r="N117" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -5950,46 +6303,49 @@
       <c r="A118" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="B118" s="2" t="n">
+      <c r="B118" t="n">
+        <v>116</v>
+      </c>
+      <c r="C118" s="2" t="n">
         <v>45440.88619212963</v>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
         <v>64131.08918148</v>
       </c>
-      <c r="F118" t="n">
+      <c r="G118" t="n">
         <v>0.00076406</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>50</v>
       </c>
-      <c r="H118" t="n">
+      <c r="I118" t="n">
         <v>1</v>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J118" t="n">
+      <c r="K118" t="n">
         <v>1.086388331666667</v>
       </c>
-      <c r="K118" t="n">
+      <c r="L118" t="n">
         <v>69671.26698383428</v>
       </c>
-      <c r="L118" t="n">
+      <c r="M118" t="n">
         <v>53.23302825166842</v>
       </c>
-      <c r="M118" t="n">
+      <c r="N118" t="n">
         <v>0.00076406</v>
       </c>
     </row>
@@ -5997,46 +6353,49 @@
       <c r="A119" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="B119" s="2" t="n">
+      <c r="B119" t="n">
+        <v>117</v>
+      </c>
+      <c r="C119" s="2" t="n">
         <v>45439.96682870371</v>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
         <v>69531.81351050001</v>
       </c>
-      <c r="F119" t="n">
+      <c r="G119" t="n">
         <v>0.0004004640000000001</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="H119" t="n">
+      <c r="I119" t="n">
         <v>4e-07</v>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J119" t="n">
-        <v>69531.81351050001</v>
       </c>
       <c r="K119" t="n">
         <v>69531.81351050001</v>
       </c>
       <c r="L119" t="n">
+        <v>69531.81351050001</v>
+      </c>
+      <c r="M119" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="M119" t="n">
+      <c r="N119" t="n">
         <v>0.0004004640000000001</v>
       </c>
     </row>
@@ -6044,46 +6403,49 @@
       <c r="A120" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="B120" s="2" t="n">
+      <c r="B120" t="n">
+        <v>118</v>
+      </c>
+      <c r="C120" s="2" t="n">
         <v>45439.96682870371</v>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>INJUSDT</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="E120" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E120" t="n">
+      <c r="F120" t="n">
         <v>25.7823964496934</v>
       </c>
-      <c r="F120" t="n">
+      <c r="G120" t="n">
         <v>1.08</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="H120" t="n">
+      <c r="I120" t="n">
         <v>4e-07</v>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J120" t="n">
+      <c r="K120" t="n">
         <v>25.7770005</v>
       </c>
-      <c r="K120" t="n">
+      <c r="L120" t="n">
         <v>25.7823964496934</v>
       </c>
-      <c r="L120" t="n">
+      <c r="M120" t="n">
         <v>27.84498816566888</v>
       </c>
-      <c r="M120" t="n">
+      <c r="N120" t="n">
         <v>1.08</v>
       </c>
     </row>
@@ -6091,46 +6453,49 @@
       <c r="A121" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="B121" s="2" t="n">
+      <c r="B121" t="n">
+        <v>119</v>
+      </c>
+      <c r="C121" s="2" t="n">
         <v>45439.96547453704</v>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>BTCUSDT</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
         <v>69520.8794125</v>
       </c>
-      <c r="F121" t="n">
+      <c r="G121" t="n">
         <v>0.000231</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="H121" t="n">
+      <c r="I121" t="n">
         <v>2.3e-07</v>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
-      </c>
-      <c r="J121" t="n">
-        <v>69520.8794125</v>
       </c>
       <c r="K121" t="n">
         <v>69520.8794125</v>
       </c>
       <c r="L121" t="n">
+        <v>69520.8794125</v>
+      </c>
+      <c r="M121" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="M121" t="n">
+      <c r="N121" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -6138,46 +6503,49 @@
       <c r="A122" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="B122" s="2" t="n">
+      <c r="B122" t="n">
+        <v>120</v>
+      </c>
+      <c r="C122" s="2" t="n">
         <v>45439.96547453704</v>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>FETUSDT</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E122" t="n">
+      <c r="F122" t="n">
         <v>2.2941890206125</v>
       </c>
-      <c r="F122" t="n">
+      <c r="G122" t="n">
         <v>7</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="H122" t="n">
+      <c r="I122" t="n">
         <v>2.3e-07</v>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="J122" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="J122" t="n">
+      <c r="K122" t="n">
         <v>2.2945667</v>
       </c>
-      <c r="K122" t="n">
+      <c r="L122" t="n">
         <v>2.2941890206125</v>
       </c>
-      <c r="L122" t="n">
+      <c r="M122" t="n">
         <v>16.0593231442875</v>
       </c>
-      <c r="M122" t="n">
+      <c r="N122" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6185,46 +6553,49 @@
       <c r="A123" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="B123" s="2" t="n">
+      <c r="B123" t="n">
+        <v>121</v>
+      </c>
+      <c r="C123" s="2" t="n">
         <v>45438.41358796296</v>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
         <v>64764.05726993</v>
       </c>
-      <c r="F123" t="n">
+      <c r="G123" t="n">
         <v>0.00302637</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>200</v>
       </c>
-      <c r="H123" t="n">
+      <c r="I123" t="n">
         <v>4</v>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="J123" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J123" t="n">
+      <c r="K123" t="n">
         <v>1.084943331666667</v>
       </c>
-      <c r="K123" t="n">
+      <c r="L123" t="n">
         <v>70265.33206668869</v>
       </c>
-      <c r="L123" t="n">
+      <c r="M123" t="n">
         <v>212.6488930066647</v>
       </c>
-      <c r="M123" t="n">
+      <c r="N123" t="n">
         <v>0.00302637</v>
       </c>
     </row>
@@ -6232,46 +6603,49 @@
       <c r="A124" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="B124" s="2" t="n">
+      <c r="B124" t="n">
+        <v>122</v>
+      </c>
+      <c r="C124" s="2" t="n">
         <v>45438.06670138889</v>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>ENSEUR</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
         <v>21.88048003</v>
       </c>
-      <c r="F124" t="n">
+      <c r="G124" t="n">
         <v>3.35870145</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>75</v>
       </c>
-      <c r="H124" t="n">
+      <c r="I124" t="n">
         <v>1</v>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="J124" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J124" t="n">
+      <c r="K124" t="n">
         <v>1.084505001666667</v>
       </c>
-      <c r="K124" t="n">
+      <c r="L124" t="n">
         <v>23.72949003140263</v>
       </c>
-      <c r="L124" t="n">
+      <c r="M124" t="n">
         <v>79.70027257623255</v>
       </c>
-      <c r="M124" t="n">
+      <c r="N124" t="n">
         <v>3.35870145</v>
       </c>
     </row>
@@ -6279,46 +6653,49 @@
       <c r="A125" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="B125" s="2" t="n">
+      <c r="B125" t="n">
+        <v>123</v>
+      </c>
+      <c r="C125" s="2" t="n">
         <v>45438.06428240741</v>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>LPTEUR</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
         <v>21.40068094</v>
       </c>
-      <c r="F125" t="n">
+      <c r="G125" t="n">
         <v>4.57929354</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>100</v>
       </c>
-      <c r="H125" t="n">
+      <c r="I125" t="n">
         <v>2</v>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="J125" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J125" t="n">
+      <c r="K125" t="n">
         <v>1.084456668333333</v>
       </c>
-      <c r="K125" t="n">
+      <c r="L125" t="n">
         <v>23.20811115225706</v>
       </c>
-      <c r="L125" t="n">
+      <c r="M125" t="n">
         <v>106.2767534751327</v>
       </c>
-      <c r="M125" t="n">
+      <c r="N125" t="n">
         <v>4.57929354</v>
       </c>
     </row>
@@ -6326,46 +6703,49 @@
       <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="B126" s="2" t="n">
+      <c r="B126" t="n">
+        <v>124</v>
+      </c>
+      <c r="C126" s="2" t="n">
         <v>45438.06288194445</v>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>JASMYEUR</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
         <v>0.02039718</v>
       </c>
-      <c r="F126" t="n">
+      <c r="G126" t="n">
         <v>4804.58606935</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>100</v>
       </c>
-      <c r="H126" t="n">
+      <c r="I126" t="n">
         <v>2</v>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="J126" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J126" t="n">
+      <c r="K126" t="n">
         <v>1.084644998333333</v>
       </c>
-      <c r="K126" t="n">
+      <c r="L126" t="n">
         <v>0.0221236992671047</v>
       </c>
-      <c r="L126" t="n">
+      <c r="M126" t="n">
         <v>106.29521730122</v>
       </c>
-      <c r="M126" t="n">
+      <c r="N126" t="n">
         <v>4804.58606935</v>
       </c>
     </row>
@@ -6373,46 +6753,49 @@
       <c r="A127" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="B127" s="2" t="n">
+      <c r="B127" t="n">
+        <v>125</v>
+      </c>
+      <c r="C127" s="2" t="n">
         <v>45438.01670138889</v>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>BBEUR</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
         <v>0.5091575699999999</v>
       </c>
-      <c r="F127" t="n">
+      <c r="G127" t="n">
         <v>288.7121952</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>150</v>
       </c>
-      <c r="H127" t="n">
+      <c r="I127" t="n">
         <v>3</v>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="J127" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J127" t="n">
+      <c r="K127" t="n">
         <v>1.084505001666667</v>
       </c>
-      <c r="K127" t="n">
+      <c r="L127" t="n">
         <v>0.5521839313014461</v>
       </c>
-      <c r="L127" t="n">
+      <c r="M127" t="n">
         <v>159.4222349602065</v>
       </c>
-      <c r="M127" t="n">
+      <c r="N127" t="n">
         <v>288.7121952</v>
       </c>
     </row>
@@ -6420,46 +6803,49 @@
       <c r="A128" s="1" t="n">
         <v>126</v>
       </c>
-      <c r="B128" s="2" t="n">
+      <c r="B128" t="n">
+        <v>126</v>
+      </c>
+      <c r="C128" s="2" t="n">
         <v>45438.01179398148</v>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>XRPEUR</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
         <v>0.50817649</v>
       </c>
-      <c r="F128" t="n">
+      <c r="G128" t="n">
         <v>192.84638819</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>100</v>
       </c>
-      <c r="H128" t="n">
+      <c r="I128" t="n">
         <v>2</v>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="J128" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J128" t="n">
+      <c r="K128" t="n">
         <v>1.0845</v>
       </c>
-      <c r="K128" t="n">
+      <c r="L128" t="n">
         <v>0.551117403405</v>
       </c>
-      <c r="L128" t="n">
+      <c r="M128" t="n">
         <v>106.2810007153055</v>
       </c>
-      <c r="M128" t="n">
+      <c r="N128" t="n">
         <v>192.84638819</v>
       </c>
     </row>
@@ -6467,46 +6853,49 @@
       <c r="A129" s="1" t="n">
         <v>127</v>
       </c>
-      <c r="B129" s="2" t="n">
+      <c r="B129" t="n">
+        <v>127</v>
+      </c>
+      <c r="C129" s="2" t="n">
         <v>45437.93450231481</v>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>PEPEEUR</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
         <v>1.414e-05</v>
       </c>
-      <c r="F129" t="n">
+      <c r="G129" t="n">
         <v>6928298.24</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>100</v>
       </c>
-      <c r="H129" t="n">
+      <c r="I129" t="n">
         <v>2</v>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J129" t="n">
+      <c r="K129" t="n">
         <v>1.0845</v>
       </c>
-      <c r="K129" t="n">
+      <c r="L129" t="n">
         <v>1.533483e-05</v>
       </c>
-      <c r="L129" t="n">
+      <c r="M129" t="n">
         <v>106.2442756996992</v>
       </c>
-      <c r="M129" t="n">
+      <c r="N129" t="n">
         <v>6928298.24</v>
       </c>
     </row>
@@ -6514,46 +6903,49 @@
       <c r="A130" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="B130" s="2" t="n">
+      <c r="B130" t="n">
+        <v>128</v>
+      </c>
+      <c r="C130" s="2" t="n">
         <v>45437.92731481481</v>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>NEAREUR</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
         <v>7.62742061</v>
       </c>
-      <c r="F130" t="n">
+      <c r="G130" t="n">
         <v>12.8483802</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>100</v>
       </c>
-      <c r="H130" t="n">
+      <c r="I130" t="n">
         <v>2</v>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="J130" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J130" t="n">
+      <c r="K130" t="n">
         <v>1.0846</v>
       </c>
-      <c r="K130" t="n">
+      <c r="L130" t="n">
         <v>8.272700393606</v>
       </c>
-      <c r="L130" t="n">
+      <c r="M130" t="n">
         <v>106.2907999377395</v>
       </c>
-      <c r="M130" t="n">
+      <c r="N130" t="n">
         <v>12.8483802</v>
       </c>
     </row>
@@ -6561,46 +6953,49 @@
       <c r="A131" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="B131" s="2" t="n">
+      <c r="B131" t="n">
+        <v>129</v>
+      </c>
+      <c r="C131" s="2" t="n">
         <v>45436.94775462963</v>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>MKREUR</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
         <v>2571.01241222</v>
       </c>
-      <c r="F131" t="n">
+      <c r="G131" t="n">
         <v>0.03811728</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>100</v>
       </c>
-      <c r="H131" t="n">
+      <c r="I131" t="n">
         <v>2</v>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="J131" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J131" t="n">
+      <c r="K131" t="n">
         <v>1.084</v>
       </c>
-      <c r="K131" t="n">
+      <c r="L131" t="n">
         <v>2786.97745484648</v>
       </c>
-      <c r="L131" t="n">
+      <c r="M131" t="n">
         <v>106.2320000000707</v>
       </c>
-      <c r="M131" t="n">
+      <c r="N131" t="n">
         <v>0.03811728</v>
       </c>
     </row>
@@ -6608,46 +7003,49 @@
       <c r="A132" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="B132" s="2" t="n">
+      <c r="B132" t="n">
+        <v>130</v>
+      </c>
+      <c r="C132" s="2" t="n">
         <v>45436.93561342593</v>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>ETHEUR</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
         <v>3502.04619556</v>
       </c>
-      <c r="F132" t="n">
+      <c r="G132" t="n">
         <v>0.04197546</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>150</v>
       </c>
-      <c r="H132" t="n">
+      <c r="I132" t="n">
         <v>3</v>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="J132" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J132" t="n">
+      <c r="K132" t="n">
         <v>1.084</v>
       </c>
-      <c r="K132" t="n">
+      <c r="L132" t="n">
         <v>3796.21807598704</v>
       </c>
-      <c r="L132" t="n">
+      <c r="M132" t="n">
         <v>159.347999999871</v>
       </c>
-      <c r="M132" t="n">
+      <c r="N132" t="n">
         <v>0.04197546</v>
       </c>
     </row>
@@ -6655,46 +7053,49 @@
       <c r="A133" s="1" t="n">
         <v>131</v>
       </c>
-      <c r="B133" s="2" t="n">
+      <c r="B133" t="n">
+        <v>131</v>
+      </c>
+      <c r="C133" s="2" t="n">
         <v>45436.93466435185</v>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
         <v>157.11043262</v>
       </c>
-      <c r="F133" t="n">
+      <c r="G133" t="n">
         <v>0.62376507</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>100</v>
       </c>
-      <c r="H133" t="n">
+      <c r="I133" t="n">
         <v>2</v>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="J133" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J133" t="n">
+      <c r="K133" t="n">
         <v>1.084108331666667</v>
       </c>
-      <c r="K133" t="n">
+      <c r="L133" t="n">
         <v>170.3247289950965</v>
       </c>
-      <c r="L133" t="n">
+      <c r="M133" t="n">
         <v>106.2426165043574</v>
       </c>
-      <c r="M133" t="n">
+      <c r="N133" t="n">
         <v>0.62376507</v>
       </c>
     </row>
@@ -6702,46 +7103,49 @@
       <c r="A134" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="B134" s="2" t="n">
+      <c r="B134" t="n">
+        <v>132</v>
+      </c>
+      <c r="C134" s="2" t="n">
         <v>45436.43322916667</v>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
         <v>63003.06014864</v>
       </c>
-      <c r="F134" t="n">
+      <c r="G134" t="n">
         <v>0.00155548</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>100</v>
       </c>
-      <c r="H134" t="n">
+      <c r="I134" t="n">
         <v>2</v>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="J134" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J134" t="n">
+      <c r="K134" t="n">
         <v>1.0829</v>
       </c>
-      <c r="K134" t="n">
+      <c r="L134" t="n">
         <v>68226.01383496226</v>
       </c>
-      <c r="L134" t="n">
+      <c r="M134" t="n">
         <v>106.1242000000071</v>
       </c>
-      <c r="M134" t="n">
+      <c r="N134" t="n">
         <v>0.00155548</v>
       </c>
     </row>
@@ -6749,46 +7153,49 @@
       <c r="A135" s="1" t="n">
         <v>133</v>
       </c>
-      <c r="B135" s="2" t="n">
+      <c r="B135" t="n">
+        <v>133</v>
+      </c>
+      <c r="C135" s="2" t="n">
         <v>45426.64160879629</v>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E135" t="n">
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
         <v>57930.57788707</v>
       </c>
-      <c r="F135" t="n">
+      <c r="G135" t="n">
         <v>0.00084584</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>50</v>
       </c>
-      <c r="H135" t="n">
+      <c r="I135" t="n">
         <v>1</v>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="J135" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J135" t="n">
+      <c r="K135" t="n">
         <v>1.0814</v>
       </c>
-      <c r="K135" t="n">
+      <c r="L135" t="n">
         <v>62646.12692707749</v>
       </c>
-      <c r="L135" t="n">
+      <c r="M135" t="n">
         <v>52.98859999999923</v>
       </c>
-      <c r="M135" t="n">
+      <c r="N135" t="n">
         <v>0.00084584</v>
       </c>
     </row>
@@ -6796,46 +7203,49 @@
       <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="B136" s="2" t="n">
+      <c r="B136" t="n">
+        <v>134</v>
+      </c>
+      <c r="C136" s="2" t="n">
         <v>45425.85847222222</v>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E136" t="n">
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
         <v>140.23996862</v>
       </c>
-      <c r="F136" t="n">
+      <c r="G136" t="n">
         <v>0.69880221</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>100</v>
       </c>
-      <c r="H136" t="n">
+      <c r="I136" t="n">
         <v>2</v>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="J136" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J136" t="n">
+      <c r="K136" t="n">
         <v>1.078779998333333</v>
       </c>
-      <c r="K136" t="n">
+      <c r="L136" t="n">
         <v>151.2880731141503</v>
       </c>
-      <c r="L136" t="n">
+      <c r="M136" t="n">
         <v>105.7204398388098</v>
       </c>
-      <c r="M136" t="n">
+      <c r="N136" t="n">
         <v>0.69880221</v>
       </c>
     </row>
@@ -6843,46 +7253,49 @@
       <c r="A137" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="B137" s="2" t="n">
+      <c r="B137" t="n">
+        <v>135</v>
+      </c>
+      <c r="C137" s="2" t="n">
         <v>45422.83993055556</v>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>RNDREUR</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
         <v>10.58084967</v>
       </c>
-      <c r="F137" t="n">
+      <c r="G137" t="n">
         <v>1.85240322</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>20</v>
       </c>
-      <c r="H137" t="n">
+      <c r="I137" t="n">
         <v>0.4</v>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J137" t="n">
+      <c r="K137" t="n">
         <v>1.076449998333333</v>
       </c>
-      <c r="K137" t="n">
+      <c r="L137" t="n">
         <v>11.38975560963675</v>
       </c>
-      <c r="L137" t="n">
+      <c r="M137" t="n">
         <v>21.09841996630417</v>
       </c>
-      <c r="M137" t="n">
+      <c r="N137" t="n">
         <v>1.85240322</v>
       </c>
     </row>
@@ -6890,46 +7303,49 @@
       <c r="A138" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="B138" s="2" t="n">
+      <c r="B138" t="n">
+        <v>136</v>
+      </c>
+      <c r="C138" s="2" t="n">
         <v>45422.83865740741</v>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>ETHEUR</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
         <v>2752.33311287</v>
       </c>
-      <c r="F138" t="n">
+      <c r="G138" t="n">
         <v>0.00533729</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>15</v>
       </c>
-      <c r="H138" t="n">
+      <c r="I138" t="n">
         <v>0.31</v>
       </c>
-      <c r="I138" t="inlineStr">
+      <c r="J138" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J138" t="n">
+      <c r="K138" t="n">
         <v>1.0764</v>
       </c>
-      <c r="K138" t="n">
+      <c r="L138" t="n">
         <v>2962.611362693268</v>
       </c>
-      <c r="L138" t="n">
+      <c r="M138" t="n">
         <v>15.81231599998915</v>
       </c>
-      <c r="M138" t="n">
+      <c r="N138" t="n">
         <v>0.00533729</v>
       </c>
     </row>
@@ -6937,46 +7353,49 @@
       <c r="A139" s="1" t="n">
         <v>137</v>
       </c>
-      <c r="B139" s="2" t="n">
+      <c r="B139" t="n">
+        <v>137</v>
+      </c>
+      <c r="C139" s="2" t="n">
         <v>45422.83754629629</v>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
         <v>57425.23976014</v>
       </c>
-      <c r="F139" t="n">
+      <c r="G139" t="n">
         <v>0.00051197</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>30</v>
       </c>
-      <c r="H139" t="n">
+      <c r="I139" t="n">
         <v>0.6</v>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="J139" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J139" t="n">
+      <c r="K139" t="n">
         <v>1.0764</v>
       </c>
-      <c r="K139" t="n">
+      <c r="L139" t="n">
         <v>61812.5280778147</v>
       </c>
-      <c r="L139" t="n">
+      <c r="M139" t="n">
         <v>31.64615999999879</v>
       </c>
-      <c r="M139" t="n">
+      <c r="N139" t="n">
         <v>0.00051197</v>
       </c>
     </row>
@@ -6984,46 +7403,49 @@
       <c r="A140" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="B140" s="2" t="n">
+      <c r="B140" t="n">
+        <v>138</v>
+      </c>
+      <c r="C140" s="2" t="n">
         <v>45422.83584490741</v>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>FETEUR</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
         <v>2.10457801</v>
       </c>
-      <c r="F140" t="n">
+      <c r="G140" t="n">
         <v>6.98002161</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>15</v>
       </c>
-      <c r="H140" t="n">
+      <c r="I140" t="n">
         <v>0.31</v>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="J140" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J140" t="n">
+      <c r="K140" t="n">
         <v>1.076438331666667</v>
       </c>
-      <c r="K140" t="n">
+      <c r="L140" t="n">
         <v>2.265448441946754</v>
       </c>
-      <c r="L140" t="n">
+      <c r="M140" t="n">
         <v>15.81287908112917</v>
       </c>
-      <c r="M140" t="n">
+      <c r="N140" t="n">
         <v>6.98002161</v>
       </c>
     </row>
@@ -7031,46 +7453,49 @@
       <c r="A141" s="1" t="n">
         <v>139</v>
       </c>
-      <c r="B141" s="2" t="n">
+      <c r="B141" t="n">
+        <v>139</v>
+      </c>
+      <c r="C141" s="2" t="n">
         <v>45422.83362268518</v>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>TRXEUR</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
         <v>0.1200639</v>
       </c>
-      <c r="F141" t="n">
+      <c r="G141" t="n">
         <v>163.24640485</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>20</v>
       </c>
-      <c r="H141" t="n">
+      <c r="I141" t="n">
         <v>0.4</v>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="J141" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J141" t="n">
+      <c r="K141" t="n">
         <v>1.0763</v>
       </c>
-      <c r="K141" t="n">
+      <c r="L141" t="n">
         <v>0.12922477557</v>
       </c>
-      <c r="L141" t="n">
+      <c r="M141" t="n">
         <v>21.09548002935061</v>
       </c>
-      <c r="M141" t="n">
+      <c r="N141" t="n">
         <v>163.24640485</v>
       </c>
     </row>
@@ -7078,46 +7503,49 @@
       <c r="A142" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="B142" s="2" t="n">
+      <c r="B142" t="n">
+        <v>140</v>
+      </c>
+      <c r="C142" s="2" t="n">
         <v>45422.83130787037</v>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
         <v>140.17980062</v>
       </c>
-      <c r="F142" t="n">
+      <c r="G142" t="n">
         <v>0.13982043</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>20</v>
       </c>
-      <c r="H142" t="n">
+      <c r="I142" t="n">
         <v>0.4</v>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="J142" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J142" t="n">
+      <c r="K142" t="n">
         <v>1.076308335</v>
       </c>
-      <c r="K142" t="n">
+      <c r="L142" t="n">
         <v>150.8766878059442</v>
       </c>
-      <c r="L142" t="n">
+      <c r="M142" t="n">
         <v>21.09564336600287</v>
       </c>
-      <c r="M142" t="n">
+      <c r="N142" t="n">
         <v>0.13982043</v>
       </c>
     </row>
@@ -7125,46 +7553,49 @@
       <c r="A143" s="1" t="n">
         <v>141</v>
       </c>
-      <c r="B143" s="2" t="n">
+      <c r="B143" t="n">
+        <v>141</v>
+      </c>
+      <c r="C143" s="2" t="n">
         <v>45422.82967592592</v>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>TNSREUR</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
         <v>0.79988478</v>
       </c>
-      <c r="F143" t="n">
+      <c r="G143" t="n">
         <v>18.36514507</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>15</v>
       </c>
-      <c r="H143" t="n">
+      <c r="I143" t="n">
         <v>0.31</v>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="J143" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J143" t="n">
+      <c r="K143" t="n">
         <v>1.076426665</v>
       </c>
-      <c r="K143" t="n">
+      <c r="L143" t="n">
         <v>0.8610173061196587</v>
       </c>
-      <c r="L143" t="n">
+      <c r="M143" t="n">
         <v>15.81270773466813</v>
       </c>
-      <c r="M143" t="n">
+      <c r="N143" t="n">
         <v>18.36514507</v>
       </c>
     </row>
@@ -7172,46 +7603,49 @@
       <c r="A144" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="B144" s="2" t="n">
+      <c r="B144" t="n">
+        <v>142</v>
+      </c>
+      <c r="C144" s="2" t="n">
         <v>45422.08221064815</v>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E144" t="n">
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
         <v>143.75063899</v>
       </c>
-      <c r="F144" t="n">
+      <c r="G144" t="n">
         <v>0.13634722</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>20</v>
       </c>
-      <c r="H144" t="n">
+      <c r="I144" t="n">
         <v>0.4</v>
       </c>
-      <c r="I144" t="inlineStr">
+      <c r="J144" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J144" t="n">
+      <c r="K144" t="n">
         <v>1.077761665</v>
       </c>
-      <c r="K144" t="n">
+      <c r="L144" t="n">
         <v>154.9289280226763</v>
       </c>
-      <c r="L144" t="n">
+      <c r="M144" t="n">
         <v>21.12412863347201</v>
       </c>
-      <c r="M144" t="n">
+      <c r="N144" t="n">
         <v>0.13634722</v>
       </c>
     </row>
@@ -7219,46 +7653,49 @@
       <c r="A145" s="1" t="n">
         <v>143</v>
       </c>
-      <c r="B145" s="2" t="n">
+      <c r="B145" t="n">
+        <v>143</v>
+      </c>
+      <c r="C145" s="2" t="n">
         <v>45422.07099537037</v>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>USDTEUR</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
         <v>0.93873598</v>
       </c>
-      <c r="F145" t="n">
+      <c r="G145" t="n">
         <v>26.08827246</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>25</v>
       </c>
-      <c r="H145" t="n">
+      <c r="I145" t="n">
         <v>0.51</v>
       </c>
-      <c r="I145" t="inlineStr">
+      <c r="J145" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J145" t="n">
+      <c r="K145" t="n">
         <v>1.0778</v>
       </c>
-      <c r="K145" t="n">
+      <c r="L145" t="n">
         <v>1.011769639244</v>
       </c>
-      <c r="L145" t="n">
+      <c r="M145" t="n">
         <v>26.39532201535338</v>
       </c>
-      <c r="M145" t="n">
+      <c r="N145" t="n">
         <v>26.08827246</v>
       </c>
     </row>
@@ -7266,46 +7703,49 @@
       <c r="A146" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="B146" s="2" t="n">
+      <c r="B146" t="n">
+        <v>144</v>
+      </c>
+      <c r="C146" s="2" t="n">
         <v>45422.06987268518</v>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>MKREUR</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
         <v>2583.15065304</v>
       </c>
-      <c r="F146" t="n">
+      <c r="G146" t="n">
         <v>0.00682887</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>18</v>
       </c>
-      <c r="H146" t="n">
+      <c r="I146" t="n">
         <v>0.36</v>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="J146" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J146" t="n">
+      <c r="K146" t="n">
         <v>1.077938331666667</v>
       </c>
-      <c r="K146" t="n">
+      <c r="L146" t="n">
         <v>2784.477105381599</v>
       </c>
-      <c r="L146" t="n">
+      <c r="M146" t="n">
         <v>19.01483217062724</v>
       </c>
-      <c r="M146" t="n">
+      <c r="N146" t="n">
         <v>0.006828869999999999</v>
       </c>
     </row>
@@ -7313,46 +7753,49 @@
       <c r="A147" s="1" t="n">
         <v>145</v>
       </c>
-      <c r="B147" s="2" t="n">
+      <c r="B147" t="n">
+        <v>145</v>
+      </c>
+      <c r="C147" s="2" t="n">
         <v>45422.05619212963</v>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>FETEUR</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
         <v>2.1432031</v>
       </c>
-      <c r="F147" t="n">
+      <c r="G147" t="n">
         <v>11.42682187</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>25</v>
       </c>
-      <c r="H147" t="n">
+      <c r="I147" t="n">
         <v>0.51</v>
       </c>
-      <c r="I147" t="inlineStr">
+      <c r="J147" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J147" t="n">
+      <c r="K147" t="n">
         <v>1.077691668333334</v>
       </c>
-      <c r="K147" t="n">
+      <c r="L147" t="n">
         <v>2.309712124416173</v>
       </c>
-      <c r="L147" t="n">
+      <c r="M147" t="n">
         <v>26.39266901668289</v>
       </c>
-      <c r="M147" t="n">
+      <c r="N147" t="n">
         <v>11.42682187</v>
       </c>
     </row>
@@ -7360,46 +7803,49 @@
       <c r="A148" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="B148" s="2" t="n">
+      <c r="B148" t="n">
+        <v>146</v>
+      </c>
+      <c r="C148" s="2" t="n">
         <v>45422.01804398148</v>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>RNDREUR</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
         <v>10.23426316</v>
       </c>
-      <c r="F148" t="n">
+      <c r="G148" t="n">
         <v>2.39294218</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>25</v>
       </c>
-      <c r="H148" t="n">
+      <c r="I148" t="n">
         <v>0.51</v>
       </c>
-      <c r="I148" t="inlineStr">
+      <c r="J148" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J148" t="n">
+      <c r="K148" t="n">
         <v>1.077698335</v>
       </c>
-      <c r="K148" t="n">
+      <c r="L148" t="n">
         <v>11.02944836748384</v>
       </c>
-      <c r="L148" t="n">
+      <c r="M148" t="n">
         <v>26.39283222068422</v>
       </c>
-      <c r="M148" t="n">
+      <c r="N148" t="n">
         <v>2.39294218</v>
       </c>
     </row>
@@ -7407,46 +7853,49 @@
       <c r="A149" s="1" t="n">
         <v>147</v>
       </c>
-      <c r="B149" s="2" t="n">
+      <c r="B149" t="n">
+        <v>147</v>
+      </c>
+      <c r="C149" s="2" t="n">
         <v>45421.93954861111</v>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>TRXEUR</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
         <v>0.11898276</v>
       </c>
-      <c r="F149" t="n">
+      <c r="G149" t="n">
         <v>205.82814242</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>25</v>
       </c>
-      <c r="H149" t="n">
+      <c r="I149" t="n">
         <v>0.51</v>
       </c>
-      <c r="I149" t="inlineStr">
+      <c r="J149" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J149" t="n">
+      <c r="K149" t="n">
         <v>1.077904998333333</v>
       </c>
-      <c r="K149" t="n">
+      <c r="L149" t="n">
         <v>0.1282521117194954</v>
       </c>
-      <c r="L149" t="n">
+      <c r="M149" t="n">
         <v>26.39789391666605</v>
       </c>
-      <c r="M149" t="n">
+      <c r="N149" t="n">
         <v>205.82814242</v>
       </c>
     </row>
@@ -7454,46 +7903,49 @@
       <c r="A150" s="1" t="n">
         <v>148</v>
       </c>
-      <c r="B150" s="2" t="n">
+      <c r="B150" t="n">
+        <v>148</v>
+      </c>
+      <c r="C150" s="2" t="n">
         <v>45421.81724537037</v>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>UMAEUR</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E150" t="n">
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
         <v>3.80349912</v>
       </c>
-      <c r="F150" t="n">
+      <c r="G150" t="n">
         <v>6.43880785</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>25</v>
       </c>
-      <c r="H150" t="n">
+      <c r="I150" t="n">
         <v>0.51</v>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="J150" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J150" t="n">
+      <c r="K150" t="n">
         <v>1.077516665</v>
       </c>
-      <c r="K150" t="n">
+      <c r="L150" t="n">
         <v>4.098333687112835</v>
       </c>
-      <c r="L150" t="n">
+      <c r="M150" t="n">
         <v>26.38838311650157</v>
       </c>
-      <c r="M150" t="n">
+      <c r="N150" t="n">
         <v>6.43880785</v>
       </c>
     </row>
@@ -7501,46 +7953,49 @@
       <c r="A151" s="1" t="n">
         <v>149</v>
       </c>
-      <c r="B151" s="2" t="n">
+      <c r="B151" t="n">
+        <v>149</v>
+      </c>
+      <c r="C151" s="2" t="n">
         <v>45418.97721064815</v>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>ETHEUR</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
         <v>2912.26895648</v>
       </c>
-      <c r="F151" t="n">
+      <c r="G151" t="n">
         <v>0.00840723</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>25</v>
       </c>
-      <c r="H151" t="n">
+      <c r="I151" t="n">
         <v>0.51</v>
       </c>
-      <c r="I151" t="inlineStr">
+      <c r="J151" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J151" t="n">
+      <c r="K151" t="n">
         <v>1.076</v>
       </c>
-      <c r="K151" t="n">
+      <c r="L151" t="n">
         <v>3133.60139717248</v>
       </c>
-      <c r="L151" t="n">
+      <c r="M151" t="n">
         <v>26.34490767435039</v>
       </c>
-      <c r="M151" t="n">
+      <c r="N151" t="n">
         <v>0.00840723</v>
       </c>
     </row>
@@ -7548,46 +8003,49 @@
       <c r="A152" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="B152" s="2" t="n">
+      <c r="B152" t="n">
+        <v>150</v>
+      </c>
+      <c r="C152" s="2" t="n">
         <v>45418.96918981482</v>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>BTCEUR</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
         <v>59899.71272325</v>
       </c>
-      <c r="F152" t="n">
+      <c r="G152" t="n">
         <v>0.00040885</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>25</v>
       </c>
-      <c r="H152" t="n">
+      <c r="I152" t="n">
         <v>0.51</v>
       </c>
-      <c r="I152" t="inlineStr">
+      <c r="J152" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J152" t="n">
+      <c r="K152" t="n">
         <v>1.0761</v>
       </c>
-      <c r="K152" t="n">
+      <c r="L152" t="n">
         <v>64458.08086148932</v>
       </c>
-      <c r="L152" t="n">
+      <c r="M152" t="n">
         <v>26.35368636021991</v>
       </c>
-      <c r="M152" t="n">
+      <c r="N152" t="n">
         <v>0.00040885</v>
       </c>
     </row>
@@ -7595,46 +8053,49 @@
       <c r="A153" s="1" t="n">
         <v>151</v>
       </c>
-      <c r="B153" s="2" t="n">
+      <c r="B153" t="n">
+        <v>151</v>
+      </c>
+      <c r="C153" s="2" t="n">
         <v>45414.95027777777</v>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>SOLEUR</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
         <v>131.18665751</v>
       </c>
-      <c r="F153" t="n">
+      <c r="G153" t="n">
         <v>0.18668057</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>25</v>
       </c>
-      <c r="H153" t="n">
+      <c r="I153" t="n">
         <v>0.51</v>
       </c>
-      <c r="I153" t="inlineStr">
+      <c r="J153" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J153" t="n">
+      <c r="K153" t="n">
         <v>1.070940001666667</v>
       </c>
-      <c r="K153" t="n">
+      <c r="L153" t="n">
         <v>140.4930392124039</v>
       </c>
-      <c r="L153" t="n">
+      <c r="M153" t="n">
         <v>26.22732064120391</v>
       </c>
-      <c r="M153" t="n">
+      <c r="N153" t="n">
         <v>0.18668057</v>
       </c>
     </row>

--- a/Trade History Reconstructed.xlsx
+++ b/Trade History Reconstructed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Trade History Reconstructed.xlsx
+++ b/Trade History Reconstructed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Trade History Reconstructed.xlsx
+++ b/Trade History Reconstructed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Jupyter\Projets\Risk Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AD31FA-9355-4DDF-B3F8-72C865E27BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484F9082-FCAD-481C-A45A-384C7BEC2DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="70">
   <si>
     <t>Date(UTC)</t>
   </si>
@@ -231,16 +231,13 @@
   <si>
     <t>UMAEUR</t>
   </si>
-  <si>
-    <t>1,132,18095891</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -297,7 +294,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -657,8 +654,8 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
-        <v>70</v>
+      <c r="D2">
+        <v>1132.1809589100001</v>
       </c>
       <c r="E2">
         <v>7.2999999999999995E-2</v>
